--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_machinery.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_machinery.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="sase_9528" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,112 +590,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.264</v>
+        <v>-0.0977</v>
       </c>
       <c r="G2">
-        <v>-0.3744164332399627</v>
+        <v>-0.1064265247646336</v>
       </c>
       <c r="H2">
-        <v>-0.3744164332399627</v>
+        <v>-0.1064265247646336</v>
       </c>
       <c r="I2">
-        <v>-0.4435107376283847</v>
+        <v>0.01923864101514531</v>
       </c>
       <c r="J2">
-        <v>-0.4435107376283847</v>
+        <v>0.01846271792447923</v>
       </c>
       <c r="K2">
-        <v>-78.09999999999999</v>
+        <v>5.500000000000002</v>
       </c>
       <c r="L2">
-        <v>-0.7292250233426704</v>
+        <v>0.02251330331559559</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>8.42</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.02526252625262526</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>1.53090909090909</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>8.42</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.02526252625262526</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>1.53090909090909</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>25.9</v>
+        <v>15.16</v>
       </c>
       <c r="V2">
-        <v>0.1697247706422018</v>
+        <v>0.04548454845484549</v>
       </c>
       <c r="W2">
-        <v>-2.2</v>
+        <v>1.751302125986831</v>
       </c>
       <c r="X2">
-        <v>0.1508691410700969</v>
+        <v>0.2230037520644241</v>
       </c>
       <c r="Y2">
-        <v>-2.350869141070096</v>
+        <v>1.528298373922407</v>
       </c>
       <c r="Z2">
-        <v>0.3197969543147208</v>
+        <v>0.7513224258826424</v>
       </c>
       <c r="AA2">
-        <v>-0.1418333830994327</v>
+        <v>0.08076912606220944</v>
       </c>
       <c r="AB2">
-        <v>0.06892622019589201</v>
+        <v>0.1135597421225913</v>
       </c>
       <c r="AC2">
-        <v>-0.2107596032953247</v>
+        <v>-0.03279061606038181</v>
       </c>
       <c r="AD2">
-        <v>299.4</v>
+        <v>308.93</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>299.4</v>
+        <v>308.93</v>
       </c>
       <c r="AG2">
-        <v>273.5</v>
+        <v>293.77</v>
       </c>
       <c r="AH2">
-        <v>0.6623893805309734</v>
+        <v>0.4810270463852514</v>
       </c>
       <c r="AI2">
-        <v>0.9934961507831166</v>
+        <v>0.685247210700264</v>
       </c>
       <c r="AJ2">
-        <v>0.6418681060783853</v>
+        <v>0.4684803929385874</v>
       </c>
       <c r="AK2">
-        <v>0.9928846293472737</v>
+        <v>0.6742947643858884</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>9.505000000000001</v>
       </c>
       <c r="AM2">
-        <v>-13.9</v>
+        <v>9.505000000000001</v>
       </c>
       <c r="AN2">
-        <v>-7.50375939849624</v>
+        <v>24.8276139194728</v>
+      </c>
+      <c r="AO2">
+        <v>0.4944765912677537</v>
       </c>
       <c r="AP2">
-        <v>-6.854636591478697</v>
+        <v>23.60925821747167</v>
       </c>
       <c r="AQ2">
-        <v>3.41726618705036</v>
+        <v>0.4944765912677537</v>
       </c>
     </row>
     <row r="3">
@@ -704,121 +712,8964 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Gas Arabian Services Company (SASE:9528)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Machinery</t>
+        </is>
+      </c>
+      <c r="G3">
+        <v>0.0930232558139535</v>
+      </c>
+      <c r="H3">
+        <v>0.0930232558139535</v>
+      </c>
+      <c r="I3">
+        <v>0.09560723514211887</v>
+      </c>
+      <c r="J3">
+        <v>0.08789527031850045</v>
+      </c>
+      <c r="K3">
+        <v>16.6</v>
+      </c>
+      <c r="L3">
+        <v>0.1429801894918174</v>
+      </c>
+      <c r="M3">
+        <v>8.42</v>
+      </c>
+      <c r="N3">
+        <v>0.03399273314493339</v>
+      </c>
+      <c r="O3">
+        <v>0.5072289156626506</v>
+      </c>
+      <c r="P3">
+        <v>8.42</v>
+      </c>
+      <c r="Q3">
+        <v>0.03399273314493339</v>
+      </c>
+      <c r="R3">
+        <v>0.5072289156626506</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>6.57</v>
+      </c>
+      <c r="V3">
+        <v>0.02652402099313686</v>
+      </c>
+      <c r="W3">
+        <v>0.2664526484751204</v>
+      </c>
+      <c r="X3">
+        <v>0.1162689002633027</v>
+      </c>
+      <c r="Y3">
+        <v>0.1501837482118177</v>
+      </c>
+      <c r="Z3">
+        <v>2.107460519150481</v>
+      </c>
+      <c r="AA3">
+        <v>0.1852358120162988</v>
+      </c>
+      <c r="AB3">
+        <v>0.1147637224393481</v>
+      </c>
+      <c r="AC3">
+        <v>0.07047208957695071</v>
+      </c>
+      <c r="AD3">
+        <v>6.13</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>6.13</v>
+      </c>
+      <c r="AG3">
+        <v>-0.4400000000000004</v>
+      </c>
+      <c r="AH3">
+        <v>0.02415002166804554</v>
+      </c>
+      <c r="AI3">
+        <v>0.07999478011222759</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.001779503356790425</v>
+      </c>
+      <c r="AK3">
+        <v>-0.006280331144733091</v>
+      </c>
+      <c r="AL3">
+        <v>0.255</v>
+      </c>
+      <c r="AM3">
+        <v>0.255</v>
+      </c>
+      <c r="AN3">
+        <v>0.5108333333333334</v>
+      </c>
+      <c r="AO3">
+        <v>43.52941176470588</v>
+      </c>
+      <c r="AP3">
+        <v>-0.0366666666666667</v>
+      </c>
+      <c r="AQ3">
+        <v>43.52941176470588</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>The Saudi Arabian Amiantit Company (SASE:2160)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Machinery</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.0977</v>
+      </c>
+      <c r="G4">
+        <v>-0.2870514820592824</v>
+      </c>
+      <c r="H4">
+        <v>-0.2870514820592824</v>
+      </c>
+      <c r="I4">
+        <v>-0.0499219968798752</v>
+      </c>
+      <c r="J4">
+        <v>-0.0499219968798752</v>
+      </c>
+      <c r="K4">
+        <v>-11.1</v>
+      </c>
+      <c r="L4">
+        <v>-0.08658346333853355</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>8.59</v>
+      </c>
+      <c r="V4">
+        <v>0.1003504672897196</v>
+      </c>
+      <c r="W4">
+        <v>3.236151603498542</v>
+      </c>
+      <c r="X4">
+        <v>0.3297386038655455</v>
+      </c>
+      <c r="Y4">
+        <v>2.906412999632996</v>
+      </c>
+      <c r="Z4">
+        <v>0.4746917465842189</v>
+      </c>
+      <c r="AA4">
+        <v>-0.02369755989187989</v>
+      </c>
+      <c r="AB4">
+        <v>0.1123557618058345</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1360533216977143</v>
+      </c>
+      <c r="AD4">
+        <v>302.8</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>302.8</v>
+      </c>
+      <c r="AG4">
+        <v>294.21</v>
+      </c>
+      <c r="AH4">
+        <v>0.7796086508753862</v>
+      </c>
+      <c r="AI4">
+        <v>0.8091929449492249</v>
+      </c>
+      <c r="AJ4">
+        <v>0.7746241541823543</v>
+      </c>
+      <c r="AK4">
+        <v>0.8047099368179208</v>
+      </c>
+      <c r="AL4">
+        <v>9.25</v>
+      </c>
+      <c r="AM4">
+        <v>9.25</v>
+      </c>
+      <c r="AN4">
+        <v>683.5214446952596</v>
+      </c>
+      <c r="AO4">
+        <v>-0.6918918918918919</v>
+      </c>
+      <c r="AP4">
+        <v>664.1309255079008</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.6918918918918919</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gas Arabian Services Company (SASE:9528)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SASE:9528</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Machinery</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0241500216680455</v>
+      </c>
+      <c r="F2">
+        <v>0.17</v>
+      </c>
+      <c r="G2">
+        <v>247.7</v>
+      </c>
+      <c r="H2">
+        <v>216.330833967312</v>
+      </c>
+      <c r="I2">
+        <v>247.26</v>
+      </c>
+      <c r="J2">
+        <v>252.911933967312</v>
+      </c>
+      <c r="K2">
+        <v>6.13</v>
+      </c>
+      <c r="L2">
+        <v>43.1511</v>
+      </c>
+      <c r="M2">
+        <v>0.114763722439348</v>
+      </c>
+      <c r="N2">
+        <v>0.113066127800758</v>
+      </c>
+      <c r="O2">
+        <v>0.053942752293578</v>
+      </c>
+      <c r="P2">
+        <v>0.044</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.116268900263303</v>
+      </c>
+      <c r="T2">
+        <v>0.127212202169588</v>
+      </c>
+      <c r="U2">
+        <v>1.08630866485024</v>
+      </c>
+      <c r="V2">
+        <v>1.23976125863258</v>
+      </c>
+      <c r="W2">
+        <v>4.571673196574995</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>247.7</v>
+      </c>
+      <c r="AB2">
+        <v>0.07131389334354851</v>
+      </c>
+      <c r="AC2">
+        <v>0.06742844036697249</v>
+      </c>
+      <c r="AD2">
+        <v>0.2</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>12</v>
+      </c>
+      <c r="AH2">
+        <v>1.15</v>
+      </c>
+      <c r="AI2">
+        <v>3.22</v>
+      </c>
+      <c r="AJ2">
+        <v>6.13</v>
+      </c>
+      <c r="AK2">
+        <v>6.13</v>
+      </c>
+      <c r="AL2">
+        <v>0.255</v>
+      </c>
+      <c r="AM2">
+        <v>6.13</v>
+      </c>
+      <c r="AN2">
+        <v>6.57</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1147649356115504</v>
+      </c>
+      <c r="C2">
+        <v>253.8260512181529</v>
+      </c>
+      <c r="D2">
+        <v>247.2560512181529</v>
+      </c>
+      <c r="E2">
+        <v>-6.13</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>6.57</v>
+      </c>
+      <c r="H2">
+        <v>247.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>12</v>
+      </c>
+      <c r="K2">
+        <v>1.15</v>
+      </c>
+      <c r="L2">
+        <v>10.85</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>10.85</v>
+      </c>
+      <c r="O2">
+        <v>2.169999999999999</v>
+      </c>
+      <c r="P2">
+        <v>8.68</v>
+      </c>
+      <c r="Q2">
+        <v>9.83</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1147649356115504</v>
+      </c>
+      <c r="T2">
+        <v>1.065219300895492</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.2</v>
+      </c>
+      <c r="W2">
+        <v>0.03656</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1145906057403273</v>
+      </c>
+      <c r="C3">
+        <v>251.8564775813605</v>
+      </c>
       <c r="D3">
-        <v>-0.264</v>
+        <v>247.8247775813605</v>
+      </c>
+      <c r="E3">
+        <v>-3.5917</v>
+      </c>
+      <c r="F3">
+        <v>2.5383</v>
       </c>
       <c r="G3">
-        <v>-0.3744164332399627</v>
+        <v>6.57</v>
       </c>
       <c r="H3">
-        <v>-0.3744164332399627</v>
+        <v>247.7</v>
       </c>
       <c r="I3">
-        <v>-0.4435107376283847</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>-0.4435107376283847</v>
+        <v>12</v>
       </c>
       <c r="K3">
-        <v>-78.09999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="L3">
-        <v>-0.7292250233426704</v>
+        <v>10.85</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.11600031</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>10.73399969</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>2.146799938</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>8.587199752</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>9.737199752</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.1153787936770983</v>
+      </c>
+      <c r="T3">
+        <v>1.073827133630001</v>
       </c>
       <c r="U3">
-        <v>25.9</v>
+        <v>0.0457</v>
       </c>
       <c r="V3">
-        <v>0.1697247706422018</v>
+        <v>0.2</v>
       </c>
       <c r="W3">
-        <v>-2.2</v>
-      </c>
-      <c r="X3">
-        <v>0.1508691410700969</v>
+        <v>0.03656</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y3">
-        <v>-2.350869141070096</v>
+        <v>93.53423279644683</v>
       </c>
       <c r="Z3">
-        <v>0.3197969543147208</v>
-      </c>
-      <c r="AA3">
-        <v>-0.1418333830994327</v>
-      </c>
-      <c r="AB3">
-        <v>0.06892622019589201</v>
-      </c>
-      <c r="AC3">
-        <v>-0.2107596032953247</v>
-      </c>
-      <c r="AD3">
-        <v>299.4</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>299.4</v>
-      </c>
-      <c r="AG3">
-        <v>273.5</v>
-      </c>
-      <c r="AH3">
-        <v>0.6623893805309734</v>
-      </c>
-      <c r="AI3">
-        <v>0.9934961507831166</v>
-      </c>
-      <c r="AJ3">
-        <v>0.6418681060783853</v>
-      </c>
-      <c r="AK3">
-        <v>0.9928846293472737</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>-13.9</v>
-      </c>
-      <c r="AN3">
-        <v>-7.50375939849624</v>
-      </c>
-      <c r="AP3">
-        <v>-6.854636591478697</v>
-      </c>
-      <c r="AQ3">
-        <v>3.41726618705036</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1144162758691042</v>
+      </c>
+      <c r="C4">
+        <v>249.8895262898904</v>
+      </c>
+      <c r="D4">
+        <v>248.3961262898904</v>
+      </c>
+      <c r="E4">
+        <v>-1.0534</v>
+      </c>
+      <c r="F4">
+        <v>5.0766</v>
+      </c>
+      <c r="G4">
+        <v>6.57</v>
+      </c>
+      <c r="H4">
+        <v>247.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <v>1.15</v>
+      </c>
+      <c r="L4">
+        <v>10.85</v>
+      </c>
+      <c r="M4">
+        <v>0.23200062</v>
+      </c>
+      <c r="N4">
+        <v>10.61799938</v>
+      </c>
+      <c r="O4">
+        <v>2.123599875999999</v>
+      </c>
+      <c r="P4">
+        <v>8.494399504</v>
+      </c>
+      <c r="Q4">
+        <v>9.644399504000001</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1160051794582696</v>
+      </c>
+      <c r="T4">
+        <v>1.082610636420316</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.2</v>
+      </c>
+      <c r="W4">
+        <v>0.03656</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>46.76711639822341</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1142419459978811</v>
+      </c>
+      <c r="C5">
+        <v>247.9252155227457</v>
+      </c>
+      <c r="D5">
+        <v>248.9701155227457</v>
+      </c>
+      <c r="E5">
+        <v>1.4849</v>
+      </c>
+      <c r="F5">
+        <v>7.6149</v>
+      </c>
+      <c r="G5">
+        <v>6.57</v>
+      </c>
+      <c r="H5">
+        <v>247.7</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>12</v>
+      </c>
+      <c r="K5">
+        <v>1.15</v>
+      </c>
+      <c r="L5">
+        <v>10.85</v>
+      </c>
+      <c r="M5">
+        <v>0.34800093</v>
+      </c>
+      <c r="N5">
+        <v>10.50199907</v>
+      </c>
+      <c r="O5">
+        <v>2.100399814</v>
+      </c>
+      <c r="P5">
+        <v>8.401599256000001</v>
+      </c>
+      <c r="Q5">
+        <v>9.551599256000001</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1166444804101867</v>
+      </c>
+      <c r="T5">
+        <v>1.091575242360947</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.2</v>
+      </c>
+      <c r="W5">
+        <v>0.03656</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>31.17807759881561</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.114067616126658</v>
+      </c>
+      <c r="C6">
+        <v>245.9635636273494</v>
+      </c>
+      <c r="D6">
+        <v>249.5467636273494</v>
+      </c>
+      <c r="E6">
+        <v>4.0232</v>
+      </c>
+      <c r="F6">
+        <v>10.1532</v>
+      </c>
+      <c r="G6">
+        <v>6.57</v>
+      </c>
+      <c r="H6">
+        <v>247.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>1.15</v>
+      </c>
+      <c r="L6">
+        <v>10.85</v>
+      </c>
+      <c r="M6">
+        <v>0.46400124</v>
+      </c>
+      <c r="N6">
+        <v>10.38599876</v>
+      </c>
+      <c r="O6">
+        <v>2.077199751999999</v>
+      </c>
+      <c r="P6">
+        <v>8.308799008000001</v>
+      </c>
+      <c r="Q6">
+        <v>9.458799008000002</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1172971001319354</v>
+      </c>
+      <c r="T6">
+        <v>1.100726610925342</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.2</v>
+      </c>
+      <c r="W6">
+        <v>0.03656</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>23.38355819911171</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1138932862554349</v>
+      </c>
+      <c r="C7">
+        <v>244.0045891214997</v>
+      </c>
+      <c r="D7">
+        <v>250.1260891214997</v>
+      </c>
+      <c r="E7">
+        <v>6.5615</v>
+      </c>
+      <c r="F7">
+        <v>12.6915</v>
+      </c>
+      <c r="G7">
+        <v>6.57</v>
+      </c>
+      <c r="H7">
+        <v>247.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>1.15</v>
+      </c>
+      <c r="L7">
+        <v>10.85</v>
+      </c>
+      <c r="M7">
+        <v>0.5800015500000001</v>
+      </c>
+      <c r="N7">
+        <v>10.26999845</v>
+      </c>
+      <c r="O7">
+        <v>2.053999689999999</v>
+      </c>
+      <c r="P7">
+        <v>8.21599876</v>
+      </c>
+      <c r="Q7">
+        <v>9.36599876</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1179634592162473</v>
+      </c>
+      <c r="T7">
+        <v>1.110070639880565</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.2</v>
+      </c>
+      <c r="W7">
+        <v>0.03656</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>18.70684655928936</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1137189563842118</v>
+      </c>
+      <c r="C8">
+        <v>242.0483106953516</v>
+      </c>
+      <c r="D8">
+        <v>250.7081106953516</v>
+      </c>
+      <c r="E8">
+        <v>9.099799999999998</v>
+      </c>
+      <c r="F8">
+        <v>15.2298</v>
+      </c>
+      <c r="G8">
+        <v>6.57</v>
+      </c>
+      <c r="H8">
+        <v>247.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>12</v>
+      </c>
+      <c r="K8">
+        <v>1.15</v>
+      </c>
+      <c r="L8">
+        <v>10.85</v>
+      </c>
+      <c r="M8">
+        <v>0.6960018600000001</v>
+      </c>
+      <c r="N8">
+        <v>10.15399814</v>
+      </c>
+      <c r="O8">
+        <v>2.030799627999999</v>
+      </c>
+      <c r="P8">
+        <v>8.123198512</v>
+      </c>
+      <c r="Q8">
+        <v>9.273198512</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1186439961534168</v>
+      </c>
+      <c r="T8">
+        <v>1.119613477962496</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.2</v>
+      </c>
+      <c r="W8">
+        <v>0.03656</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>15.5890387994078</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1135446265129887</v>
+      </c>
+      <c r="C9">
+        <v>240.0947472134278</v>
+      </c>
+      <c r="D9">
+        <v>251.2928472134278</v>
+      </c>
+      <c r="E9">
+        <v>11.6381</v>
+      </c>
+      <c r="F9">
+        <v>17.7681</v>
+      </c>
+      <c r="G9">
+        <v>6.57</v>
+      </c>
+      <c r="H9">
+        <v>247.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>12</v>
+      </c>
+      <c r="K9">
+        <v>1.15</v>
+      </c>
+      <c r="L9">
+        <v>10.85</v>
+      </c>
+      <c r="M9">
+        <v>0.8120021700000001</v>
+      </c>
+      <c r="N9">
+        <v>10.03799783</v>
+      </c>
+      <c r="O9">
+        <v>2.007599566</v>
+      </c>
+      <c r="P9">
+        <v>8.030398264</v>
+      </c>
+      <c r="Q9">
+        <v>9.180398264000001</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1193391682935363</v>
+      </c>
+      <c r="T9">
+        <v>1.129361538368769</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.2</v>
+      </c>
+      <c r="W9">
+        <v>0.03656</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>13.36203325663526</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1134726966417657</v>
+      </c>
+      <c r="C10">
+        <v>237.798509747021</v>
+      </c>
+      <c r="D10">
+        <v>251.534909747021</v>
+      </c>
+      <c r="E10">
+        <v>14.1764</v>
+      </c>
+      <c r="F10">
+        <v>20.3064</v>
+      </c>
+      <c r="G10">
+        <v>6.57</v>
+      </c>
+      <c r="H10">
+        <v>247.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>12</v>
+      </c>
+      <c r="K10">
+        <v>1.15</v>
+      </c>
+      <c r="L10">
+        <v>10.85</v>
+      </c>
+      <c r="M10">
+        <v>0.9604927200000001</v>
+      </c>
+      <c r="N10">
+        <v>9.88950728</v>
+      </c>
+      <c r="O10">
+        <v>1.977901456</v>
+      </c>
+      <c r="P10">
+        <v>7.911605824</v>
+      </c>
+      <c r="Q10">
+        <v>9.061605824000001</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1200494528714844</v>
+      </c>
+      <c r="T10">
+        <v>1.1393215131317</v>
+      </c>
+      <c r="U10">
+        <v>0.0473</v>
+      </c>
+      <c r="V10">
+        <v>0.2</v>
+      </c>
+      <c r="W10">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>11.29628551479287</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1135847667705425</v>
+      </c>
+      <c r="C11">
+        <v>234.8832673435805</v>
+      </c>
+      <c r="D11">
+        <v>251.1579673435805</v>
+      </c>
+      <c r="E11">
+        <v>16.7147</v>
+      </c>
+      <c r="F11">
+        <v>22.8447</v>
+      </c>
+      <c r="G11">
+        <v>6.57</v>
+      </c>
+      <c r="H11">
+        <v>247.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>12</v>
+      </c>
+      <c r="K11">
+        <v>1.15</v>
+      </c>
+      <c r="L11">
+        <v>10.85</v>
+      </c>
+      <c r="M11">
+        <v>1.16736417</v>
+      </c>
+      <c r="N11">
+        <v>9.682635830000001</v>
+      </c>
+      <c r="O11">
+        <v>1.936527166</v>
+      </c>
+      <c r="P11">
+        <v>7.746108664000001</v>
+      </c>
+      <c r="Q11">
+        <v>8.896108664000002</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1207753480994973</v>
+      </c>
+      <c r="T11">
+        <v>1.149500388438871</v>
+      </c>
+      <c r="U11">
+        <v>0.0511</v>
+      </c>
+      <c r="V11">
+        <v>0.2</v>
+      </c>
+      <c r="W11">
+        <v>0.04088</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>9.294443224173998</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1134536368993194</v>
+      </c>
+      <c r="C12">
+        <v>232.7861288633981</v>
+      </c>
+      <c r="D12">
+        <v>251.5991288633981</v>
+      </c>
+      <c r="E12">
+        <v>19.253</v>
+      </c>
+      <c r="F12">
+        <v>25.383</v>
+      </c>
+      <c r="G12">
+        <v>6.57</v>
+      </c>
+      <c r="H12">
+        <v>247.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>12</v>
+      </c>
+      <c r="K12">
+        <v>1.15</v>
+      </c>
+      <c r="L12">
+        <v>10.85</v>
+      </c>
+      <c r="M12">
+        <v>1.2970713</v>
+      </c>
+      <c r="N12">
+        <v>9.552928699999999</v>
+      </c>
+      <c r="O12">
+        <v>1.910585739999999</v>
+      </c>
+      <c r="P12">
+        <v>7.64234296</v>
+      </c>
+      <c r="Q12">
+        <v>8.792342959999999</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1215173743325771</v>
+      </c>
+      <c r="T12">
+        <v>1.159905460975091</v>
+      </c>
+      <c r="U12">
+        <v>0.0511</v>
+      </c>
+      <c r="V12">
+        <v>0.2</v>
+      </c>
+      <c r="W12">
+        <v>0.04088</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>8.364998901756595</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1134897070280963</v>
+      </c>
+      <c r="C13">
+        <v>230.1263233261646</v>
+      </c>
+      <c r="D13">
+        <v>251.4776233261646</v>
+      </c>
+      <c r="E13">
+        <v>21.7913</v>
+      </c>
+      <c r="F13">
+        <v>27.9213</v>
+      </c>
+      <c r="G13">
+        <v>6.57</v>
+      </c>
+      <c r="H13">
+        <v>247.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>12</v>
+      </c>
+      <c r="K13">
+        <v>1.15</v>
+      </c>
+      <c r="L13">
+        <v>10.85</v>
+      </c>
+      <c r="M13">
+        <v>1.4798289</v>
+      </c>
+      <c r="N13">
+        <v>9.3701711</v>
+      </c>
+      <c r="O13">
+        <v>1.87403422</v>
+      </c>
+      <c r="P13">
+        <v>7.496136880000001</v>
+      </c>
+      <c r="Q13">
+        <v>8.64613688</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1222760753124678</v>
+      </c>
+      <c r="T13">
+        <v>1.170544355366057</v>
+      </c>
+      <c r="U13">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V13">
+        <v>0.2</v>
+      </c>
+      <c r="W13">
+        <v>0.04240000000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>7.3319287114882</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1133737771568732</v>
+      </c>
+      <c r="C14">
+        <v>227.9789619321892</v>
+      </c>
+      <c r="D14">
+        <v>251.8685619321892</v>
+      </c>
+      <c r="E14">
+        <v>24.3296</v>
+      </c>
+      <c r="F14">
+        <v>30.4596</v>
+      </c>
+      <c r="G14">
+        <v>6.57</v>
+      </c>
+      <c r="H14">
+        <v>247.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>12</v>
+      </c>
+      <c r="K14">
+        <v>1.15</v>
+      </c>
+      <c r="L14">
+        <v>10.85</v>
+      </c>
+      <c r="M14">
+        <v>1.6143588</v>
+      </c>
+      <c r="N14">
+        <v>9.2356412</v>
+      </c>
+      <c r="O14">
+        <v>1.84712824</v>
+      </c>
+      <c r="P14">
+        <v>7.38851296</v>
+      </c>
+      <c r="Q14">
+        <v>8.53851296</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1230520194964468</v>
+      </c>
+      <c r="T14">
+        <v>1.181425042811364</v>
+      </c>
+      <c r="U14">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V14">
+        <v>0.2</v>
+      </c>
+      <c r="W14">
+        <v>0.04240000000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>6.720934652197516</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1134658472856501</v>
+      </c>
+      <c r="C15">
+        <v>225.1300839132559</v>
+      </c>
+      <c r="D15">
+        <v>251.557983913256</v>
+      </c>
+      <c r="E15">
+        <v>26.8679</v>
+      </c>
+      <c r="F15">
+        <v>32.9979</v>
+      </c>
+      <c r="G15">
+        <v>6.57</v>
+      </c>
+      <c r="H15">
+        <v>247.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>12</v>
+      </c>
+      <c r="K15">
+        <v>1.15</v>
+      </c>
+      <c r="L15">
+        <v>10.85</v>
+      </c>
+      <c r="M15">
+        <v>1.8148845</v>
+      </c>
+      <c r="N15">
+        <v>9.0351155</v>
+      </c>
+      <c r="O15">
+        <v>1.8070231</v>
+      </c>
+      <c r="P15">
+        <v>7.2280924</v>
+      </c>
+      <c r="Q15">
+        <v>8.3780924</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1238458014777588</v>
+      </c>
+      <c r="T15">
+        <v>1.192555861002539</v>
+      </c>
+      <c r="U15">
+        <v>0.055</v>
+      </c>
+      <c r="V15">
+        <v>0.2</v>
+      </c>
+      <c r="W15">
+        <v>0.044</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>5.978341872444224</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.113365917414427</v>
+      </c>
+      <c r="C16">
+        <v>222.9289105497846</v>
+      </c>
+      <c r="D16">
+        <v>251.8951105497846</v>
+      </c>
+      <c r="E16">
+        <v>29.4062</v>
+      </c>
+      <c r="F16">
+        <v>35.5362</v>
+      </c>
+      <c r="G16">
+        <v>6.57</v>
+      </c>
+      <c r="H16">
+        <v>247.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>12</v>
+      </c>
+      <c r="K16">
+        <v>1.15</v>
+      </c>
+      <c r="L16">
+        <v>10.85</v>
+      </c>
+      <c r="M16">
+        <v>1.954491</v>
+      </c>
+      <c r="N16">
+        <v>8.895509000000001</v>
+      </c>
+      <c r="O16">
+        <v>1.7791018</v>
+      </c>
+      <c r="P16">
+        <v>7.116407200000001</v>
+      </c>
+      <c r="Q16">
+        <v>8.266407200000002</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1246580435051477</v>
+      </c>
+      <c r="T16">
+        <v>1.203945535430719</v>
+      </c>
+      <c r="U16">
+        <v>0.055</v>
+      </c>
+      <c r="V16">
+        <v>0.2</v>
+      </c>
+      <c r="W16">
+        <v>0.044</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>5.551317452983923</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1132659875432039</v>
+      </c>
+      <c r="C17">
+        <v>220.7286420026591</v>
+      </c>
+      <c r="D17">
+        <v>252.2331420026591</v>
+      </c>
+      <c r="E17">
+        <v>31.94449999999999</v>
+      </c>
+      <c r="F17">
+        <v>38.07449999999999</v>
+      </c>
+      <c r="G17">
+        <v>6.57</v>
+      </c>
+      <c r="H17">
+        <v>247.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>12</v>
+      </c>
+      <c r="K17">
+        <v>1.15</v>
+      </c>
+      <c r="L17">
+        <v>10.85</v>
+      </c>
+      <c r="M17">
+        <v>2.0940975</v>
+      </c>
+      <c r="N17">
+        <v>8.755902499999999</v>
+      </c>
+      <c r="O17">
+        <v>1.7511805</v>
+      </c>
+      <c r="P17">
+        <v>7.004722</v>
+      </c>
+      <c r="Q17">
+        <v>8.154722</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1254893971096517</v>
+      </c>
+      <c r="T17">
+        <v>1.215603202198385</v>
+      </c>
+      <c r="U17">
+        <v>0.055</v>
+      </c>
+      <c r="V17">
+        <v>0.2</v>
+      </c>
+      <c r="W17">
+        <v>0.044</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>5.181229622784995</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1131660576719808</v>
+      </c>
+      <c r="C18">
+        <v>218.5292819194382</v>
+      </c>
+      <c r="D18">
+        <v>252.5720819194381</v>
+      </c>
+      <c r="E18">
+        <v>34.4828</v>
+      </c>
+      <c r="F18">
+        <v>40.6128</v>
+      </c>
+      <c r="G18">
+        <v>6.57</v>
+      </c>
+      <c r="H18">
+        <v>247.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>12</v>
+      </c>
+      <c r="K18">
+        <v>1.15</v>
+      </c>
+      <c r="L18">
+        <v>10.85</v>
+      </c>
+      <c r="M18">
+        <v>2.233704</v>
+      </c>
+      <c r="N18">
+        <v>8.616296</v>
+      </c>
+      <c r="O18">
+        <v>1.7232592</v>
+      </c>
+      <c r="P18">
+        <v>6.893036800000001</v>
+      </c>
+      <c r="Q18">
+        <v>8.043036800000001</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1263405448475962</v>
+      </c>
+      <c r="T18">
+        <v>1.227538432460519</v>
+      </c>
+      <c r="U18">
+        <v>0.055</v>
+      </c>
+      <c r="V18">
+        <v>0.2</v>
+      </c>
+      <c r="W18">
+        <v>0.044</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>4.857402771360933</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1130661278007577</v>
+      </c>
+      <c r="C19">
+        <v>216.3308339673122</v>
+      </c>
+      <c r="D19">
+        <v>252.9119339673122</v>
+      </c>
+      <c r="E19">
+        <v>37.0211</v>
+      </c>
+      <c r="F19">
+        <v>43.1511</v>
+      </c>
+      <c r="G19">
+        <v>6.57</v>
+      </c>
+      <c r="H19">
+        <v>247.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>12</v>
+      </c>
+      <c r="K19">
+        <v>1.15</v>
+      </c>
+      <c r="L19">
+        <v>10.85</v>
+      </c>
+      <c r="M19">
+        <v>2.3733105</v>
+      </c>
+      <c r="N19">
+        <v>8.476689499999999</v>
+      </c>
+      <c r="O19">
+        <v>1.6953379</v>
+      </c>
+      <c r="P19">
+        <v>6.7813516</v>
+      </c>
+      <c r="Q19">
+        <v>7.931351599999999</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1272122021695876</v>
+      </c>
+      <c r="T19">
+        <v>1.239761258632585</v>
+      </c>
+      <c r="U19">
+        <v>0.055</v>
+      </c>
+      <c r="V19">
+        <v>0.2</v>
+      </c>
+      <c r="W19">
+        <v>0.044</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>4.571673196574995</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1135133979295346</v>
+      </c>
+      <c r="C20">
+        <v>212.2784821853083</v>
+      </c>
+      <c r="D20">
+        <v>251.3978821853082</v>
+      </c>
+      <c r="E20">
+        <v>39.55939999999999</v>
+      </c>
+      <c r="F20">
+        <v>45.68939999999999</v>
+      </c>
+      <c r="G20">
+        <v>6.57</v>
+      </c>
+      <c r="H20">
+        <v>247.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>12</v>
+      </c>
+      <c r="K20">
+        <v>1.15</v>
+      </c>
+      <c r="L20">
+        <v>10.85</v>
+      </c>
+      <c r="M20">
+        <v>2.68653672</v>
+      </c>
+      <c r="N20">
+        <v>8.16346328</v>
+      </c>
+      <c r="O20">
+        <v>1.632692656</v>
+      </c>
+      <c r="P20">
+        <v>6.530770624000001</v>
+      </c>
+      <c r="Q20">
+        <v>7.680770624000001</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1281051194262617</v>
+      </c>
+      <c r="T20">
+        <v>1.252282202516164</v>
+      </c>
+      <c r="U20">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V20">
+        <v>0.2</v>
+      </c>
+      <c r="W20">
+        <v>0.04704000000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>4.038656877170844</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1140822680583115</v>
+      </c>
+      <c r="C21">
+        <v>207.8404951899295</v>
+      </c>
+      <c r="D21">
+        <v>249.4981951899295</v>
+      </c>
+      <c r="E21">
+        <v>42.0977</v>
+      </c>
+      <c r="F21">
+        <v>48.2277</v>
+      </c>
+      <c r="G21">
+        <v>6.57</v>
+      </c>
+      <c r="H21">
+        <v>247.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>12</v>
+      </c>
+      <c r="K21">
+        <v>1.15</v>
+      </c>
+      <c r="L21">
+        <v>10.85</v>
+      </c>
+      <c r="M21">
+        <v>3.0383451</v>
+      </c>
+      <c r="N21">
+        <v>7.8116549</v>
+      </c>
+      <c r="O21">
+        <v>1.56233098</v>
+      </c>
+      <c r="P21">
+        <v>6.24932392</v>
+      </c>
+      <c r="Q21">
+        <v>7.39932392</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1290200840226068</v>
+      </c>
+      <c r="T21">
+        <v>1.26511230550798</v>
+      </c>
+      <c r="U21">
+        <v>0.063</v>
+      </c>
+      <c r="V21">
+        <v>0.2</v>
+      </c>
+      <c r="W21">
+        <v>0.0504</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>3.571022922972114</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1151823381870884</v>
+      </c>
+      <c r="C22">
+        <v>201.7088839844002</v>
+      </c>
+      <c r="D22">
+        <v>245.9048839844002</v>
+      </c>
+      <c r="E22">
+        <v>44.636</v>
+      </c>
+      <c r="F22">
+        <v>50.766</v>
+      </c>
+      <c r="G22">
+        <v>6.57</v>
+      </c>
+      <c r="H22">
+        <v>247.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>12</v>
+      </c>
+      <c r="K22">
+        <v>1.15</v>
+      </c>
+      <c r="L22">
+        <v>10.85</v>
+      </c>
+      <c r="M22">
+        <v>3.5586966</v>
+      </c>
+      <c r="N22">
+        <v>7.2913034</v>
+      </c>
+      <c r="O22">
+        <v>1.45826068</v>
+      </c>
+      <c r="P22">
+        <v>5.833042720000001</v>
+      </c>
+      <c r="Q22">
+        <v>6.98304272</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1299579227338605</v>
+      </c>
+      <c r="T22">
+        <v>1.27826316107459</v>
+      </c>
+      <c r="U22">
+        <v>0.0701</v>
+      </c>
+      <c r="V22">
+        <v>0.2</v>
+      </c>
+      <c r="W22">
+        <v>0.05608</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>3.048869071895592</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1187816083158653</v>
+      </c>
+      <c r="C23">
+        <v>188.1045636569516</v>
+      </c>
+      <c r="D23">
+        <v>234.8388636569516</v>
+      </c>
+      <c r="E23">
+        <v>47.1743</v>
+      </c>
+      <c r="F23">
+        <v>53.3043</v>
+      </c>
+      <c r="G23">
+        <v>6.57</v>
+      </c>
+      <c r="H23">
+        <v>247.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>12</v>
+      </c>
+      <c r="K23">
+        <v>1.15</v>
+      </c>
+      <c r="L23">
+        <v>10.85</v>
+      </c>
+      <c r="M23">
+        <v>4.872013020000001</v>
+      </c>
+      <c r="N23">
+        <v>5.977986979999999</v>
+      </c>
+      <c r="O23">
+        <v>1.195597395999999</v>
+      </c>
+      <c r="P23">
+        <v>4.782389584</v>
+      </c>
+      <c r="Q23">
+        <v>5.932389583999999</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1309195041972979</v>
+      </c>
+      <c r="T23">
+        <v>1.291746949693521</v>
+      </c>
+      <c r="U23">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V23">
+        <v>0.2</v>
+      </c>
+      <c r="W23">
+        <v>0.07312</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>2.227005542772543</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1189728784446422</v>
+      </c>
+      <c r="C24">
+        <v>185.0060036218264</v>
+      </c>
+      <c r="D24">
+        <v>234.2786036218264</v>
+      </c>
+      <c r="E24">
+        <v>49.71259999999999</v>
+      </c>
+      <c r="F24">
+        <v>55.8426</v>
+      </c>
+      <c r="G24">
+        <v>6.57</v>
+      </c>
+      <c r="H24">
+        <v>247.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>12</v>
+      </c>
+      <c r="K24">
+        <v>1.15</v>
+      </c>
+      <c r="L24">
+        <v>10.85</v>
+      </c>
+      <c r="M24">
+        <v>5.104013640000001</v>
+      </c>
+      <c r="N24">
+        <v>5.745986359999999</v>
+      </c>
+      <c r="O24">
+        <v>1.149197271999999</v>
+      </c>
+      <c r="P24">
+        <v>4.596789088</v>
+      </c>
+      <c r="Q24">
+        <v>5.746789088</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1319057415956951</v>
+      </c>
+      <c r="T24">
+        <v>1.305576476482167</v>
+      </c>
+      <c r="U24">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V24">
+        <v>0.2</v>
+      </c>
+      <c r="W24">
+        <v>0.07312</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>2.125778018101064</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1191641485734191</v>
+      </c>
+      <c r="C25">
+        <v>181.9101104726439</v>
+      </c>
+      <c r="D25">
+        <v>233.7210104726439</v>
+      </c>
+      <c r="E25">
+        <v>52.25089999999999</v>
+      </c>
+      <c r="F25">
+        <v>58.3809</v>
+      </c>
+      <c r="G25">
+        <v>6.57</v>
+      </c>
+      <c r="H25">
+        <v>247.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>12</v>
+      </c>
+      <c r="K25">
+        <v>1.15</v>
+      </c>
+      <c r="L25">
+        <v>10.85</v>
+      </c>
+      <c r="M25">
+        <v>5.336014260000001</v>
+      </c>
+      <c r="N25">
+        <v>5.513985739999999</v>
+      </c>
+      <c r="O25">
+        <v>1.102797148</v>
+      </c>
+      <c r="P25">
+        <v>4.411188591999999</v>
+      </c>
+      <c r="Q25">
+        <v>5.561188591999999</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.132917595549895</v>
+      </c>
+      <c r="T25">
+        <v>1.31976521175883</v>
+      </c>
+      <c r="U25">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V25">
+        <v>0.2</v>
+      </c>
+      <c r="W25">
+        <v>0.07312</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>2.033352886879279</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.123406618702196</v>
+      </c>
+      <c r="C26">
+        <v>167.6522261114265</v>
+      </c>
+      <c r="D26">
+        <v>222.0014261114265</v>
+      </c>
+      <c r="E26">
+        <v>54.78919999999999</v>
+      </c>
+      <c r="F26">
+        <v>60.9192</v>
+      </c>
+      <c r="G26">
+        <v>6.57</v>
+      </c>
+      <c r="H26">
+        <v>247.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>12</v>
+      </c>
+      <c r="K26">
+        <v>1.15</v>
+      </c>
+      <c r="L26">
+        <v>10.85</v>
+      </c>
+      <c r="M26">
+        <v>6.853409999999999</v>
+      </c>
+      <c r="N26">
+        <v>3.99659</v>
+      </c>
+      <c r="O26">
+        <v>0.7993179999999999</v>
+      </c>
+      <c r="P26">
+        <v>3.197272</v>
+      </c>
+      <c r="Q26">
+        <v>4.347272</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1339560772397316</v>
+      </c>
+      <c r="T26">
+        <v>1.334327334805932</v>
+      </c>
+      <c r="U26">
+        <v>0.1125</v>
+      </c>
+      <c r="V26">
+        <v>0.2</v>
+      </c>
+      <c r="W26">
+        <v>0.09000000000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>1.583153495850971</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1237666888309729</v>
+      </c>
+      <c r="C27">
+        <v>164.1731329230793</v>
+      </c>
+      <c r="D27">
+        <v>221.0606329230793</v>
+      </c>
+      <c r="E27">
+        <v>57.32749999999999</v>
+      </c>
+      <c r="F27">
+        <v>63.4575</v>
+      </c>
+      <c r="G27">
+        <v>6.57</v>
+      </c>
+      <c r="H27">
+        <v>247.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>12</v>
+      </c>
+      <c r="K27">
+        <v>1.15</v>
+      </c>
+      <c r="L27">
+        <v>10.85</v>
+      </c>
+      <c r="M27">
+        <v>7.13896875</v>
+      </c>
+      <c r="N27">
+        <v>3.71103125</v>
+      </c>
+      <c r="O27">
+        <v>0.7422062499999997</v>
+      </c>
+      <c r="P27">
+        <v>2.968825</v>
+      </c>
+      <c r="Q27">
+        <v>4.118824999999999</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1350222517746305</v>
+      </c>
+      <c r="T27">
+        <v>1.34927778113429</v>
+      </c>
+      <c r="U27">
+        <v>0.1125</v>
+      </c>
+      <c r="V27">
+        <v>0.2</v>
+      </c>
+      <c r="W27">
+        <v>0.09000000000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>1.519827356016932</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1439406186961739</v>
+      </c>
+      <c r="C28">
+        <v>119.21866912406</v>
+      </c>
+      <c r="D28">
+        <v>178.64446912406</v>
+      </c>
+      <c r="E28">
+        <v>59.8658</v>
+      </c>
+      <c r="F28">
+        <v>65.9958</v>
+      </c>
+      <c r="G28">
+        <v>6.57</v>
+      </c>
+      <c r="H28">
+        <v>247.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>12</v>
+      </c>
+      <c r="K28">
+        <v>1.15</v>
+      </c>
+      <c r="L28">
+        <v>10.85</v>
+      </c>
+      <c r="M28">
+        <v>12.97477428</v>
+      </c>
+      <c r="N28">
+        <v>-2.12477428</v>
+      </c>
+      <c r="O28">
+        <v>-0.424954856</v>
+      </c>
+      <c r="P28">
+        <v>-1.699819424</v>
+      </c>
+      <c r="Q28">
+        <v>-0.5498194240000005</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1369914156402285</v>
+      </c>
+      <c r="T28">
+        <v>1.376890407135674</v>
+      </c>
+      <c r="U28">
+        <v>0.1966</v>
+      </c>
+      <c r="V28">
+        <v>0.1672476108771273</v>
+      </c>
+      <c r="W28">
+        <v>0.1637191197015568</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.8362380543856367</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1455186186961739</v>
+      </c>
+      <c r="C29">
+        <v>114.038834069335</v>
+      </c>
+      <c r="D29">
+        <v>176.002934069335</v>
+      </c>
+      <c r="E29">
+        <v>62.40409999999999</v>
+      </c>
+      <c r="F29">
+        <v>68.5341</v>
+      </c>
+      <c r="G29">
+        <v>6.57</v>
+      </c>
+      <c r="H29">
+        <v>247.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>12</v>
+      </c>
+      <c r="K29">
+        <v>1.15</v>
+      </c>
+      <c r="L29">
+        <v>10.85</v>
+      </c>
+      <c r="M29">
+        <v>13.47380406</v>
+      </c>
+      <c r="N29">
+        <v>-2.623804059999999</v>
+      </c>
+      <c r="O29">
+        <v>-0.5247608119999998</v>
+      </c>
+      <c r="P29">
+        <v>-2.099043248</v>
+      </c>
+      <c r="Q29">
+        <v>-0.9490432479999997</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1383365035257111</v>
+      </c>
+      <c r="T29">
+        <v>1.39575191956219</v>
+      </c>
+      <c r="U29">
+        <v>0.1966</v>
+      </c>
+      <c r="V29">
+        <v>0.1610532549187152</v>
+      </c>
+      <c r="W29">
+        <v>0.1649369300829806</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.8052662745935761</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1521783649742367</v>
+      </c>
+      <c r="C30">
+        <v>101.1622752193089</v>
+      </c>
+      <c r="D30">
+        <v>165.6646752193089</v>
+      </c>
+      <c r="E30">
+        <v>64.94240000000001</v>
+      </c>
+      <c r="F30">
+        <v>71.0724</v>
+      </c>
+      <c r="G30">
+        <v>6.57</v>
+      </c>
+      <c r="H30">
+        <v>247.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>12</v>
+      </c>
+      <c r="K30">
+        <v>1.15</v>
+      </c>
+      <c r="L30">
+        <v>10.85</v>
+      </c>
+      <c r="M30">
+        <v>15.19527912</v>
+      </c>
+      <c r="N30">
+        <v>-4.345279120000001</v>
+      </c>
+      <c r="O30">
+        <v>-0.8690558239999999</v>
+      </c>
+      <c r="P30">
+        <v>-3.476223296000001</v>
+      </c>
+      <c r="Q30">
+        <v>-2.326223296000001</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1400880470164333</v>
+      </c>
+      <c r="T30">
+        <v>1.420312961017103</v>
+      </c>
+      <c r="U30">
+        <v>0.2138</v>
+      </c>
+      <c r="V30">
+        <v>0.1428075116530008</v>
+      </c>
+      <c r="W30">
+        <v>0.1832677540085884</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.714037558265004</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1539283649742367</v>
+      </c>
+      <c r="C31">
+        <v>96.10580185952342</v>
+      </c>
+      <c r="D31">
+        <v>163.1465018595234</v>
+      </c>
+      <c r="E31">
+        <v>67.4807</v>
+      </c>
+      <c r="F31">
+        <v>73.61069999999999</v>
+      </c>
+      <c r="G31">
+        <v>6.57</v>
+      </c>
+      <c r="H31">
+        <v>247.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>12</v>
+      </c>
+      <c r="K31">
+        <v>1.15</v>
+      </c>
+      <c r="L31">
+        <v>10.85</v>
+      </c>
+      <c r="M31">
+        <v>15.73796766</v>
+      </c>
+      <c r="N31">
+        <v>-4.887967659999999</v>
+      </c>
+      <c r="O31">
+        <v>-0.9775935319999997</v>
+      </c>
+      <c r="P31">
+        <v>-3.910374128</v>
+      </c>
+      <c r="Q31">
+        <v>-2.760374128</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1415146392279323</v>
+      </c>
+      <c r="T31">
+        <v>1.440317368918753</v>
+      </c>
+      <c r="U31">
+        <v>0.2138</v>
+      </c>
+      <c r="V31">
+        <v>0.137883114699449</v>
+      </c>
+      <c r="W31">
+        <v>0.1843205900772578</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.6894155734972454</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1556783649742367</v>
+      </c>
+      <c r="C32">
+        <v>91.12473686775526</v>
+      </c>
+      <c r="D32">
+        <v>160.7037368677553</v>
+      </c>
+      <c r="E32">
+        <v>70.01899999999999</v>
+      </c>
+      <c r="F32">
+        <v>76.14899999999999</v>
+      </c>
+      <c r="G32">
+        <v>6.57</v>
+      </c>
+      <c r="H32">
+        <v>247.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>12</v>
+      </c>
+      <c r="K32">
+        <v>1.15</v>
+      </c>
+      <c r="L32">
+        <v>10.85</v>
+      </c>
+      <c r="M32">
+        <v>16.2806562</v>
+      </c>
+      <c r="N32">
+        <v>-5.430656199999996</v>
+      </c>
+      <c r="O32">
+        <v>-1.086131239999999</v>
+      </c>
+      <c r="P32">
+        <v>-4.344524959999998</v>
+      </c>
+      <c r="Q32">
+        <v>-3.194524959999998</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1429819912169028</v>
+      </c>
+      <c r="T32">
+        <v>1.460893331331878</v>
+      </c>
+      <c r="U32">
+        <v>0.2138</v>
+      </c>
+      <c r="V32">
+        <v>0.1332870108761341</v>
+      </c>
+      <c r="W32">
+        <v>0.1853032370746825</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.6664350543806706</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1574283649742367</v>
+      </c>
+      <c r="C33">
+        <v>86.21574298202526</v>
+      </c>
+      <c r="D33">
+        <v>158.3330429820253</v>
+      </c>
+      <c r="E33">
+        <v>72.5573</v>
+      </c>
+      <c r="F33">
+        <v>78.68729999999999</v>
+      </c>
+      <c r="G33">
+        <v>6.57</v>
+      </c>
+      <c r="H33">
+        <v>247.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>12</v>
+      </c>
+      <c r="K33">
+        <v>1.15</v>
+      </c>
+      <c r="L33">
+        <v>10.85</v>
+      </c>
+      <c r="M33">
+        <v>16.82334474</v>
+      </c>
+      <c r="N33">
+        <v>-5.973344739999996</v>
+      </c>
+      <c r="O33">
+        <v>-1.194668947999999</v>
+      </c>
+      <c r="P33">
+        <v>-4.778675791999998</v>
+      </c>
+      <c r="Q33">
+        <v>-3.628675791999998</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1444918751475825</v>
+      </c>
+      <c r="T33">
+        <v>1.482065698452629</v>
+      </c>
+      <c r="U33">
+        <v>0.2138</v>
+      </c>
+      <c r="V33">
+        <v>0.1289874298801298</v>
+      </c>
+      <c r="W33">
+        <v>0.1862224874916282</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.6449371494006491</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1591783649742367</v>
+      </c>
+      <c r="C34">
+        <v>81.37567700208488</v>
+      </c>
+      <c r="D34">
+        <v>156.0312770020849</v>
+      </c>
+      <c r="E34">
+        <v>75.0956</v>
+      </c>
+      <c r="F34">
+        <v>81.2256</v>
+      </c>
+      <c r="G34">
+        <v>6.57</v>
+      </c>
+      <c r="H34">
+        <v>247.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>12</v>
+      </c>
+      <c r="K34">
+        <v>1.15</v>
+      </c>
+      <c r="L34">
+        <v>10.85</v>
+      </c>
+      <c r="M34">
+        <v>17.36603328</v>
+      </c>
+      <c r="N34">
+        <v>-6.51603328</v>
+      </c>
+      <c r="O34">
+        <v>-1.303206656</v>
+      </c>
+      <c r="P34">
+        <v>-5.212826624000001</v>
+      </c>
+      <c r="Q34">
+        <v>-4.062826624000001</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1460461674291647</v>
+      </c>
+      <c r="T34">
+        <v>1.503860782253404</v>
+      </c>
+      <c r="U34">
+        <v>0.2138</v>
+      </c>
+      <c r="V34">
+        <v>0.1249565726963757</v>
+      </c>
+      <c r="W34">
+        <v>0.1870842847575149</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.6247828634818786</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1609283649742367</v>
+      </c>
+      <c r="C35">
+        <v>76.60157588568369</v>
+      </c>
+      <c r="D35">
+        <v>153.7954758856837</v>
+      </c>
+      <c r="E35">
+        <v>77.6339</v>
+      </c>
+      <c r="F35">
+        <v>83.76389999999999</v>
+      </c>
+      <c r="G35">
+        <v>6.57</v>
+      </c>
+      <c r="H35">
+        <v>247.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>12</v>
+      </c>
+      <c r="K35">
+        <v>1.15</v>
+      </c>
+      <c r="L35">
+        <v>10.85</v>
+      </c>
+      <c r="M35">
+        <v>17.90872182</v>
+      </c>
+      <c r="N35">
+        <v>-7.058721819999997</v>
+      </c>
+      <c r="O35">
+        <v>-1.411744363999999</v>
+      </c>
+      <c r="P35">
+        <v>-5.646977455999998</v>
+      </c>
+      <c r="Q35">
+        <v>-4.496977455999998</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1476468564952716</v>
+      </c>
+      <c r="T35">
+        <v>1.526306465570618</v>
+      </c>
+      <c r="U35">
+        <v>0.2138</v>
+      </c>
+      <c r="V35">
+        <v>0.1211700098873946</v>
+      </c>
+      <c r="W35">
+        <v>0.187893851886075</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.6058500494369732</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1626783649742367</v>
+      </c>
+      <c r="C36">
+        <v>71.89064402332482</v>
+      </c>
+      <c r="D36">
+        <v>151.6228440233248</v>
+      </c>
+      <c r="E36">
+        <v>80.1722</v>
+      </c>
+      <c r="F36">
+        <v>86.3022</v>
+      </c>
+      <c r="G36">
+        <v>6.57</v>
+      </c>
+      <c r="H36">
+        <v>247.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>12</v>
+      </c>
+      <c r="K36">
+        <v>1.15</v>
+      </c>
+      <c r="L36">
+        <v>10.85</v>
+      </c>
+      <c r="M36">
+        <v>18.45141036</v>
+      </c>
+      <c r="N36">
+        <v>-7.601410360000001</v>
+      </c>
+      <c r="O36">
+        <v>-1.520282072</v>
+      </c>
+      <c r="P36">
+        <v>-6.081128288000001</v>
+      </c>
+      <c r="Q36">
+        <v>-4.931128288000002</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1492960512906545</v>
+      </c>
+      <c r="T36">
+        <v>1.549432321109568</v>
+      </c>
+      <c r="U36">
+        <v>0.2138</v>
+      </c>
+      <c r="V36">
+        <v>0.1176061860671771</v>
+      </c>
+      <c r="W36">
+        <v>0.1886557974188375</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.5880309303358857</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1644283649742367</v>
+      </c>
+      <c r="C37">
+        <v>67.2402415765945</v>
+      </c>
+      <c r="D37">
+        <v>149.5107415765945</v>
+      </c>
+      <c r="E37">
+        <v>82.71050000000001</v>
+      </c>
+      <c r="F37">
+        <v>88.84050000000001</v>
+      </c>
+      <c r="G37">
+        <v>6.57</v>
+      </c>
+      <c r="H37">
+        <v>247.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>12</v>
+      </c>
+      <c r="K37">
+        <v>1.15</v>
+      </c>
+      <c r="L37">
+        <v>10.85</v>
+      </c>
+      <c r="M37">
+        <v>18.9940989</v>
+      </c>
+      <c r="N37">
+        <v>-8.144098900000001</v>
+      </c>
+      <c r="O37">
+        <v>-1.62881978</v>
+      </c>
+      <c r="P37">
+        <v>-6.515279120000002</v>
+      </c>
+      <c r="Q37">
+        <v>-5.365279120000002</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1509959905412799</v>
+      </c>
+      <c r="T37">
+        <v>1.57326974143433</v>
+      </c>
+      <c r="U37">
+        <v>0.2138</v>
+      </c>
+      <c r="V37">
+        <v>0.1142460093224006</v>
+      </c>
+      <c r="W37">
+        <v>0.1893742032068707</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.5712300466120033</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1661783649742367</v>
+      </c>
+      <c r="C38">
+        <v>62.6478737777814</v>
+      </c>
+      <c r="D38">
+        <v>147.4566737777814</v>
+      </c>
+      <c r="E38">
+        <v>85.24879999999999</v>
+      </c>
+      <c r="F38">
+        <v>91.37879999999998</v>
+      </c>
+      <c r="G38">
+        <v>6.57</v>
+      </c>
+      <c r="H38">
+        <v>247.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>12</v>
+      </c>
+      <c r="K38">
+        <v>1.15</v>
+      </c>
+      <c r="L38">
+        <v>10.85</v>
+      </c>
+      <c r="M38">
+        <v>19.53678743999999</v>
+      </c>
+      <c r="N38">
+        <v>-8.686787439999994</v>
+      </c>
+      <c r="O38">
+        <v>-1.737357487999998</v>
+      </c>
+      <c r="P38">
+        <v>-6.949429951999996</v>
+      </c>
+      <c r="Q38">
+        <v>-5.799429951999995</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1527490528934874</v>
+      </c>
+      <c r="T38">
+        <v>1.597852081144241</v>
+      </c>
+      <c r="U38">
+        <v>0.2138</v>
+      </c>
+      <c r="V38">
+        <v>0.1110725090634451</v>
+      </c>
+      <c r="W38">
+        <v>0.1900526975622354</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.5553625453172255</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1679283649742367</v>
+      </c>
+      <c r="C39">
+        <v>58.11118109959169</v>
+      </c>
+      <c r="D39">
+        <v>145.4582810995917</v>
+      </c>
+      <c r="E39">
+        <v>87.7871</v>
+      </c>
+      <c r="F39">
+        <v>93.91709999999999</v>
+      </c>
+      <c r="G39">
+        <v>6.57</v>
+      </c>
+      <c r="H39">
+        <v>247.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>12</v>
+      </c>
+      <c r="K39">
+        <v>1.15</v>
+      </c>
+      <c r="L39">
+        <v>10.85</v>
+      </c>
+      <c r="M39">
+        <v>20.07947598</v>
+      </c>
+      <c r="N39">
+        <v>-9.229475979999998</v>
+      </c>
+      <c r="O39">
+        <v>-1.845895195999999</v>
+      </c>
+      <c r="P39">
+        <v>-7.383580783999999</v>
+      </c>
+      <c r="Q39">
+        <v>-6.233580783999999</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1545577680187809</v>
+      </c>
+      <c r="T39">
+        <v>1.623214812590975</v>
+      </c>
+      <c r="U39">
+        <v>0.2138</v>
+      </c>
+      <c r="V39">
+        <v>0.1080705493590276</v>
+      </c>
+      <c r="W39">
+        <v>0.1906945165470399</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.5403527467951383</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1696783649742367</v>
+      </c>
+      <c r="C40">
+        <v>53.62793021351979</v>
+      </c>
+      <c r="D40">
+        <v>143.5133302135198</v>
+      </c>
+      <c r="E40">
+        <v>90.3254</v>
+      </c>
+      <c r="F40">
+        <v>96.4554</v>
+      </c>
+      <c r="G40">
+        <v>6.57</v>
+      </c>
+      <c r="H40">
+        <v>247.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>12</v>
+      </c>
+      <c r="K40">
+        <v>1.15</v>
+      </c>
+      <c r="L40">
+        <v>10.85</v>
+      </c>
+      <c r="M40">
+        <v>20.62216452</v>
+      </c>
+      <c r="N40">
+        <v>-9.772164519999999</v>
+      </c>
+      <c r="O40">
+        <v>-1.954432903999999</v>
+      </c>
+      <c r="P40">
+        <v>-7.817731616</v>
+      </c>
+      <c r="Q40">
+        <v>-6.667731615999999</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1564248287932773</v>
+      </c>
+      <c r="T40">
+        <v>1.649395696665023</v>
+      </c>
+      <c r="U40">
+        <v>0.2138</v>
+      </c>
+      <c r="V40">
+        <v>0.1052265875337901</v>
+      </c>
+      <c r="W40">
+        <v>0.1913025555852757</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.5261329376689504</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1714283649742367</v>
+      </c>
+      <c r="C41">
+        <v>49.19600566403189</v>
+      </c>
+      <c r="D41">
+        <v>141.6197056640319</v>
+      </c>
+      <c r="E41">
+        <v>92.86370000000001</v>
+      </c>
+      <c r="F41">
+        <v>98.9937</v>
+      </c>
+      <c r="G41">
+        <v>6.57</v>
+      </c>
+      <c r="H41">
+        <v>247.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>12</v>
+      </c>
+      <c r="K41">
+        <v>1.15</v>
+      </c>
+      <c r="L41">
+        <v>10.85</v>
+      </c>
+      <c r="M41">
+        <v>21.16485306</v>
+      </c>
+      <c r="N41">
+        <v>-10.31485306</v>
+      </c>
+      <c r="O41">
+        <v>-2.062970612</v>
+      </c>
+      <c r="P41">
+        <v>-8.251882448</v>
+      </c>
+      <c r="Q41">
+        <v>-7.101882448</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1583531046751344</v>
+      </c>
+      <c r="T41">
+        <v>1.676434970380843</v>
+      </c>
+      <c r="U41">
+        <v>0.2138</v>
+      </c>
+      <c r="V41">
+        <v>0.1025284699047185</v>
+      </c>
+      <c r="W41">
+        <v>0.1918794131343712</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.5126423495235927</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1834963655772223</v>
+      </c>
+      <c r="C42">
+        <v>34.84630538089154</v>
+      </c>
+      <c r="D42">
+        <v>129.8083053808915</v>
+      </c>
+      <c r="E42">
+        <v>95.402</v>
+      </c>
+      <c r="F42">
+        <v>101.532</v>
+      </c>
+      <c r="G42">
+        <v>6.57</v>
+      </c>
+      <c r="H42">
+        <v>247.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>12</v>
+      </c>
+      <c r="K42">
+        <v>1.15</v>
+      </c>
+      <c r="L42">
+        <v>10.85</v>
+      </c>
+      <c r="M42">
+        <v>24.2458416</v>
+      </c>
+      <c r="N42">
+        <v>-13.3958416</v>
+      </c>
+      <c r="O42">
+        <v>-2.67916832</v>
+      </c>
+      <c r="P42">
+        <v>-10.71667328</v>
+      </c>
+      <c r="Q42">
+        <v>-9.566673280000002</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.160875657424696</v>
+      </c>
+      <c r="T42">
+        <v>1.711807499228895</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.08949988355941413</v>
+      </c>
+      <c r="W42">
+        <v>0.2174274278060119</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.4474994177970708</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1854963655772223</v>
+      </c>
+      <c r="C43">
+        <v>30.53825048791759</v>
+      </c>
+      <c r="D43">
+        <v>128.0385504879176</v>
+      </c>
+      <c r="E43">
+        <v>97.94030000000001</v>
+      </c>
+      <c r="F43">
+        <v>104.0703</v>
+      </c>
+      <c r="G43">
+        <v>6.57</v>
+      </c>
+      <c r="H43">
+        <v>247.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>12</v>
+      </c>
+      <c r="K43">
+        <v>1.15</v>
+      </c>
+      <c r="L43">
+        <v>10.85</v>
+      </c>
+      <c r="M43">
+        <v>24.85198764</v>
+      </c>
+      <c r="N43">
+        <v>-14.00198764</v>
+      </c>
+      <c r="O43">
+        <v>-2.800397528</v>
+      </c>
+      <c r="P43">
+        <v>-11.201590112</v>
+      </c>
+      <c r="Q43">
+        <v>-10.051590112</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1629447363640976</v>
+      </c>
+      <c r="T43">
+        <v>1.740821185656504</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.08731695957016014</v>
+      </c>
+      <c r="W43">
+        <v>0.2179487100546458</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.4365847978508007</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1874963655772223</v>
+      </c>
+      <c r="C44">
+        <v>26.27780280810194</v>
+      </c>
+      <c r="D44">
+        <v>126.3164028081019</v>
+      </c>
+      <c r="E44">
+        <v>100.4786</v>
+      </c>
+      <c r="F44">
+        <v>106.6086</v>
+      </c>
+      <c r="G44">
+        <v>6.57</v>
+      </c>
+      <c r="H44">
+        <v>247.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>12</v>
+      </c>
+      <c r="K44">
+        <v>1.15</v>
+      </c>
+      <c r="L44">
+        <v>10.85</v>
+      </c>
+      <c r="M44">
+        <v>25.45813368</v>
+      </c>
+      <c r="N44">
+        <v>-14.60813368</v>
+      </c>
+      <c r="O44">
+        <v>-2.921626735999999</v>
+      </c>
+      <c r="P44">
+        <v>-11.686506944</v>
+      </c>
+      <c r="Q44">
+        <v>-10.536506944</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1650851628531337</v>
+      </c>
+      <c r="T44">
+        <v>1.770835344029891</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.08523798434229918</v>
+      </c>
+      <c r="W44">
+        <v>0.2184451693390589</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.4261899217114961</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1894963655772223</v>
+      </c>
+      <c r="C45">
+        <v>22.06306685260611</v>
+      </c>
+      <c r="D45">
+        <v>124.6399668526061</v>
+      </c>
+      <c r="E45">
+        <v>103.0169</v>
+      </c>
+      <c r="F45">
+        <v>109.1469</v>
+      </c>
+      <c r="G45">
+        <v>6.57</v>
+      </c>
+      <c r="H45">
+        <v>247.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>12</v>
+      </c>
+      <c r="K45">
+        <v>1.15</v>
+      </c>
+      <c r="L45">
+        <v>10.85</v>
+      </c>
+      <c r="M45">
+        <v>26.06427972</v>
+      </c>
+      <c r="N45">
+        <v>-15.21427972</v>
+      </c>
+      <c r="O45">
+        <v>-3.042855943999999</v>
+      </c>
+      <c r="P45">
+        <v>-12.171423776</v>
+      </c>
+      <c r="Q45">
+        <v>-11.021423776</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1673006920259957</v>
+      </c>
+      <c r="T45">
+        <v>1.801902630767258</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.08325570563666433</v>
+      </c>
+      <c r="W45">
+        <v>0.2189185374939646</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.4162785281833217</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1914963655772223</v>
+      </c>
+      <c r="C46">
+        <v>17.89224644019886</v>
+      </c>
+      <c r="D46">
+        <v>123.0074464401988</v>
+      </c>
+      <c r="E46">
+        <v>105.5552</v>
+      </c>
+      <c r="F46">
+        <v>111.6852</v>
+      </c>
+      <c r="G46">
+        <v>6.57</v>
+      </c>
+      <c r="H46">
+        <v>247.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>12</v>
+      </c>
+      <c r="K46">
+        <v>1.15</v>
+      </c>
+      <c r="L46">
+        <v>10.85</v>
+      </c>
+      <c r="M46">
+        <v>26.67042576</v>
+      </c>
+      <c r="N46">
+        <v>-15.82042576</v>
+      </c>
+      <c r="O46">
+        <v>-3.164085151999999</v>
+      </c>
+      <c r="P46">
+        <v>-12.656340608</v>
+      </c>
+      <c r="Q46">
+        <v>-11.506340608</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1695953472407457</v>
+      </c>
+      <c r="T46">
+        <v>1.834079463459531</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.08136353050855831</v>
+      </c>
+      <c r="W46">
+        <v>0.2193703889145563</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.4068176525427917</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1934963655772223</v>
+      </c>
+      <c r="C47">
+        <v>13.76363827773858</v>
+      </c>
+      <c r="D47">
+        <v>121.4171382777386</v>
+      </c>
+      <c r="E47">
+        <v>108.0935</v>
+      </c>
+      <c r="F47">
+        <v>114.2235</v>
+      </c>
+      <c r="G47">
+        <v>6.57</v>
+      </c>
+      <c r="H47">
+        <v>247.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>12</v>
+      </c>
+      <c r="K47">
+        <v>1.15</v>
+      </c>
+      <c r="L47">
+        <v>10.85</v>
+      </c>
+      <c r="M47">
+        <v>27.2765718</v>
+      </c>
+      <c r="N47">
+        <v>-16.4265718</v>
+      </c>
+      <c r="O47">
+        <v>-3.28531436</v>
+      </c>
+      <c r="P47">
+        <v>-13.14125744</v>
+      </c>
+      <c r="Q47">
+        <v>-11.99125744</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1719734444633046</v>
+      </c>
+      <c r="T47">
+        <v>1.867426362795158</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.07955545205281256</v>
+      </c>
+      <c r="W47">
+        <v>0.2198021580497884</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.3977772602640628</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1954963655772223</v>
+      </c>
+      <c r="C48">
+        <v>9.675626032269776</v>
+      </c>
+      <c r="D48">
+        <v>119.8674260322698</v>
+      </c>
+      <c r="E48">
+        <v>110.6318</v>
+      </c>
+      <c r="F48">
+        <v>116.7618</v>
+      </c>
+      <c r="G48">
+        <v>6.57</v>
+      </c>
+      <c r="H48">
+        <v>247.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>12</v>
+      </c>
+      <c r="K48">
+        <v>1.15</v>
+      </c>
+      <c r="L48">
+        <v>10.85</v>
+      </c>
+      <c r="M48">
+        <v>27.88271784</v>
+      </c>
+      <c r="N48">
+        <v>-17.03271784</v>
+      </c>
+      <c r="O48">
+        <v>-3.406543568</v>
+      </c>
+      <c r="P48">
+        <v>-13.626174272</v>
+      </c>
+      <c r="Q48">
+        <v>-12.476174272</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1744396193607733</v>
+      </c>
+      <c r="T48">
+        <v>1.90200833247655</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.07782598570383838</v>
+      </c>
+      <c r="W48">
+        <v>0.2202151546139234</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.3891299285191919</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1974963655772223</v>
+      </c>
+      <c r="C49">
+        <v>5.626674851364911</v>
+      </c>
+      <c r="D49">
+        <v>118.3567748513649</v>
+      </c>
+      <c r="E49">
+        <v>113.1701</v>
+      </c>
+      <c r="F49">
+        <v>119.3001</v>
+      </c>
+      <c r="G49">
+        <v>6.57</v>
+      </c>
+      <c r="H49">
+        <v>247.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>12</v>
+      </c>
+      <c r="K49">
+        <v>1.15</v>
+      </c>
+      <c r="L49">
+        <v>10.85</v>
+      </c>
+      <c r="M49">
+        <v>28.48886388</v>
+      </c>
+      <c r="N49">
+        <v>-17.63886388</v>
+      </c>
+      <c r="O49">
+        <v>-3.527772775999999</v>
+      </c>
+      <c r="P49">
+        <v>-14.111091104</v>
+      </c>
+      <c r="Q49">
+        <v>-12.961091104</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1769988574619199</v>
+      </c>
+      <c r="T49">
+        <v>1.937895282145919</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.0761701136675865</v>
+      </c>
+      <c r="W49">
+        <v>0.2206105768561804</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.3808505683379325</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1994963655772223</v>
+      </c>
+      <c r="C50">
+        <v>1.615326292659475</v>
+      </c>
+      <c r="D50">
+        <v>116.8837262926595</v>
+      </c>
+      <c r="E50">
+        <v>115.7084</v>
+      </c>
+      <c r="F50">
+        <v>121.8384</v>
+      </c>
+      <c r="G50">
+        <v>6.57</v>
+      </c>
+      <c r="H50">
+        <v>247.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>12</v>
+      </c>
+      <c r="K50">
+        <v>1.15</v>
+      </c>
+      <c r="L50">
+        <v>10.85</v>
+      </c>
+      <c r="M50">
+        <v>29.09500992</v>
+      </c>
+      <c r="N50">
+        <v>-18.24500992</v>
+      </c>
+      <c r="O50">
+        <v>-3.649001983999999</v>
+      </c>
+      <c r="P50">
+        <v>-14.596007936</v>
+      </c>
+      <c r="Q50">
+        <v>-13.446007936</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1796565277977261</v>
+      </c>
+      <c r="T50">
+        <v>1.975162499110264</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.07458323629951179</v>
+      </c>
+      <c r="W50">
+        <v>0.2209895231716766</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.372916181497559</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2014963655772223</v>
+      </c>
+      <c r="C51">
+        <v>-2.35980637263053</v>
+      </c>
+      <c r="D51">
+        <v>115.4468936273694</v>
+      </c>
+      <c r="E51">
+        <v>118.2467</v>
+      </c>
+      <c r="F51">
+        <v>124.3767</v>
+      </c>
+      <c r="G51">
+        <v>6.57</v>
+      </c>
+      <c r="H51">
+        <v>247.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>12</v>
+      </c>
+      <c r="K51">
+        <v>1.15</v>
+      </c>
+      <c r="L51">
+        <v>10.85</v>
+      </c>
+      <c r="M51">
+        <v>29.70115596</v>
+      </c>
+      <c r="N51">
+        <v>-18.85115596</v>
+      </c>
+      <c r="O51">
+        <v>-3.770231191999999</v>
+      </c>
+      <c r="P51">
+        <v>-15.080924768</v>
+      </c>
+      <c r="Q51">
+        <v>-13.930924768</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1824184204996423</v>
+      </c>
+      <c r="T51">
+        <v>2.013891175563406</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.07306112943625645</v>
+      </c>
+      <c r="W51">
+        <v>0.221353002290622</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.3653056471812822</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2034963655772223</v>
+      </c>
+      <c r="C52">
+        <v>-6.300042513998989</v>
+      </c>
+      <c r="D52">
+        <v>114.044957486001</v>
+      </c>
+      <c r="E52">
+        <v>120.785</v>
+      </c>
+      <c r="F52">
+        <v>126.915</v>
+      </c>
+      <c r="G52">
+        <v>6.57</v>
+      </c>
+      <c r="H52">
+        <v>247.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>12</v>
+      </c>
+      <c r="K52">
+        <v>1.15</v>
+      </c>
+      <c r="L52">
+        <v>10.85</v>
+      </c>
+      <c r="M52">
+        <v>30.307302</v>
+      </c>
+      <c r="N52">
+        <v>-19.457302</v>
+      </c>
+      <c r="O52">
+        <v>-3.891460399999999</v>
+      </c>
+      <c r="P52">
+        <v>-15.5658416</v>
+      </c>
+      <c r="Q52">
+        <v>-14.4158416</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1852907889096351</v>
+      </c>
+      <c r="T52">
+        <v>2.054168999074674</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.07159990684753131</v>
+      </c>
+      <c r="W52">
+        <v>0.2217019422448095</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.3579995342376567</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2054963655772223</v>
+      </c>
+      <c r="C53">
+        <v>-10.20663818248696</v>
+      </c>
+      <c r="D53">
+        <v>112.676661817513</v>
+      </c>
+      <c r="E53">
+        <v>123.3233</v>
+      </c>
+      <c r="F53">
+        <v>129.4533</v>
+      </c>
+      <c r="G53">
+        <v>6.57</v>
+      </c>
+      <c r="H53">
+        <v>247.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>12</v>
+      </c>
+      <c r="K53">
+        <v>1.15</v>
+      </c>
+      <c r="L53">
+        <v>10.85</v>
+      </c>
+      <c r="M53">
+        <v>30.91344804</v>
+      </c>
+      <c r="N53">
+        <v>-20.06344804</v>
+      </c>
+      <c r="O53">
+        <v>-4.012689607999999</v>
+      </c>
+      <c r="P53">
+        <v>-16.050758432</v>
+      </c>
+      <c r="Q53">
+        <v>-14.900758432</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1882803968465665</v>
+      </c>
+      <c r="T53">
+        <v>2.096090815382321</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.07019598710542285</v>
+      </c>
+      <c r="W53">
+        <v>0.222037198279225</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.3509799355271144</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2074963655772223</v>
+      </c>
+      <c r="C54">
+        <v>-14.0807898640804</v>
+      </c>
+      <c r="D54">
+        <v>111.3408101359196</v>
+      </c>
+      <c r="E54">
+        <v>125.8616</v>
+      </c>
+      <c r="F54">
+        <v>131.9916</v>
+      </c>
+      <c r="G54">
+        <v>6.57</v>
+      </c>
+      <c r="H54">
+        <v>247.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>12</v>
+      </c>
+      <c r="K54">
+        <v>1.15</v>
+      </c>
+      <c r="L54">
+        <v>10.85</v>
+      </c>
+      <c r="M54">
+        <v>31.51959408</v>
+      </c>
+      <c r="N54">
+        <v>-20.66959408</v>
+      </c>
+      <c r="O54">
+        <v>-4.133918816</v>
+      </c>
+      <c r="P54">
+        <v>-16.53567526400001</v>
+      </c>
+      <c r="Q54">
+        <v>-15.385675264</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.19139457178087</v>
+      </c>
+      <c r="T54">
+        <v>2.13975937403612</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.0688460642764724</v>
+      </c>
+      <c r="W54">
+        <v>0.2223595598507784</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.3442303213823622</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2094963655772223</v>
+      </c>
+      <c r="C55">
+        <v>-17.92363796924258</v>
+      </c>
+      <c r="D55">
+        <v>110.0362620307574</v>
+      </c>
+      <c r="E55">
+        <v>128.3999</v>
+      </c>
+      <c r="F55">
+        <v>134.5299</v>
+      </c>
+      <c r="G55">
+        <v>6.57</v>
+      </c>
+      <c r="H55">
+        <v>247.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>12</v>
+      </c>
+      <c r="K55">
+        <v>1.15</v>
+      </c>
+      <c r="L55">
+        <v>10.85</v>
+      </c>
+      <c r="M55">
+        <v>32.12574012</v>
+      </c>
+      <c r="N55">
+        <v>-21.27574012</v>
+      </c>
+      <c r="O55">
+        <v>-4.255148023999999</v>
+      </c>
+      <c r="P55">
+        <v>-17.020592096</v>
+      </c>
+      <c r="Q55">
+        <v>-15.870592096</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1946412647974842</v>
+      </c>
+      <c r="T55">
+        <v>2.185286169228377</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.06754708193163331</v>
+      </c>
+      <c r="W55">
+        <v>0.222669756834726</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.3377354096581666</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2114963655772223</v>
+      </c>
+      <c r="C56">
+        <v>-21.73627007997311</v>
+      </c>
+      <c r="D56">
+        <v>108.7619299200269</v>
+      </c>
+      <c r="E56">
+        <v>130.9382</v>
+      </c>
+      <c r="F56">
+        <v>137.0682</v>
+      </c>
+      <c r="G56">
+        <v>6.57</v>
+      </c>
+      <c r="H56">
+        <v>247.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>12</v>
+      </c>
+      <c r="K56">
+        <v>1.15</v>
+      </c>
+      <c r="L56">
+        <v>10.85</v>
+      </c>
+      <c r="M56">
+        <v>32.73188616</v>
+      </c>
+      <c r="N56">
+        <v>-21.88188616</v>
+      </c>
+      <c r="O56">
+        <v>-4.376377231999999</v>
+      </c>
+      <c r="P56">
+        <v>-17.505508928</v>
+      </c>
+      <c r="Q56">
+        <v>-16.355508928</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1980291183800382</v>
+      </c>
+      <c r="T56">
+        <v>2.232792390298559</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.06629621004401047</v>
+      </c>
+      <c r="W56">
+        <v>0.2229684650414903</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.3314810502200525</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2134963655772223</v>
+      </c>
+      <c r="C57">
+        <v>-25.51972397382389</v>
+      </c>
+      <c r="D57">
+        <v>107.5167760261761</v>
+      </c>
+      <c r="E57">
+        <v>133.4765</v>
+      </c>
+      <c r="F57">
+        <v>139.6065</v>
+      </c>
+      <c r="G57">
+        <v>6.57</v>
+      </c>
+      <c r="H57">
+        <v>247.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>12</v>
+      </c>
+      <c r="K57">
+        <v>1.15</v>
+      </c>
+      <c r="L57">
+        <v>10.85</v>
+      </c>
+      <c r="M57">
+        <v>33.33803220000001</v>
+      </c>
+      <c r="N57">
+        <v>-22.48803220000001</v>
+      </c>
+      <c r="O57">
+        <v>-4.49760644</v>
+      </c>
+      <c r="P57">
+        <v>-17.99042576000001</v>
+      </c>
+      <c r="Q57">
+        <v>-16.84042576000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.201567543232928</v>
+      </c>
+      <c r="T57">
+        <v>2.282409998971861</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.06509082440684663</v>
+      </c>
+      <c r="W57">
+        <v>0.223256311131645</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.3254541220342333</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2154963655772223</v>
+      </c>
+      <c r="C58">
+        <v>-29.27499044254492</v>
+      </c>
+      <c r="D58">
+        <v>106.2998095574551</v>
+      </c>
+      <c r="E58">
+        <v>136.0148</v>
+      </c>
+      <c r="F58">
+        <v>142.1448</v>
+      </c>
+      <c r="G58">
+        <v>6.57</v>
+      </c>
+      <c r="H58">
+        <v>247.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>12</v>
+      </c>
+      <c r="K58">
+        <v>1.15</v>
+      </c>
+      <c r="L58">
+        <v>10.85</v>
+      </c>
+      <c r="M58">
+        <v>33.94417824</v>
+      </c>
+      <c r="N58">
+        <v>-23.09417824</v>
+      </c>
+      <c r="O58">
+        <v>-4.618835647999998</v>
+      </c>
+      <c r="P58">
+        <v>-18.475342592</v>
+      </c>
+      <c r="Q58">
+        <v>-17.325342592</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2052668055791309</v>
+      </c>
+      <c r="T58">
+        <v>2.334282953493949</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.06392848825672438</v>
+      </c>
+      <c r="W58">
+        <v>0.2235338770042942</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.3196424412836221</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2174963655772224</v>
+      </c>
+      <c r="C59">
+        <v>-33.00301592144973</v>
+      </c>
+      <c r="D59">
+        <v>105.1100840785503</v>
+      </c>
+      <c r="E59">
+        <v>138.5531</v>
+      </c>
+      <c r="F59">
+        <v>144.6831</v>
+      </c>
+      <c r="G59">
+        <v>6.57</v>
+      </c>
+      <c r="H59">
+        <v>247.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>12</v>
+      </c>
+      <c r="K59">
+        <v>1.15</v>
+      </c>
+      <c r="L59">
+        <v>10.85</v>
+      </c>
+      <c r="M59">
+        <v>34.55032428</v>
+      </c>
+      <c r="N59">
+        <v>-23.70032428</v>
+      </c>
+      <c r="O59">
+        <v>-4.740064855999998</v>
+      </c>
+      <c r="P59">
+        <v>-18.960259424</v>
+      </c>
+      <c r="Q59">
+        <v>-17.810259424</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2091381266391106</v>
+      </c>
+      <c r="T59">
+        <v>2.388568603575203</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.06280693583116782</v>
+      </c>
+      <c r="W59">
+        <v>0.2238017037235171</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.3140346791558393</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2194963655772223</v>
+      </c>
+      <c r="C60">
+        <v>-36.70470494416503</v>
+      </c>
+      <c r="D60">
+        <v>103.946695055835</v>
+      </c>
+      <c r="E60">
+        <v>141.0914</v>
+      </c>
+      <c r="F60">
+        <v>147.2214</v>
+      </c>
+      <c r="G60">
+        <v>6.57</v>
+      </c>
+      <c r="H60">
+        <v>247.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>12</v>
+      </c>
+      <c r="K60">
+        <v>1.15</v>
+      </c>
+      <c r="L60">
+        <v>10.85</v>
+      </c>
+      <c r="M60">
+        <v>35.15647032</v>
+      </c>
+      <c r="N60">
+        <v>-24.30647032</v>
+      </c>
+      <c r="O60">
+        <v>-4.861294063999998</v>
+      </c>
+      <c r="P60">
+        <v>-19.445176256</v>
+      </c>
+      <c r="Q60">
+        <v>-18.295176256</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2131937963209942</v>
+      </c>
+      <c r="T60">
+        <v>2.445439284612707</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.06172405762718217</v>
+      </c>
+      <c r="W60">
+        <v>0.2240602950386289</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.308620288135911</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2214963655772223</v>
+      </c>
+      <c r="C61">
+        <v>-40.38092243614599</v>
+      </c>
+      <c r="D61">
+        <v>102.808777563854</v>
+      </c>
+      <c r="E61">
+        <v>143.6297</v>
+      </c>
+      <c r="F61">
+        <v>149.7597</v>
+      </c>
+      <c r="G61">
+        <v>6.57</v>
+      </c>
+      <c r="H61">
+        <v>247.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>12</v>
+      </c>
+      <c r="K61">
+        <v>1.15</v>
+      </c>
+      <c r="L61">
+        <v>10.85</v>
+      </c>
+      <c r="M61">
+        <v>35.76261636</v>
+      </c>
+      <c r="N61">
+        <v>-24.91261635999999</v>
+      </c>
+      <c r="O61">
+        <v>-4.982523271999998</v>
+      </c>
+      <c r="P61">
+        <v>-19.930093088</v>
+      </c>
+      <c r="Q61">
+        <v>-18.780093088</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2174473035483355</v>
+      </c>
+      <c r="T61">
+        <v>2.505084145213017</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.06067788715892485</v>
+      </c>
+      <c r="W61">
+        <v>0.2243101205464487</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.3033894357946244</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2234963655772223</v>
+      </c>
+      <c r="C62">
+        <v>-44.03249585917791</v>
+      </c>
+      <c r="D62">
+        <v>101.6955041408221</v>
+      </c>
+      <c r="E62">
+        <v>146.168</v>
+      </c>
+      <c r="F62">
+        <v>152.298</v>
+      </c>
+      <c r="G62">
+        <v>6.57</v>
+      </c>
+      <c r="H62">
+        <v>247.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>12</v>
+      </c>
+      <c r="K62">
+        <v>1.15</v>
+      </c>
+      <c r="L62">
+        <v>10.85</v>
+      </c>
+      <c r="M62">
+        <v>36.36876239999999</v>
+      </c>
+      <c r="N62">
+        <v>-25.51876239999999</v>
+      </c>
+      <c r="O62">
+        <v>-5.103752479999997</v>
+      </c>
+      <c r="P62">
+        <v>-20.41500992</v>
+      </c>
+      <c r="Q62">
+        <v>-19.26500992</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2219134861370439</v>
+      </c>
+      <c r="T62">
+        <v>2.567711248843343</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.05966658903960944</v>
+      </c>
+      <c r="W62">
+        <v>0.2245516185373413</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2983329451980473</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2254963655772223</v>
+      </c>
+      <c r="C63">
+        <v>-47.66021721803946</v>
+      </c>
+      <c r="D63">
+        <v>100.6060827819605</v>
+      </c>
+      <c r="E63">
+        <v>148.7063</v>
+      </c>
+      <c r="F63">
+        <v>154.8363</v>
+      </c>
+      <c r="G63">
+        <v>6.57</v>
+      </c>
+      <c r="H63">
+        <v>247.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>12</v>
+      </c>
+      <c r="K63">
+        <v>1.15</v>
+      </c>
+      <c r="L63">
+        <v>10.85</v>
+      </c>
+      <c r="M63">
+        <v>36.97490844</v>
+      </c>
+      <c r="N63">
+        <v>-26.12490844</v>
+      </c>
+      <c r="O63">
+        <v>-5.224981687999999</v>
+      </c>
+      <c r="P63">
+        <v>-20.899926752</v>
+      </c>
+      <c r="Q63">
+        <v>-19.749926752</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2266087037303015</v>
+      </c>
+      <c r="T63">
+        <v>2.633549998813685</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.0586884482356814</v>
+      </c>
+      <c r="W63">
+        <v>0.2247851985613193</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.2934422411784071</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2274963655772224</v>
+      </c>
+      <c r="C64">
+        <v>-51.26484493955337</v>
+      </c>
+      <c r="D64">
+        <v>99.53975506044661</v>
+      </c>
+      <c r="E64">
+        <v>151.2446</v>
+      </c>
+      <c r="F64">
+        <v>157.3746</v>
+      </c>
+      <c r="G64">
+        <v>6.57</v>
+      </c>
+      <c r="H64">
+        <v>247.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>12</v>
+      </c>
+      <c r="K64">
+        <v>1.15</v>
+      </c>
+      <c r="L64">
+        <v>10.85</v>
+      </c>
+      <c r="M64">
+        <v>37.58105448</v>
+      </c>
+      <c r="N64">
+        <v>-26.73105448</v>
+      </c>
+      <c r="O64">
+        <v>-5.346210895999998</v>
+      </c>
+      <c r="P64">
+        <v>-21.384843584</v>
+      </c>
+      <c r="Q64">
+        <v>-20.234843584</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2315510380389936</v>
+      </c>
+      <c r="T64">
+        <v>2.702853946150887</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.05774186036091235</v>
+      </c>
+      <c r="W64">
+        <v>0.2250112437458142</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.2887093018045619</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2294963655772224</v>
+      </c>
+      <c r="C65">
+        <v>-54.84710563339405</v>
+      </c>
+      <c r="D65">
+        <v>98.49579436660592</v>
+      </c>
+      <c r="E65">
+        <v>153.7829</v>
+      </c>
+      <c r="F65">
+        <v>159.9129</v>
+      </c>
+      <c r="G65">
+        <v>6.57</v>
+      </c>
+      <c r="H65">
+        <v>247.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>12</v>
+      </c>
+      <c r="K65">
+        <v>1.15</v>
+      </c>
+      <c r="L65">
+        <v>10.85</v>
+      </c>
+      <c r="M65">
+        <v>38.18720052</v>
+      </c>
+      <c r="N65">
+        <v>-27.33720052</v>
+      </c>
+      <c r="O65">
+        <v>-5.467440103999998</v>
+      </c>
+      <c r="P65">
+        <v>-21.869760416</v>
+      </c>
+      <c r="Q65">
+        <v>-20.719760416</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.236760525553561</v>
+      </c>
+      <c r="T65">
+        <v>2.775904052803614</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.05682532289486612</v>
+      </c>
+      <c r="W65">
+        <v>0.225230112892706</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2841266144743307</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2314963655772223</v>
+      </c>
+      <c r="C66">
+        <v>-58.40769574324187</v>
+      </c>
+      <c r="D66">
+        <v>97.47350425675813</v>
+      </c>
+      <c r="E66">
+        <v>156.3212</v>
+      </c>
+      <c r="F66">
+        <v>162.4512</v>
+      </c>
+      <c r="G66">
+        <v>6.57</v>
+      </c>
+      <c r="H66">
+        <v>247.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>12</v>
+      </c>
+      <c r="K66">
+        <v>1.15</v>
+      </c>
+      <c r="L66">
+        <v>10.85</v>
+      </c>
+      <c r="M66">
+        <v>38.79334656</v>
+      </c>
+      <c r="N66">
+        <v>-27.94334656</v>
+      </c>
+      <c r="O66">
+        <v>-5.588669312</v>
+      </c>
+      <c r="P66">
+        <v>-22.354677248</v>
+      </c>
+      <c r="Q66">
+        <v>-21.204677248</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2422594290411599</v>
+      </c>
+      <c r="T66">
+        <v>2.853012498714826</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.05593742722463384</v>
+      </c>
+      <c r="W66">
+        <v>0.2254421423787575</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2796871361231693</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2334963655772223</v>
+      </c>
+      <c r="C67">
+        <v>-61.94728309616985</v>
+      </c>
+      <c r="D67">
+        <v>96.47221690383014</v>
+      </c>
+      <c r="E67">
+        <v>158.8595</v>
+      </c>
+      <c r="F67">
+        <v>164.9895</v>
+      </c>
+      <c r="G67">
+        <v>6.57</v>
+      </c>
+      <c r="H67">
+        <v>247.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>12</v>
+      </c>
+      <c r="K67">
+        <v>1.15</v>
+      </c>
+      <c r="L67">
+        <v>10.85</v>
+      </c>
+      <c r="M67">
+        <v>39.3994926</v>
+      </c>
+      <c r="N67">
+        <v>-28.5494926</v>
+      </c>
+      <c r="O67">
+        <v>-5.709898519999999</v>
+      </c>
+      <c r="P67">
+        <v>-22.83959408</v>
+      </c>
+      <c r="Q67">
+        <v>-21.68959408</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2480725555851931</v>
+      </c>
+      <c r="T67">
+        <v>2.934527141535249</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.05507685142117793</v>
+      </c>
+      <c r="W67">
+        <v>0.2256476478806227</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2753842571058898</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2354963655772224</v>
+      </c>
+      <c r="C68">
+        <v>-65.4665083575058</v>
+      </c>
+      <c r="D68">
+        <v>95.49129164249419</v>
+      </c>
+      <c r="E68">
+        <v>161.3978</v>
+      </c>
+      <c r="F68">
+        <v>167.5278</v>
+      </c>
+      <c r="G68">
+        <v>6.57</v>
+      </c>
+      <c r="H68">
+        <v>247.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>12</v>
+      </c>
+      <c r="K68">
+        <v>1.15</v>
+      </c>
+      <c r="L68">
+        <v>10.85</v>
+      </c>
+      <c r="M68">
+        <v>40.00563864</v>
+      </c>
+      <c r="N68">
+        <v>-29.15563864</v>
+      </c>
+      <c r="O68">
+        <v>-5.831127727999998</v>
+      </c>
+      <c r="P68">
+        <v>-23.324510912</v>
+      </c>
+      <c r="Q68">
+        <v>-22.174510912</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2542276307494634</v>
+      </c>
+      <c r="T68">
+        <v>3.020836763345109</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.0542423536723722</v>
+      </c>
+      <c r="W68">
+        <v>0.2258469259430375</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2712117683618611</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2374963655772223</v>
+      </c>
+      <c r="C69">
+        <v>-68.96598639782962</v>
+      </c>
+      <c r="D69">
+        <v>94.53011360217039</v>
+      </c>
+      <c r="E69">
+        <v>163.9361</v>
+      </c>
+      <c r="F69">
+        <v>170.0661</v>
+      </c>
+      <c r="G69">
+        <v>6.57</v>
+      </c>
+      <c r="H69">
+        <v>247.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>12</v>
+      </c>
+      <c r="K69">
+        <v>1.15</v>
+      </c>
+      <c r="L69">
+        <v>10.85</v>
+      </c>
+      <c r="M69">
+        <v>40.61178468000001</v>
+      </c>
+      <c r="N69">
+        <v>-29.76178468000001</v>
+      </c>
+      <c r="O69">
+        <v>-5.952356936</v>
+      </c>
+      <c r="P69">
+        <v>-23.809427744</v>
+      </c>
+      <c r="Q69">
+        <v>-22.65942774400001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2607557407721744</v>
+      </c>
+      <c r="T69">
+        <v>3.112377271325264</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.05343276630412783</v>
+      </c>
+      <c r="W69">
+        <v>0.2260402554065743</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.2671638315206393</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2394963655772224</v>
+      </c>
+      <c r="C70">
+        <v>-72.44630757823612</v>
+      </c>
+      <c r="D70">
+        <v>93.58809242176389</v>
+      </c>
+      <c r="E70">
+        <v>166.4744</v>
+      </c>
+      <c r="F70">
+        <v>172.6044</v>
+      </c>
+      <c r="G70">
+        <v>6.57</v>
+      </c>
+      <c r="H70">
+        <v>247.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>12</v>
+      </c>
+      <c r="K70">
+        <v>1.15</v>
+      </c>
+      <c r="L70">
+        <v>10.85</v>
+      </c>
+      <c r="M70">
+        <v>41.21793072</v>
+      </c>
+      <c r="N70">
+        <v>-30.36793072</v>
+      </c>
+      <c r="O70">
+        <v>-6.073586143999998</v>
+      </c>
+      <c r="P70">
+        <v>-24.294344576</v>
+      </c>
+      <c r="Q70">
+        <v>-23.144344576</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2676918576713049</v>
+      </c>
+      <c r="T70">
+        <v>3.209639061054179</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.05264699032906715</v>
+      </c>
+      <c r="W70">
+        <v>0.2262278987094188</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.2632349516453358</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2414963655772223</v>
+      </c>
+      <c r="C71">
+        <v>-75.90803895950683</v>
+      </c>
+      <c r="D71">
+        <v>92.66466104049317</v>
+      </c>
+      <c r="E71">
+        <v>169.0127</v>
+      </c>
+      <c r="F71">
+        <v>175.1427</v>
+      </c>
+      <c r="G71">
+        <v>6.57</v>
+      </c>
+      <c r="H71">
+        <v>247.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>12</v>
+      </c>
+      <c r="K71">
+        <v>1.15</v>
+      </c>
+      <c r="L71">
+        <v>10.85</v>
+      </c>
+      <c r="M71">
+        <v>41.82407676</v>
+      </c>
+      <c r="N71">
+        <v>-30.97407676</v>
+      </c>
+      <c r="O71">
+        <v>-6.194815351999997</v>
+      </c>
+      <c r="P71">
+        <v>-24.779261408</v>
+      </c>
+      <c r="Q71">
+        <v>-23.629261408</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2750754659832825</v>
+      </c>
+      <c r="T71">
+        <v>3.313175804959153</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.05188399046922559</v>
+      </c>
+      <c r="W71">
+        <v>0.2264101030759489</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.259419952346128</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2434963655772223</v>
+      </c>
+      <c r="C72">
+        <v>-79.35172544039705</v>
+      </c>
+      <c r="D72">
+        <v>91.75927455960297</v>
+      </c>
+      <c r="E72">
+        <v>171.551</v>
+      </c>
+      <c r="F72">
+        <v>177.681</v>
+      </c>
+      <c r="G72">
+        <v>6.57</v>
+      </c>
+      <c r="H72">
+        <v>247.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>12</v>
+      </c>
+      <c r="K72">
+        <v>1.15</v>
+      </c>
+      <c r="L72">
+        <v>10.85</v>
+      </c>
+      <c r="M72">
+        <v>42.4302228</v>
+      </c>
+      <c r="N72">
+        <v>-31.5802228</v>
+      </c>
+      <c r="O72">
+        <v>-6.316044559999999</v>
+      </c>
+      <c r="P72">
+        <v>-25.26417824</v>
+      </c>
+      <c r="Q72">
+        <v>-24.11417824</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2829513148493919</v>
+      </c>
+      <c r="T72">
+        <v>3.423614998457791</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.0511427906053795</v>
+      </c>
+      <c r="W72">
+        <v>0.2265871016034354</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2557139530268976</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2454963655772223</v>
+      </c>
+      <c r="C73">
+        <v>-82.77789082983776</v>
+      </c>
+      <c r="D73">
+        <v>90.87140917016222</v>
+      </c>
+      <c r="E73">
+        <v>174.0893</v>
+      </c>
+      <c r="F73">
+        <v>180.2193</v>
+      </c>
+      <c r="G73">
+        <v>6.57</v>
+      </c>
+      <c r="H73">
+        <v>247.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>12</v>
+      </c>
+      <c r="K73">
+        <v>1.15</v>
+      </c>
+      <c r="L73">
+        <v>10.85</v>
+      </c>
+      <c r="M73">
+        <v>43.03636883999999</v>
+      </c>
+      <c r="N73">
+        <v>-32.18636883999999</v>
+      </c>
+      <c r="O73">
+        <v>-6.437273767999997</v>
+      </c>
+      <c r="P73">
+        <v>-25.749095072</v>
+      </c>
+      <c r="Q73">
+        <v>-24.599095072</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2913703257062674</v>
+      </c>
+      <c r="T73">
+        <v>3.541670688059783</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.05042246961093755</v>
+      </c>
+      <c r="W73">
+        <v>0.2267591142569081</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2521123480546879</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2474963655772223</v>
+      </c>
+      <c r="C74">
+        <v>-86.18703885748621</v>
+      </c>
+      <c r="D74">
+        <v>90.00056114251376</v>
+      </c>
+      <c r="E74">
+        <v>176.6276</v>
+      </c>
+      <c r="F74">
+        <v>182.7576</v>
+      </c>
+      <c r="G74">
+        <v>6.57</v>
+      </c>
+      <c r="H74">
+        <v>247.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>12</v>
+      </c>
+      <c r="K74">
+        <v>1.15</v>
+      </c>
+      <c r="L74">
+        <v>10.85</v>
+      </c>
+      <c r="M74">
+        <v>43.64251487999999</v>
+      </c>
+      <c r="N74">
+        <v>-32.79251487999999</v>
+      </c>
+      <c r="O74">
+        <v>-6.558502975999997</v>
+      </c>
+      <c r="P74">
+        <v>-26.234011904</v>
+      </c>
+      <c r="Q74">
+        <v>-25.084011904</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3003906944814913</v>
+      </c>
+      <c r="T74">
+        <v>3.668158926919061</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.04972215753300786</v>
+      </c>
+      <c r="W74">
+        <v>0.2269263487811177</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2486107876650394</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2494963655772223</v>
+      </c>
+      <c r="C75">
+        <v>-89.57965412672164</v>
+      </c>
+      <c r="D75">
+        <v>89.14624587327835</v>
+      </c>
+      <c r="E75">
+        <v>179.1659</v>
+      </c>
+      <c r="F75">
+        <v>185.2959</v>
+      </c>
+      <c r="G75">
+        <v>6.57</v>
+      </c>
+      <c r="H75">
+        <v>247.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>12</v>
+      </c>
+      <c r="K75">
+        <v>1.15</v>
+      </c>
+      <c r="L75">
+        <v>10.85</v>
+      </c>
+      <c r="M75">
+        <v>44.24866092</v>
+      </c>
+      <c r="N75">
+        <v>-33.39866092</v>
+      </c>
+      <c r="O75">
+        <v>-6.679732183999998</v>
+      </c>
+      <c r="P75">
+        <v>-26.718928736</v>
+      </c>
+      <c r="Q75">
+        <v>-25.568928736</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3100792387215465</v>
+      </c>
+      <c r="T75">
+        <v>3.8040166649531</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.04904103208735022</v>
+      </c>
+      <c r="W75">
+        <v>0.2270890015375408</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.2452051604367512</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2514963655772223</v>
+      </c>
+      <c r="C76">
+        <v>-92.95620301387444</v>
+      </c>
+      <c r="D76">
+        <v>88.30799698612554</v>
+      </c>
+      <c r="E76">
+        <v>181.7042</v>
+      </c>
+      <c r="F76">
+        <v>187.8342</v>
+      </c>
+      <c r="G76">
+        <v>6.57</v>
+      </c>
+      <c r="H76">
+        <v>247.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>12</v>
+      </c>
+      <c r="K76">
+        <v>1.15</v>
+      </c>
+      <c r="L76">
+        <v>10.85</v>
+      </c>
+      <c r="M76">
+        <v>44.85480696</v>
+      </c>
+      <c r="N76">
+        <v>-34.00480696</v>
+      </c>
+      <c r="O76">
+        <v>-6.800961391999998</v>
+      </c>
+      <c r="P76">
+        <v>-27.203845568</v>
+      </c>
+      <c r="Q76">
+        <v>-26.053845568</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3205130555954522</v>
+      </c>
+      <c r="T76">
+        <v>3.950324998220527</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.04837831543752116</v>
+      </c>
+      <c r="W76">
+        <v>0.22724725827352</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2418915771876059</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2534963655772223</v>
+      </c>
+      <c r="C77">
+        <v>-96.31713451719503</v>
+      </c>
+      <c r="D77">
+        <v>87.48536548280498</v>
+      </c>
+      <c r="E77">
+        <v>184.2425</v>
+      </c>
+      <c r="F77">
+        <v>190.3725</v>
+      </c>
+      <c r="G77">
+        <v>6.57</v>
+      </c>
+      <c r="H77">
+        <v>247.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>12</v>
+      </c>
+      <c r="K77">
+        <v>1.15</v>
+      </c>
+      <c r="L77">
+        <v>10.85</v>
+      </c>
+      <c r="M77">
+        <v>45.460953</v>
+      </c>
+      <c r="N77">
+        <v>-34.610953</v>
+      </c>
+      <c r="O77">
+        <v>-6.922190599999999</v>
+      </c>
+      <c r="P77">
+        <v>-27.6887624</v>
+      </c>
+      <c r="Q77">
+        <v>-26.5387624</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3317815778192703</v>
+      </c>
+      <c r="T77">
+        <v>4.108337998149349</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.04773327123168754</v>
+      </c>
+      <c r="W77">
+        <v>0.227401294829873</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2386663561584378</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2554963655772223</v>
+      </c>
+      <c r="C78">
+        <v>-99.66288105880884</v>
+      </c>
+      <c r="D78">
+        <v>86.67791894119115</v>
+      </c>
+      <c r="E78">
+        <v>186.7808</v>
+      </c>
+      <c r="F78">
+        <v>192.9108</v>
+      </c>
+      <c r="G78">
+        <v>6.57</v>
+      </c>
+      <c r="H78">
+        <v>247.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>12</v>
+      </c>
+      <c r="K78">
+        <v>1.15</v>
+      </c>
+      <c r="L78">
+        <v>10.85</v>
+      </c>
+      <c r="M78">
+        <v>46.06709904</v>
+      </c>
+      <c r="N78">
+        <v>-35.21709904</v>
+      </c>
+      <c r="O78">
+        <v>-7.043419807999999</v>
+      </c>
+      <c r="P78">
+        <v>-28.173679232</v>
+      </c>
+      <c r="Q78">
+        <v>-27.023679232</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3439891435617399</v>
+      </c>
+      <c r="T78">
+        <v>4.279518748072239</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.04710520187337586</v>
+      </c>
+      <c r="W78">
+        <v>0.2275512777926379</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2355260093668794</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2574963655772223</v>
+      </c>
+      <c r="C79">
+        <v>-102.9938592426682</v>
+      </c>
+      <c r="D79">
+        <v>85.88524075733184</v>
+      </c>
+      <c r="E79">
+        <v>189.3191</v>
+      </c>
+      <c r="F79">
+        <v>195.4491</v>
+      </c>
+      <c r="G79">
+        <v>6.57</v>
+      </c>
+      <c r="H79">
+        <v>247.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>12</v>
+      </c>
+      <c r="K79">
+        <v>1.15</v>
+      </c>
+      <c r="L79">
+        <v>10.85</v>
+      </c>
+      <c r="M79">
+        <v>46.67324508</v>
+      </c>
+      <c r="N79">
+        <v>-35.82324508</v>
+      </c>
+      <c r="O79">
+        <v>-7.164649015999998</v>
+      </c>
+      <c r="P79">
+        <v>-28.658596064</v>
+      </c>
+      <c r="Q79">
+        <v>-27.508596064</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3572582367600764</v>
+      </c>
+      <c r="T79">
+        <v>4.465584780597118</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.04649344600489046</v>
+      </c>
+      <c r="W79">
+        <v>0.2276973650940322</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2324672300244524</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2594963655772223</v>
+      </c>
+      <c r="C80">
+        <v>-106.3104705712911</v>
+      </c>
+      <c r="D80">
+        <v>85.1069294287089</v>
+      </c>
+      <c r="E80">
+        <v>191.8574</v>
+      </c>
+      <c r="F80">
+        <v>197.9874</v>
+      </c>
+      <c r="G80">
+        <v>6.57</v>
+      </c>
+      <c r="H80">
+        <v>247.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>12</v>
+      </c>
+      <c r="K80">
+        <v>1.15</v>
+      </c>
+      <c r="L80">
+        <v>10.85</v>
+      </c>
+      <c r="M80">
+        <v>47.27939112000001</v>
+      </c>
+      <c r="N80">
+        <v>-36.42939112000001</v>
+      </c>
+      <c r="O80">
+        <v>-7.285878223999999</v>
+      </c>
+      <c r="P80">
+        <v>-29.143512896</v>
+      </c>
+      <c r="Q80">
+        <v>-27.99351289600001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3717336111582618</v>
+      </c>
+      <c r="T80">
+        <v>4.668565906987897</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.04589737618431493</v>
+      </c>
+      <c r="W80">
+        <v>0.2278397065671856</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2294868809215748</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2614963655772223</v>
+      </c>
+      <c r="C81">
+        <v>-109.6131021238794</v>
+      </c>
+      <c r="D81">
+        <v>84.34259787612056</v>
+      </c>
+      <c r="E81">
+        <v>194.3957</v>
+      </c>
+      <c r="F81">
+        <v>200.5257</v>
+      </c>
+      <c r="G81">
+        <v>6.57</v>
+      </c>
+      <c r="H81">
+        <v>247.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>12</v>
+      </c>
+      <c r="K81">
+        <v>1.15</v>
+      </c>
+      <c r="L81">
+        <v>10.85</v>
+      </c>
+      <c r="M81">
+        <v>47.88553716000001</v>
+      </c>
+      <c r="N81">
+        <v>-37.03553716</v>
+      </c>
+      <c r="O81">
+        <v>-7.407107431999999</v>
+      </c>
+      <c r="P81">
+        <v>-29.628429728</v>
+      </c>
+      <c r="Q81">
+        <v>-28.47842972800001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3875875926419884</v>
+      </c>
+      <c r="T81">
+        <v>4.890878569225415</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.04531639673894387</v>
+      </c>
+      <c r="W81">
+        <v>0.2279784444587402</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2265819836947194</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2634963655772223</v>
+      </c>
+      <c r="C82">
+        <v>-112.902127198221</v>
+      </c>
+      <c r="D82">
+        <v>83.591872801779</v>
+      </c>
+      <c r="E82">
+        <v>196.934</v>
+      </c>
+      <c r="F82">
+        <v>203.064</v>
+      </c>
+      <c r="G82">
+        <v>6.57</v>
+      </c>
+      <c r="H82">
+        <v>247.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>12</v>
+      </c>
+      <c r="K82">
+        <v>1.15</v>
+      </c>
+      <c r="L82">
+        <v>10.85</v>
+      </c>
+      <c r="M82">
+        <v>48.4916832</v>
+      </c>
+      <c r="N82">
+        <v>-37.6416832</v>
+      </c>
+      <c r="O82">
+        <v>-7.528336639999999</v>
+      </c>
+      <c r="P82">
+        <v>-30.11334656</v>
+      </c>
+      <c r="Q82">
+        <v>-28.96334656000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4050269722740879</v>
+      </c>
+      <c r="T82">
+        <v>5.135422497686687</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.04474994177970706</v>
+      </c>
+      <c r="W82">
+        <v>0.228113713903006</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2237497088985354</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2654963655772223</v>
+      </c>
+      <c r="C83">
+        <v>-116.1779059186137</v>
+      </c>
+      <c r="D83">
+        <v>82.85439408138635</v>
+      </c>
+      <c r="E83">
+        <v>199.4723</v>
+      </c>
+      <c r="F83">
+        <v>205.6023</v>
+      </c>
+      <c r="G83">
+        <v>6.57</v>
+      </c>
+      <c r="H83">
+        <v>247.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>12</v>
+      </c>
+      <c r="K83">
+        <v>1.15</v>
+      </c>
+      <c r="L83">
+        <v>10.85</v>
+      </c>
+      <c r="M83">
+        <v>49.09782924</v>
+      </c>
+      <c r="N83">
+        <v>-38.24782924</v>
+      </c>
+      <c r="O83">
+        <v>-7.649565847999998</v>
+      </c>
+      <c r="P83">
+        <v>-30.598263392</v>
+      </c>
+      <c r="Q83">
+        <v>-29.448263392</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4243020760779872</v>
+      </c>
+      <c r="T83">
+        <v>5.405707892301775</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.04419747336267365</v>
+      </c>
+      <c r="W83">
+        <v>0.2282456433609935</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.2209873668133683</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2674963655772223</v>
+      </c>
+      <c r="C84">
+        <v>-119.4407858118906</v>
+      </c>
+      <c r="D84">
+        <v>82.12981418810936</v>
+      </c>
+      <c r="E84">
+        <v>202.0106</v>
+      </c>
+      <c r="F84">
+        <v>208.1406</v>
+      </c>
+      <c r="G84">
+        <v>6.57</v>
+      </c>
+      <c r="H84">
+        <v>247.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>12</v>
+      </c>
+      <c r="K84">
+        <v>1.15</v>
+      </c>
+      <c r="L84">
+        <v>10.85</v>
+      </c>
+      <c r="M84">
+        <v>49.70397528</v>
+      </c>
+      <c r="N84">
+        <v>-38.85397528</v>
+      </c>
+      <c r="O84">
+        <v>-7.770795055999998</v>
+      </c>
+      <c r="P84">
+        <v>-31.083180224</v>
+      </c>
+      <c r="Q84">
+        <v>-29.933180224</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4457188580823199</v>
+      </c>
+      <c r="T84">
+        <v>5.706024997429653</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.04365847978508007</v>
+      </c>
+      <c r="W84">
+        <v>0.2283743550273229</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2182923989254004</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2694963655772223</v>
+      </c>
+      <c r="C85">
+        <v>-122.691102353483</v>
+      </c>
+      <c r="D85">
+        <v>81.41779764651702</v>
+      </c>
+      <c r="E85">
+        <v>204.5489</v>
+      </c>
+      <c r="F85">
+        <v>210.6789</v>
+      </c>
+      <c r="G85">
+        <v>6.57</v>
+      </c>
+      <c r="H85">
+        <v>247.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>12</v>
+      </c>
+      <c r="K85">
+        <v>1.15</v>
+      </c>
+      <c r="L85">
+        <v>10.85</v>
+      </c>
+      <c r="M85">
+        <v>50.31012132</v>
+      </c>
+      <c r="N85">
+        <v>-39.46012132</v>
+      </c>
+      <c r="O85">
+        <v>-7.892024263999998</v>
+      </c>
+      <c r="P85">
+        <v>-31.568097056</v>
+      </c>
+      <c r="Q85">
+        <v>-30.418097056</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.469655261498927</v>
+      </c>
+      <c r="T85">
+        <v>6.041673526690221</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.04313247400453694</v>
+      </c>
+      <c r="W85">
+        <v>0.2284999652077166</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2156623700226847</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2714963655772223</v>
+      </c>
+      <c r="C86">
+        <v>-125.9291794853222</v>
+      </c>
+      <c r="D86">
+        <v>80.71802051467783</v>
+      </c>
+      <c r="E86">
+        <v>207.0872</v>
+      </c>
+      <c r="F86">
+        <v>213.2172</v>
+      </c>
+      <c r="G86">
+        <v>6.57</v>
+      </c>
+      <c r="H86">
+        <v>247.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>12</v>
+      </c>
+      <c r="K86">
+        <v>1.15</v>
+      </c>
+      <c r="L86">
+        <v>10.85</v>
+      </c>
+      <c r="M86">
+        <v>50.91626736</v>
+      </c>
+      <c r="N86">
+        <v>-40.06626736</v>
+      </c>
+      <c r="O86">
+        <v>-8.013253471999997</v>
+      </c>
+      <c r="P86">
+        <v>-32.053013888</v>
+      </c>
+      <c r="Q86">
+        <v>-30.903013888</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4965837153426097</v>
+      </c>
+      <c r="T86">
+        <v>6.419278122108357</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.04261899217114959</v>
+      </c>
+      <c r="W86">
+        <v>0.2286225846695295</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2130949608557481</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2734963655772223</v>
+      </c>
+      <c r="C87">
+        <v>-129.1553301072622</v>
+      </c>
+      <c r="D87">
+        <v>80.0301698927378</v>
+      </c>
+      <c r="E87">
+        <v>209.6255</v>
+      </c>
+      <c r="F87">
+        <v>215.7555</v>
+      </c>
+      <c r="G87">
+        <v>6.57</v>
+      </c>
+      <c r="H87">
+        <v>247.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>12</v>
+      </c>
+      <c r="K87">
+        <v>1.15</v>
+      </c>
+      <c r="L87">
+        <v>10.85</v>
+      </c>
+      <c r="M87">
+        <v>51.5224134</v>
+      </c>
+      <c r="N87">
+        <v>-40.6724134</v>
+      </c>
+      <c r="O87">
+        <v>-8.134482679999998</v>
+      </c>
+      <c r="P87">
+        <v>-32.53793072</v>
+      </c>
+      <c r="Q87">
+        <v>-31.38793072</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5271026296987837</v>
+      </c>
+      <c r="T87">
+        <v>6.84722999691558</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.04211759226325371</v>
+      </c>
+      <c r="W87">
+        <v>0.228742318967535</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2105879613162687</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2754963655772223</v>
+      </c>
+      <c r="C88">
+        <v>-132.3698565435876</v>
+      </c>
+      <c r="D88">
+        <v>79.35394345641234</v>
+      </c>
+      <c r="E88">
+        <v>212.1638</v>
+      </c>
+      <c r="F88">
+        <v>218.2938</v>
+      </c>
+      <c r="G88">
+        <v>6.57</v>
+      </c>
+      <c r="H88">
+        <v>247.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>12</v>
+      </c>
+      <c r="K88">
+        <v>1.15</v>
+      </c>
+      <c r="L88">
+        <v>10.85</v>
+      </c>
+      <c r="M88">
+        <v>52.12855944</v>
+      </c>
+      <c r="N88">
+        <v>-41.27855944</v>
+      </c>
+      <c r="O88">
+        <v>-8.255711887999997</v>
+      </c>
+      <c r="P88">
+        <v>-33.022847552</v>
+      </c>
+      <c r="Q88">
+        <v>-31.872847552</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5619813889629826</v>
+      </c>
+      <c r="T88">
+        <v>7.336317853838122</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.04162785281833217</v>
+      </c>
+      <c r="W88">
+        <v>0.2288592687469823</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2081392640916608</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2774963655772223</v>
+      </c>
+      <c r="C89">
+        <v>-135.5730509860691</v>
+      </c>
+      <c r="D89">
+        <v>78.68904901393084</v>
+      </c>
+      <c r="E89">
+        <v>214.7021</v>
+      </c>
+      <c r="F89">
+        <v>220.8321</v>
+      </c>
+      <c r="G89">
+        <v>6.57</v>
+      </c>
+      <c r="H89">
+        <v>247.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>12</v>
+      </c>
+      <c r="K89">
+        <v>1.15</v>
+      </c>
+      <c r="L89">
+        <v>10.85</v>
+      </c>
+      <c r="M89">
+        <v>52.73470548</v>
+      </c>
+      <c r="N89">
+        <v>-41.88470548</v>
+      </c>
+      <c r="O89">
+        <v>-8.376941095999998</v>
+      </c>
+      <c r="P89">
+        <v>-33.50776438400001</v>
+      </c>
+      <c r="Q89">
+        <v>-32.35776438400001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6022261111909044</v>
+      </c>
+      <c r="T89">
+        <v>7.900649996441055</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.04114937175145477</v>
+      </c>
+      <c r="W89">
+        <v>0.2289735300257526</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2057468587572739</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2794963655772223</v>
+      </c>
+      <c r="C90">
+        <v>-138.7651959149298</v>
+      </c>
+      <c r="D90">
+        <v>78.03520408507016</v>
+      </c>
+      <c r="E90">
+        <v>217.2404</v>
+      </c>
+      <c r="F90">
+        <v>223.3704</v>
+      </c>
+      <c r="G90">
+        <v>6.57</v>
+      </c>
+      <c r="H90">
+        <v>247.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>12</v>
+      </c>
+      <c r="K90">
+        <v>1.15</v>
+      </c>
+      <c r="L90">
+        <v>10.85</v>
+      </c>
+      <c r="M90">
+        <v>53.34085152</v>
+      </c>
+      <c r="N90">
+        <v>-42.49085152</v>
+      </c>
+      <c r="O90">
+        <v>-8.498170303999999</v>
+      </c>
+      <c r="P90">
+        <v>-33.992681216</v>
+      </c>
+      <c r="Q90">
+        <v>-32.842681216</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6491782871234799</v>
+      </c>
+      <c r="T90">
+        <v>8.559037496144478</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.04068176525427915</v>
+      </c>
+      <c r="W90">
+        <v>0.2290851944572782</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2034088262713959</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2814963655772224</v>
+      </c>
+      <c r="C91">
+        <v>-141.9465644989976</v>
+      </c>
+      <c r="D91">
+        <v>77.39213550100237</v>
+      </c>
+      <c r="E91">
+        <v>219.7787</v>
+      </c>
+      <c r="F91">
+        <v>225.9087</v>
+      </c>
+      <c r="G91">
+        <v>6.57</v>
+      </c>
+      <c r="H91">
+        <v>247.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>12</v>
+      </c>
+      <c r="K91">
+        <v>1.15</v>
+      </c>
+      <c r="L91">
+        <v>10.85</v>
+      </c>
+      <c r="M91">
+        <v>53.94699756</v>
+      </c>
+      <c r="N91">
+        <v>-43.09699756</v>
+      </c>
+      <c r="O91">
+        <v>-8.619399511999998</v>
+      </c>
+      <c r="P91">
+        <v>-34.477598048</v>
+      </c>
+      <c r="Q91">
+        <v>-33.32759804800001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.7046672223165236</v>
+      </c>
+      <c r="T91">
+        <v>9.337131813975795</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.04022466676827602</v>
+      </c>
+      <c r="W91">
+        <v>0.2291943495757357</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2011233338413801</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2834963655772224</v>
+      </c>
+      <c r="C92">
+        <v>-145.1174209762337</v>
+      </c>
+      <c r="D92">
+        <v>76.75957902376628</v>
+      </c>
+      <c r="E92">
+        <v>222.317</v>
+      </c>
+      <c r="F92">
+        <v>228.447</v>
+      </c>
+      <c r="G92">
+        <v>6.57</v>
+      </c>
+      <c r="H92">
+        <v>247.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>12</v>
+      </c>
+      <c r="K92">
+        <v>1.15</v>
+      </c>
+      <c r="L92">
+        <v>10.85</v>
+      </c>
+      <c r="M92">
+        <v>54.55314360000001</v>
+      </c>
+      <c r="N92">
+        <v>-43.7031436</v>
+      </c>
+      <c r="O92">
+        <v>-8.740628719999998</v>
+      </c>
+      <c r="P92">
+        <v>-34.96251488000001</v>
+      </c>
+      <c r="Q92">
+        <v>-33.81251488000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7712539445481759</v>
+      </c>
+      <c r="T92">
+        <v>10.27084499537337</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.03977772602640628</v>
+      </c>
+      <c r="W92">
+        <v>0.2293010790248942</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1988886301320315</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2854963655772224</v>
+      </c>
+      <c r="C93">
+        <v>-148.2780210157512</v>
+      </c>
+      <c r="D93">
+        <v>76.13727898424877</v>
+      </c>
+      <c r="E93">
+        <v>224.8553</v>
+      </c>
+      <c r="F93">
+        <v>230.9853</v>
+      </c>
+      <c r="G93">
+        <v>6.57</v>
+      </c>
+      <c r="H93">
+        <v>247.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>12</v>
+      </c>
+      <c r="K93">
+        <v>1.15</v>
+      </c>
+      <c r="L93">
+        <v>10.85</v>
+      </c>
+      <c r="M93">
+        <v>55.15928964</v>
+      </c>
+      <c r="N93">
+        <v>-44.30928964</v>
+      </c>
+      <c r="O93">
+        <v>-8.861857927999999</v>
+      </c>
+      <c r="P93">
+        <v>-35.447431712</v>
+      </c>
+      <c r="Q93">
+        <v>-34.29743171200001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8526377161646399</v>
+      </c>
+      <c r="T93">
+        <v>11.41204999485931</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.03934060815798424</v>
+      </c>
+      <c r="W93">
+        <v>0.2294054627718734</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1967030407899213</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2874963655772224</v>
+      </c>
+      <c r="C94">
+        <v>-151.4286120623657</v>
+      </c>
+      <c r="D94">
+        <v>75.52498793763428</v>
+      </c>
+      <c r="E94">
+        <v>227.3936</v>
+      </c>
+      <c r="F94">
+        <v>233.5236</v>
+      </c>
+      <c r="G94">
+        <v>6.57</v>
+      </c>
+      <c r="H94">
+        <v>247.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>12</v>
+      </c>
+      <c r="K94">
+        <v>1.15</v>
+      </c>
+      <c r="L94">
+        <v>10.85</v>
+      </c>
+      <c r="M94">
+        <v>55.76543568</v>
+      </c>
+      <c r="N94">
+        <v>-44.91543568</v>
+      </c>
+      <c r="O94">
+        <v>-8.983087135999998</v>
+      </c>
+      <c r="P94">
+        <v>-35.93234854400001</v>
+      </c>
+      <c r="Q94">
+        <v>-34.78234854400001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.9543674306852201</v>
+      </c>
+      <c r="T94">
+        <v>12.83855624421672</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.03891299285191919</v>
+      </c>
+      <c r="W94">
+        <v>0.2295075773069617</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.194564964259596</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2894963655772224</v>
+      </c>
+      <c r="C95">
+        <v>-154.5694336646533</v>
+      </c>
+      <c r="D95">
+        <v>74.92246633534668</v>
+      </c>
+      <c r="E95">
+        <v>229.9319</v>
+      </c>
+      <c r="F95">
+        <v>236.0619</v>
+      </c>
+      <c r="G95">
+        <v>6.57</v>
+      </c>
+      <c r="H95">
+        <v>247.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>12</v>
+      </c>
+      <c r="K95">
+        <v>1.15</v>
+      </c>
+      <c r="L95">
+        <v>10.85</v>
+      </c>
+      <c r="M95">
+        <v>56.37158172</v>
+      </c>
+      <c r="N95">
+        <v>-45.52158172</v>
+      </c>
+      <c r="O95">
+        <v>-9.104316343999997</v>
+      </c>
+      <c r="P95">
+        <v>-36.417265376</v>
+      </c>
+      <c r="Q95">
+        <v>-35.267265376</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.085162777925966</v>
+      </c>
+      <c r="T95">
+        <v>14.67263570767626</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.03849457357394157</v>
+      </c>
+      <c r="W95">
+        <v>0.2296074958305428</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1924728678697079</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2914963655772224</v>
+      </c>
+      <c r="C96">
+        <v>-157.7007177874301</v>
+      </c>
+      <c r="D96">
+        <v>74.32948221256986</v>
+      </c>
+      <c r="E96">
+        <v>232.4702</v>
+      </c>
+      <c r="F96">
+        <v>238.6002</v>
+      </c>
+      <c r="G96">
+        <v>6.57</v>
+      </c>
+      <c r="H96">
+        <v>247.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>12</v>
+      </c>
+      <c r="K96">
+        <v>1.15</v>
+      </c>
+      <c r="L96">
+        <v>10.85</v>
+      </c>
+      <c r="M96">
+        <v>56.97772776</v>
+      </c>
+      <c r="N96">
+        <v>-46.12772776</v>
+      </c>
+      <c r="O96">
+        <v>-9.225545551999998</v>
+      </c>
+      <c r="P96">
+        <v>-36.902182208</v>
+      </c>
+      <c r="Q96">
+        <v>-35.752182208</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.259556574246961</v>
+      </c>
+      <c r="T96">
+        <v>17.11807499228897</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.03808505683379325</v>
+      </c>
+      <c r="W96">
+        <v>0.2297052884280902</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1904252841689663</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2934963655772224</v>
+      </c>
+      <c r="C97">
+        <v>-160.822689109509</v>
+      </c>
+      <c r="D97">
+        <v>73.74581089049101</v>
+      </c>
+      <c r="E97">
+        <v>235.0085</v>
+      </c>
+      <c r="F97">
+        <v>241.1385</v>
+      </c>
+      <c r="G97">
+        <v>6.57</v>
+      </c>
+      <c r="H97">
+        <v>247.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>12</v>
+      </c>
+      <c r="K97">
+        <v>1.15</v>
+      </c>
+      <c r="L97">
+        <v>10.85</v>
+      </c>
+      <c r="M97">
+        <v>57.5838738</v>
+      </c>
+      <c r="N97">
+        <v>-46.7338738</v>
+      </c>
+      <c r="O97">
+        <v>-9.346774759999997</v>
+      </c>
+      <c r="P97">
+        <v>-37.38709904</v>
+      </c>
+      <c r="Q97">
+        <v>-36.23709904</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.503707889096354</v>
+      </c>
+      <c r="T97">
+        <v>20.54168999074678</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.03768416149870069</v>
+      </c>
+      <c r="W97">
+        <v>0.2298010222341103</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1884208074935035</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2954963655772223</v>
+      </c>
+      <c r="C98">
+        <v>-163.935565307537</v>
+      </c>
+      <c r="D98">
+        <v>73.17123469246296</v>
+      </c>
+      <c r="E98">
+        <v>237.5468</v>
+      </c>
+      <c r="F98">
+        <v>243.6768</v>
+      </c>
+      <c r="G98">
+        <v>6.57</v>
+      </c>
+      <c r="H98">
+        <v>247.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>12</v>
+      </c>
+      <c r="K98">
+        <v>1.15</v>
+      </c>
+      <c r="L98">
+        <v>10.85</v>
+      </c>
+      <c r="M98">
+        <v>58.19001984</v>
+      </c>
+      <c r="N98">
+        <v>-47.34001984</v>
+      </c>
+      <c r="O98">
+        <v>-9.468003967999998</v>
+      </c>
+      <c r="P98">
+        <v>-37.872015872</v>
+      </c>
+      <c r="Q98">
+        <v>-36.722015872</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.869934861370438</v>
+      </c>
+      <c r="T98">
+        <v>25.67711248843341</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.03729161814975589</v>
+      </c>
+      <c r="W98">
+        <v>0.2298947615858383</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1864580907487795</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2974963655772224</v>
+      </c>
+      <c r="C99">
+        <v>-167.0395573266669</v>
+      </c>
+      <c r="D99">
+        <v>72.60554267333312</v>
+      </c>
+      <c r="E99">
+        <v>240.0851</v>
+      </c>
+      <c r="F99">
+        <v>246.2151</v>
+      </c>
+      <c r="G99">
+        <v>6.57</v>
+      </c>
+      <c r="H99">
+        <v>247.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>12</v>
+      </c>
+      <c r="K99">
+        <v>1.15</v>
+      </c>
+      <c r="L99">
+        <v>10.85</v>
+      </c>
+      <c r="M99">
+        <v>58.79616588</v>
+      </c>
+      <c r="N99">
+        <v>-47.94616588</v>
+      </c>
+      <c r="O99">
+        <v>-9.589233175999997</v>
+      </c>
+      <c r="P99">
+        <v>-38.356932704</v>
+      </c>
+      <c r="Q99">
+        <v>-37.206932704</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.480313148493917</v>
+      </c>
+      <c r="T99">
+        <v>34.23614998457788</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.03690716847810893</v>
+      </c>
+      <c r="W99">
+        <v>0.2299865681674276</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1845358423905447</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2994963655772224</v>
+      </c>
+      <c r="C100">
+        <v>-170.1348696387685</v>
+      </c>
+      <c r="D100">
+        <v>72.04853036123147</v>
+      </c>
+      <c r="E100">
+        <v>242.6234</v>
+      </c>
+      <c r="F100">
+        <v>248.7534</v>
+      </c>
+      <c r="G100">
+        <v>6.57</v>
+      </c>
+      <c r="H100">
+        <v>247.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>12</v>
+      </c>
+      <c r="K100">
+        <v>1.15</v>
+      </c>
+      <c r="L100">
+        <v>10.85</v>
+      </c>
+      <c r="M100">
+        <v>59.40231192</v>
+      </c>
+      <c r="N100">
+        <v>-48.55231191999999</v>
+      </c>
+      <c r="O100">
+        <v>-9.710462383999996</v>
+      </c>
+      <c r="P100">
+        <v>-38.841849536</v>
+      </c>
+      <c r="Q100">
+        <v>-37.691849536</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.701069722740876</v>
+      </c>
+      <c r="T100">
+        <v>51.35422497686682</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.03653056471812823</v>
+      </c>
+      <c r="W100">
+        <v>0.230076501145311</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1826528235906412</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3014963655772223</v>
+      </c>
+      <c r="C101">
+        <v>-173.2217004888465</v>
+      </c>
+      <c r="D101">
+        <v>71.49999951115352</v>
+      </c>
+      <c r="E101">
+        <v>245.1617</v>
+      </c>
+      <c r="F101">
+        <v>251.2917</v>
+      </c>
+      <c r="G101">
+        <v>6.57</v>
+      </c>
+      <c r="H101">
+        <v>247.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>12</v>
+      </c>
+      <c r="K101">
+        <v>1.15</v>
+      </c>
+      <c r="L101">
+        <v>10.85</v>
+      </c>
+      <c r="M101">
+        <v>60.00845796</v>
+      </c>
+      <c r="N101">
+        <v>-49.15845796</v>
+      </c>
+      <c r="O101">
+        <v>-9.831691591999999</v>
+      </c>
+      <c r="P101">
+        <v>-39.326766368</v>
+      </c>
+      <c r="Q101">
+        <v>-38.176766368</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.363339445481751</v>
+      </c>
+      <c r="T101">
+        <v>102.7084499537336</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.0361615691149148</v>
+      </c>
+      <c r="W101">
+        <v>0.2301646172953583</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1808078455745741</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_machinery.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_machinery.xlsx
@@ -1519,7 +1519,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1656,22 +1656,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09875159672360384</v>
+        <v>0.09859009353015663</v>
       </c>
       <c r="C2">
-        <v>33.97059154412668</v>
+        <v>33.71641167586966</v>
       </c>
       <c r="D2">
-        <v>28.28059154412669</v>
+        <v>28.36711167586965</v>
       </c>
       <c r="E2">
-        <v>-1.17</v>
+        <v>-0.8292999999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.3407</v>
       </c>
       <c r="G2">
         <v>5.69</v>
@@ -1692,28 +1692,28 @@
         <v>0.377</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01713721</v>
       </c>
       <c r="N2">
-        <v>0.377</v>
+        <v>0.35986279</v>
       </c>
       <c r="O2">
-        <v>0.07540000000000001</v>
+        <v>0.07197255800000001</v>
       </c>
       <c r="P2">
-        <v>0.3016</v>
+        <v>0.287890232</v>
       </c>
       <c r="Q2">
-        <v>0.6586</v>
+        <v>0.644890232</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09875159672360384</v>
+        <v>0.09917948841429963</v>
       </c>
       <c r="T2">
-        <v>1.032125178898191</v>
+        <v>1.040465584384237</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>21.99891347541402</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1738,22 +1738,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09859009353015663</v>
+        <v>0.09845259033670942</v>
       </c>
       <c r="C3">
-        <v>33.71641167586966</v>
+        <v>33.44979290187131</v>
       </c>
       <c r="D3">
-        <v>28.36711167586965</v>
+        <v>28.4411929018713</v>
       </c>
       <c r="E3">
-        <v>-0.8292999999999999</v>
+        <v>-0.4885999999999999</v>
       </c>
       <c r="F3">
-        <v>0.3407</v>
+        <v>0.6814</v>
       </c>
       <c r="G3">
         <v>5.69</v>
@@ -1774,45 +1774,45 @@
         <v>0.377</v>
       </c>
       <c r="M3">
-        <v>0.01713721</v>
+        <v>0.03529652</v>
       </c>
       <c r="N3">
-        <v>0.35986279</v>
+        <v>0.34170348</v>
       </c>
       <c r="O3">
-        <v>0.07197255800000001</v>
+        <v>0.06834069600000001</v>
       </c>
       <c r="P3">
-        <v>0.287890232</v>
+        <v>0.273362784</v>
       </c>
       <c r="Q3">
-        <v>0.644890232</v>
+        <v>0.630362784</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09917948841429963</v>
+        <v>0.09961611258847899</v>
       </c>
       <c r="T3">
-        <v>1.040465584384237</v>
+        <v>1.048976202227141</v>
       </c>
       <c r="U3">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V3">
         <v>0.2</v>
       </c>
       <c r="W3">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y3">
-        <v>21.99891347541402</v>
+        <v>10.68093965070778</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1820,22 +1820,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09845259033670942</v>
+        <v>0.09836308714326221</v>
       </c>
       <c r="C4">
-        <v>33.44979290187131</v>
+        <v>33.15752189888259</v>
       </c>
       <c r="D4">
-        <v>28.4411929018713</v>
+        <v>28.4896218988826</v>
       </c>
       <c r="E4">
-        <v>-0.4885999999999999</v>
+        <v>-0.1478999999999999</v>
       </c>
       <c r="F4">
-        <v>0.6814</v>
+        <v>1.0221</v>
       </c>
       <c r="G4">
         <v>5.69</v>
@@ -1856,45 +1856,45 @@
         <v>0.377</v>
       </c>
       <c r="M4">
-        <v>0.03529652</v>
+        <v>0.05550003</v>
       </c>
       <c r="N4">
-        <v>0.34170348</v>
+        <v>0.32149997</v>
       </c>
       <c r="O4">
-        <v>0.06834069600000001</v>
+        <v>0.06429999400000001</v>
       </c>
       <c r="P4">
-        <v>0.273362784</v>
+        <v>0.257199976</v>
       </c>
       <c r="Q4">
-        <v>0.630362784</v>
+        <v>0.614199976</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09961611258847899</v>
+        <v>0.1000617393229507</v>
       </c>
       <c r="T4">
-        <v>1.048976202227141</v>
+        <v>1.0576622967266</v>
       </c>
       <c r="U4">
-        <v>0.0518</v>
+        <v>0.0543</v>
       </c>
       <c r="V4">
         <v>0.2</v>
       </c>
       <c r="W4">
-        <v>0.04144</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y4">
-        <v>10.68093965070778</v>
+        <v>6.792789121014891</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1902,22 +1902,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09836308714326221</v>
+        <v>0.09826558394981501</v>
       </c>
       <c r="C5">
-        <v>33.15752189888259</v>
+        <v>32.86976763790079</v>
       </c>
       <c r="D5">
-        <v>28.4896218988826</v>
+        <v>28.54256763790079</v>
       </c>
       <c r="E5">
-        <v>-0.1478999999999999</v>
+        <v>0.1928000000000001</v>
       </c>
       <c r="F5">
-        <v>1.0221</v>
+        <v>1.3628</v>
       </c>
       <c r="G5">
         <v>5.69</v>
@@ -1938,45 +1938,45 @@
         <v>0.377</v>
       </c>
       <c r="M5">
-        <v>0.05550003</v>
+        <v>0.07536284</v>
       </c>
       <c r="N5">
-        <v>0.32149997</v>
+        <v>0.30163716</v>
       </c>
       <c r="O5">
-        <v>0.06429999400000001</v>
+        <v>0.06032743200000001</v>
       </c>
       <c r="P5">
-        <v>0.257199976</v>
+        <v>0.241309728</v>
       </c>
       <c r="Q5">
-        <v>0.614199976</v>
+        <v>0.598309728</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1000617393229507</v>
+        <v>0.100516649947724</v>
       </c>
       <c r="T5">
-        <v>1.0576622967266</v>
+        <v>1.066529351528131</v>
       </c>
       <c r="U5">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V5">
         <v>0.2</v>
       </c>
       <c r="W5">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y5">
-        <v>6.792789121014891</v>
+        <v>5.002465406027692</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1984,22 +1984,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09826558394981501</v>
+        <v>0.0983840807563678</v>
       </c>
       <c r="C6">
-        <v>32.86976763790079</v>
+        <v>32.46474773219438</v>
       </c>
       <c r="D6">
-        <v>28.54256763790079</v>
+        <v>28.47824773219438</v>
       </c>
       <c r="E6">
-        <v>0.1928000000000001</v>
+        <v>0.5335000000000001</v>
       </c>
       <c r="F6">
-        <v>1.3628</v>
+        <v>1.7035</v>
       </c>
       <c r="G6">
         <v>5.69</v>
@@ -2020,45 +2020,45 @@
         <v>0.377</v>
       </c>
       <c r="M6">
-        <v>0.07536284</v>
+        <v>0.10442455</v>
       </c>
       <c r="N6">
-        <v>0.30163716</v>
+        <v>0.27257545</v>
       </c>
       <c r="O6">
-        <v>0.06032743200000001</v>
+        <v>0.05451509</v>
       </c>
       <c r="P6">
-        <v>0.241309728</v>
+        <v>0.21806036</v>
       </c>
       <c r="Q6">
-        <v>0.598309728</v>
+        <v>0.5750603599999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.100516649947724</v>
+        <v>0.1009811376382819</v>
       </c>
       <c r="T6">
-        <v>1.066529351528131</v>
+        <v>1.075583081167589</v>
       </c>
       <c r="U6">
-        <v>0.0553</v>
+        <v>0.0613</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.04424</v>
+        <v>0.04904</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y6">
-        <v>5.002465406027692</v>
+        <v>3.610262146209871</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2066,22 +2066,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0983840807563678</v>
+        <v>0.09881937756292059</v>
       </c>
       <c r="C7">
-        <v>32.46474773219438</v>
+        <v>31.89023717341647</v>
       </c>
       <c r="D7">
-        <v>28.47824773219438</v>
+        <v>28.24443717341647</v>
       </c>
       <c r="E7">
-        <v>0.5335000000000001</v>
+        <v>0.8742000000000001</v>
       </c>
       <c r="F7">
-        <v>1.7035</v>
+        <v>2.0442</v>
       </c>
       <c r="G7">
         <v>5.69</v>
@@ -2102,45 +2102,45 @@
         <v>0.377</v>
       </c>
       <c r="M7">
-        <v>0.10442455</v>
+        <v>0.14697798</v>
       </c>
       <c r="N7">
-        <v>0.27257545</v>
+        <v>0.23002202</v>
       </c>
       <c r="O7">
-        <v>0.05451509</v>
+        <v>0.046004404</v>
       </c>
       <c r="P7">
-        <v>0.21806036</v>
+        <v>0.184017616</v>
       </c>
       <c r="Q7">
-        <v>0.5750603599999999</v>
+        <v>0.541017616</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1009811376382819</v>
+        <v>0.1014555080456602</v>
       </c>
       <c r="T7">
-        <v>1.075583081167589</v>
+        <v>1.084829443352567</v>
       </c>
       <c r="U7">
-        <v>0.0613</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.04904</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>3.610262146209871</v>
+        <v>2.565010078380448</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2148,22 +2148,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09881937756292059</v>
+        <v>0.09904907436947338</v>
       </c>
       <c r="C8">
-        <v>31.89023717341647</v>
+        <v>31.4277011208947</v>
       </c>
       <c r="D8">
-        <v>28.24443717341647</v>
+        <v>28.1226011208947</v>
       </c>
       <c r="E8">
-        <v>0.8742000000000001</v>
+        <v>1.2149</v>
       </c>
       <c r="F8">
-        <v>2.0442</v>
+        <v>2.3849</v>
       </c>
       <c r="G8">
         <v>5.69</v>
@@ -2184,45 +2184,45 @@
         <v>0.377</v>
       </c>
       <c r="M8">
-        <v>0.14697798</v>
+        <v>0.18077542</v>
       </c>
       <c r="N8">
-        <v>0.23002202</v>
+        <v>0.19622458</v>
       </c>
       <c r="O8">
-        <v>0.046004404</v>
+        <v>0.039244916</v>
       </c>
       <c r="P8">
-        <v>0.184017616</v>
+        <v>0.156979664</v>
       </c>
       <c r="Q8">
-        <v>0.541017616</v>
+        <v>0.5139796640000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1014555080456602</v>
+        <v>0.1019400799671757</v>
       </c>
       <c r="T8">
-        <v>1.084829443352567</v>
+        <v>1.094274652036147</v>
       </c>
       <c r="U8">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y8">
-        <v>2.565010078380448</v>
+        <v>2.085460512275397</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2230,22 +2230,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0990490743694734</v>
+        <v>0.1000003711760262</v>
       </c>
       <c r="C9">
-        <v>31.42770112089469</v>
+        <v>30.59340781041016</v>
       </c>
       <c r="D9">
-        <v>28.12260112089469</v>
+        <v>27.62900781041016</v>
       </c>
       <c r="E9">
-        <v>1.214900000000001</v>
+        <v>1.5556</v>
       </c>
       <c r="F9">
-        <v>2.3849</v>
+        <v>2.7256</v>
       </c>
       <c r="G9">
         <v>5.69</v>
@@ -2266,45 +2266,45 @@
         <v>0.377</v>
       </c>
       <c r="M9">
-        <v>0.18077542</v>
+        <v>0.245304</v>
       </c>
       <c r="N9">
-        <v>0.19622458</v>
+        <v>0.131696</v>
       </c>
       <c r="O9">
-        <v>0.03924491599999999</v>
+        <v>0.0263392</v>
       </c>
       <c r="P9">
-        <v>0.156979664</v>
+        <v>0.1053568</v>
       </c>
       <c r="Q9">
-        <v>0.5139796639999999</v>
+        <v>0.4623568</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1019400799671757</v>
+        <v>0.102435186060898</v>
       </c>
       <c r="T9">
-        <v>1.094274652036147</v>
+        <v>1.103925191343283</v>
       </c>
       <c r="U9">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y9">
-        <v>2.085460512275396</v>
+        <v>1.536868538629619</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2312,22 +2312,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1000003711760262</v>
+        <v>0.1048302315999964</v>
       </c>
       <c r="C10">
-        <v>30.59340781041016</v>
+        <v>27.99209917378283</v>
       </c>
       <c r="D10">
-        <v>27.62900781041016</v>
+        <v>25.36839917378283</v>
       </c>
       <c r="E10">
-        <v>1.5556</v>
+        <v>1.8963</v>
       </c>
       <c r="F10">
-        <v>2.7256</v>
+        <v>3.0663</v>
       </c>
       <c r="G10">
         <v>5.69</v>
@@ -2348,45 +2348,45 @@
         <v>0.377</v>
       </c>
       <c r="M10">
-        <v>0.245304</v>
+        <v>0.45013284</v>
       </c>
       <c r="N10">
-        <v>0.131696</v>
+        <v>-0.07313284000000003</v>
       </c>
       <c r="O10">
-        <v>0.0263392</v>
+        <v>-0.01462656800000001</v>
       </c>
       <c r="P10">
-        <v>0.1053568</v>
+        <v>-0.05850627200000003</v>
       </c>
       <c r="Q10">
-        <v>0.4623568</v>
+        <v>0.298493728</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.102435186060898</v>
+        <v>0.1031113431820033</v>
       </c>
       <c r="T10">
-        <v>1.103925191343283</v>
+        <v>1.117104752164213</v>
       </c>
       <c r="U10">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V10">
-        <v>0.2</v>
+        <v>0.167506107752547</v>
       </c>
       <c r="W10">
-        <v>0.07199999999999999</v>
+        <v>0.1222101033819261</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y10">
-        <v>1.536868538629619</v>
+        <v>0.837530538762735</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2394,22 +2394,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1048302315999964</v>
+        <v>0.1114549069939753</v>
       </c>
       <c r="C11">
-        <v>27.99209917378283</v>
+        <v>25.0916908825714</v>
       </c>
       <c r="D11">
-        <v>25.36839917378283</v>
+        <v>22.8086908825714</v>
       </c>
       <c r="E11">
-        <v>1.8963</v>
+        <v>2.237</v>
       </c>
       <c r="F11">
-        <v>3.0663</v>
+        <v>3.407</v>
       </c>
       <c r="G11">
         <v>5.69</v>
@@ -2430,45 +2430,45 @@
         <v>0.377</v>
       </c>
       <c r="M11">
-        <v>0.45013284</v>
+        <v>0.6841255999999999</v>
       </c>
       <c r="N11">
-        <v>-0.07313284000000003</v>
+        <v>-0.3071255999999999</v>
       </c>
       <c r="O11">
-        <v>-0.01462656800000001</v>
+        <v>-0.06142511999999998</v>
       </c>
       <c r="P11">
-        <v>-0.05850627200000003</v>
+        <v>-0.2457004799999999</v>
       </c>
       <c r="Q11">
-        <v>0.298493728</v>
+        <v>0.1112995200000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1031113431820033</v>
+        <v>0.1039866640995577</v>
       </c>
       <c r="T11">
-        <v>1.117104752164213</v>
+        <v>1.134166386081315</v>
       </c>
       <c r="U11">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V11">
-        <v>0.167506107752547</v>
+        <v>0.1102136800610882</v>
       </c>
       <c r="W11">
-        <v>0.1222101033819261</v>
+        <v>0.1786690930437335</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y11">
-        <v>0.837530538762735</v>
+        <v>0.5510684003054411</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2476,22 +2476,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1114549069939753</v>
+        <v>0.1130049069939753</v>
       </c>
       <c r="C12">
-        <v>25.0916908825714</v>
+        <v>24.22493597900379</v>
       </c>
       <c r="D12">
-        <v>22.8086908825714</v>
+        <v>22.28263597900379</v>
       </c>
       <c r="E12">
-        <v>2.237</v>
+        <v>2.5777</v>
       </c>
       <c r="F12">
-        <v>3.407</v>
+        <v>3.7477</v>
       </c>
       <c r="G12">
         <v>5.69</v>
@@ -2512,37 +2512,37 @@
         <v>0.377</v>
       </c>
       <c r="M12">
-        <v>0.6841256</v>
+        <v>0.7525381600000001</v>
       </c>
       <c r="N12">
-        <v>-0.3071256</v>
+        <v>-0.3755381600000001</v>
       </c>
       <c r="O12">
-        <v>-0.06142512</v>
+        <v>-0.07510763200000002</v>
       </c>
       <c r="P12">
-        <v>-0.24570048</v>
+        <v>-0.300430528</v>
       </c>
       <c r="Q12">
-        <v>0.11129952</v>
+        <v>0.05656947199999995</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1039866640995577</v>
+        <v>0.1046404468422494</v>
       </c>
       <c r="T12">
-        <v>1.134166386081315</v>
+        <v>1.146909828621554</v>
       </c>
       <c r="U12">
         <v>0.2008</v>
       </c>
       <c r="V12">
-        <v>0.1102136800610882</v>
+        <v>0.1001942546009893</v>
       </c>
       <c r="W12">
-        <v>0.1786690930437335</v>
+        <v>0.1806809936761214</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.5510684003054409</v>
+        <v>0.5009712730049463</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2558,22 +2558,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1130049069939753</v>
+        <v>0.118841531108437</v>
       </c>
       <c r="C13">
-        <v>24.22493597900379</v>
+        <v>22.1036685605067</v>
       </c>
       <c r="D13">
-        <v>22.28263597900379</v>
+        <v>20.5020685605067</v>
       </c>
       <c r="E13">
-        <v>2.5777</v>
+        <v>2.9184</v>
       </c>
       <c r="F13">
-        <v>3.7477</v>
+        <v>4.0884</v>
       </c>
       <c r="G13">
         <v>5.69</v>
@@ -2594,45 +2594,45 @@
         <v>0.377</v>
       </c>
       <c r="M13">
-        <v>0.7525381600000001</v>
+        <v>0.9640447200000001</v>
       </c>
       <c r="N13">
-        <v>-0.3755381600000001</v>
+        <v>-0.5870447200000001</v>
       </c>
       <c r="O13">
-        <v>-0.07510763200000002</v>
+        <v>-0.117408944</v>
       </c>
       <c r="P13">
-        <v>-0.300430528</v>
+        <v>-0.4696357760000001</v>
       </c>
       <c r="Q13">
-        <v>0.05656947199999995</v>
+        <v>-0.1126357760000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1046404468422494</v>
+        <v>0.105407524777345</v>
       </c>
       <c r="T13">
-        <v>1.146909828621554</v>
+        <v>1.161861605337978</v>
       </c>
       <c r="U13">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.1001942546009893</v>
+        <v>0.07821213937046406</v>
       </c>
       <c r="W13">
-        <v>0.1806809936761214</v>
+        <v>0.2173575775364446</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y13">
-        <v>0.5009712730049463</v>
+        <v>0.3910606968523203</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2640,22 +2640,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.118841531108437</v>
+        <v>0.120741531108437</v>
       </c>
       <c r="C14">
-        <v>22.1036685605067</v>
+        <v>21.24317760229157</v>
       </c>
       <c r="D14">
-        <v>20.5020685605067</v>
+        <v>19.98227760229157</v>
       </c>
       <c r="E14">
-        <v>2.9184</v>
+        <v>3.2591</v>
       </c>
       <c r="F14">
-        <v>4.0884</v>
+        <v>4.4291</v>
       </c>
       <c r="G14">
         <v>5.69</v>
@@ -2676,37 +2676,37 @@
         <v>0.377</v>
       </c>
       <c r="M14">
-        <v>0.9640447200000001</v>
+        <v>1.04438178</v>
       </c>
       <c r="N14">
-        <v>-0.5870447200000001</v>
+        <v>-0.6673817800000001</v>
       </c>
       <c r="O14">
-        <v>-0.117408944</v>
+        <v>-0.133476356</v>
       </c>
       <c r="P14">
-        <v>-0.4696357760000001</v>
+        <v>-0.5339054240000001</v>
       </c>
       <c r="Q14">
-        <v>-0.1126357760000001</v>
+        <v>-0.1769054240000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.105407524777345</v>
+        <v>0.106092668740303</v>
       </c>
       <c r="T14">
-        <v>1.161861605337978</v>
+        <v>1.175216336433817</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.07821213937046406</v>
+        <v>0.07219582095735143</v>
       </c>
       <c r="W14">
-        <v>0.2173575775364446</v>
+        <v>0.2187762254182565</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.3910606968523203</v>
+        <v>0.3609791047867571</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2722,22 +2722,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.120741531108437</v>
+        <v>0.122641531108437</v>
       </c>
       <c r="C15">
-        <v>21.24317760229157</v>
+        <v>20.40839156708781</v>
       </c>
       <c r="D15">
-        <v>19.98227760229157</v>
+        <v>19.48819156708781</v>
       </c>
       <c r="E15">
-        <v>3.2591</v>
+        <v>3.599800000000001</v>
       </c>
       <c r="F15">
-        <v>4.4291</v>
+        <v>4.769800000000001</v>
       </c>
       <c r="G15">
         <v>5.69</v>
@@ -2758,37 +2758,37 @@
         <v>0.377</v>
       </c>
       <c r="M15">
-        <v>1.04438178</v>
+        <v>1.12471884</v>
       </c>
       <c r="N15">
-        <v>-0.6673817800000001</v>
+        <v>-0.7477188400000003</v>
       </c>
       <c r="O15">
-        <v>-0.133476356</v>
+        <v>-0.1495437680000001</v>
       </c>
       <c r="P15">
-        <v>-0.5339054240000001</v>
+        <v>-0.5981750720000003</v>
       </c>
       <c r="Q15">
-        <v>-0.1769054240000001</v>
+        <v>-0.2411750720000003</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.106092668740303</v>
+        <v>0.1067937462837949</v>
       </c>
       <c r="T15">
-        <v>1.175216336433817</v>
+        <v>1.18888164267142</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.07219582095735143</v>
+        <v>0.06703897660325489</v>
       </c>
       <c r="W15">
-        <v>0.2187762254182565</v>
+        <v>0.2199922093169525</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.3609791047867571</v>
+        <v>0.3351948830162744</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2804,22 +2804,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.122641531108437</v>
+        <v>0.124541531108437</v>
       </c>
       <c r="C16">
-        <v>20.40839156708781</v>
+        <v>19.59744970797949</v>
       </c>
       <c r="D16">
-        <v>19.48819156708781</v>
+        <v>19.01794970797949</v>
       </c>
       <c r="E16">
-        <v>3.599800000000001</v>
+        <v>3.940500000000001</v>
       </c>
       <c r="F16">
-        <v>4.769800000000001</v>
+        <v>5.110500000000001</v>
       </c>
       <c r="G16">
         <v>5.69</v>
@@ -2840,37 +2840,37 @@
         <v>0.377</v>
       </c>
       <c r="M16">
-        <v>1.12471884</v>
+        <v>1.2050559</v>
       </c>
       <c r="N16">
-        <v>-0.7477188400000003</v>
+        <v>-0.8280559000000003</v>
       </c>
       <c r="O16">
-        <v>-0.1495437680000001</v>
+        <v>-0.1656111800000001</v>
       </c>
       <c r="P16">
-        <v>-0.5981750720000003</v>
+        <v>-0.6624447200000002</v>
       </c>
       <c r="Q16">
-        <v>-0.2411750720000003</v>
+        <v>-0.3054447200000002</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1067937462837949</v>
+        <v>0.1075113197694866</v>
       </c>
       <c r="T16">
-        <v>1.18888164267142</v>
+        <v>1.202868485526378</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.06703897660325489</v>
+        <v>0.06256971149637124</v>
       </c>
       <c r="W16">
-        <v>0.2199922093169525</v>
+        <v>0.2210460620291557</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.3351948830162744</v>
+        <v>0.3128485574818561</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2886,22 +2886,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.124541531108437</v>
+        <v>0.1264415311084369</v>
       </c>
       <c r="C17">
-        <v>19.5974497079795</v>
+        <v>18.80866664273397</v>
       </c>
       <c r="D17">
-        <v>19.0179497079795</v>
+        <v>18.56986664273397</v>
       </c>
       <c r="E17">
-        <v>3.9405</v>
+        <v>4.2812</v>
       </c>
       <c r="F17">
-        <v>5.1105</v>
+        <v>5.4512</v>
       </c>
       <c r="G17">
         <v>5.69</v>
@@ -2922,37 +2922,37 @@
         <v>0.377</v>
       </c>
       <c r="M17">
-        <v>1.2050559</v>
+        <v>1.28539296</v>
       </c>
       <c r="N17">
-        <v>-0.8280559000000001</v>
+        <v>-0.90839296</v>
       </c>
       <c r="O17">
-        <v>-0.16561118</v>
+        <v>-0.181678592</v>
       </c>
       <c r="P17">
-        <v>-0.6624447200000001</v>
+        <v>-0.726714368</v>
       </c>
       <c r="Q17">
-        <v>-0.3054447200000001</v>
+        <v>-0.369714368</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1075113197694866</v>
+        <v>0.108245978338171</v>
       </c>
       <c r="T17">
-        <v>1.202868485526378</v>
+        <v>1.217188348449311</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.06256971149637124</v>
+        <v>0.05865910452784804</v>
       </c>
       <c r="W17">
-        <v>0.2210460620291557</v>
+        <v>0.2219681831523334</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.3128485574818562</v>
+        <v>0.2932955226392402</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2968,22 +2968,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1264415311084369</v>
+        <v>0.128341531108437</v>
       </c>
       <c r="C18">
-        <v>18.80866664273397</v>
+        <v>18.0405121704533</v>
       </c>
       <c r="D18">
-        <v>18.56986664273397</v>
+        <v>18.1424121704533</v>
       </c>
       <c r="E18">
-        <v>4.2812</v>
+        <v>4.6219</v>
       </c>
       <c r="F18">
-        <v>5.4512</v>
+        <v>5.7919</v>
       </c>
       <c r="G18">
         <v>5.69</v>
@@ -3004,37 +3004,37 @@
         <v>0.377</v>
       </c>
       <c r="M18">
-        <v>1.28539296</v>
+        <v>1.36573002</v>
       </c>
       <c r="N18">
-        <v>-0.90839296</v>
+        <v>-0.98873002</v>
       </c>
       <c r="O18">
-        <v>-0.181678592</v>
+        <v>-0.197746004</v>
       </c>
       <c r="P18">
-        <v>-0.726714368</v>
+        <v>-0.790984016</v>
       </c>
       <c r="Q18">
-        <v>-0.369714368</v>
+        <v>-0.433984016</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.108245978338171</v>
+        <v>0.1089983395229682</v>
       </c>
       <c r="T18">
-        <v>1.217188348449311</v>
+        <v>1.231853268310146</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.05865910452784804</v>
+        <v>0.0552085689673864</v>
       </c>
       <c r="W18">
-        <v>0.2219681831523334</v>
+        <v>0.2227818194374903</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.2932955226392402</v>
+        <v>0.276042844836932</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3050,22 +3050,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.128341531108437</v>
+        <v>0.1302415311084369</v>
       </c>
       <c r="C19">
-        <v>18.0405121704533</v>
+        <v>17.29159381307186</v>
       </c>
       <c r="D19">
-        <v>18.1424121704533</v>
+        <v>17.73419381307185</v>
       </c>
       <c r="E19">
-        <v>4.6219</v>
+        <v>4.962600000000001</v>
       </c>
       <c r="F19">
-        <v>5.7919</v>
+        <v>6.132600000000001</v>
       </c>
       <c r="G19">
         <v>5.69</v>
@@ -3086,37 +3086,37 @@
         <v>0.377</v>
       </c>
       <c r="M19">
-        <v>1.36573002</v>
+        <v>1.44606708</v>
       </c>
       <c r="N19">
-        <v>-0.98873002</v>
+        <v>-1.06906708</v>
       </c>
       <c r="O19">
-        <v>-0.197746004</v>
+        <v>-0.213813416</v>
       </c>
       <c r="P19">
-        <v>-0.790984016</v>
+        <v>-0.8552536640000001</v>
       </c>
       <c r="Q19">
-        <v>-0.433984016</v>
+        <v>-0.4982536640000002</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1089983395229682</v>
+        <v>0.1097690509805654</v>
       </c>
       <c r="T19">
-        <v>1.231853268310146</v>
+        <v>1.246875869143196</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.0552085689673864</v>
+        <v>0.05214142624697603</v>
       </c>
       <c r="W19">
-        <v>0.2227818194374903</v>
+        <v>0.223505051690963</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.276042844836932</v>
+        <v>0.2607071312348802</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3132,22 +3132,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.130241531108437</v>
+        <v>0.132141531108437</v>
       </c>
       <c r="C20">
-        <v>17.29159381307185</v>
+        <v>16.56064166196604</v>
       </c>
       <c r="D20">
-        <v>17.73419381307185</v>
+        <v>17.34394166196604</v>
       </c>
       <c r="E20">
-        <v>4.9626</v>
+        <v>5.3033</v>
       </c>
       <c r="F20">
-        <v>6.1326</v>
+        <v>6.4733</v>
       </c>
       <c r="G20">
         <v>5.69</v>
@@ -3168,37 +3168,37 @@
         <v>0.377</v>
       </c>
       <c r="M20">
-        <v>1.44606708</v>
+        <v>1.52640414</v>
       </c>
       <c r="N20">
-        <v>-1.06906708</v>
+        <v>-1.14940414</v>
       </c>
       <c r="O20">
-        <v>-0.213813416</v>
+        <v>-0.229880828</v>
       </c>
       <c r="P20">
-        <v>-0.8552536640000001</v>
+        <v>-0.9195233120000001</v>
       </c>
       <c r="Q20">
-        <v>-0.4982536640000002</v>
+        <v>-0.5625233120000002</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1097690509805654</v>
+        <v>0.1105587923506959</v>
       </c>
       <c r="T20">
-        <v>1.246875869143196</v>
+        <v>1.262269398391878</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.05214142624697603</v>
+        <v>0.04939714065502993</v>
       </c>
       <c r="W20">
-        <v>0.223505051690963</v>
+        <v>0.2241521542335439</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.2607071312348802</v>
+        <v>0.2469857032751497</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3214,22 +3214,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.132141531108437</v>
+        <v>0.134041531108437</v>
       </c>
       <c r="C21">
-        <v>16.56064166196604</v>
+        <v>15.84649518224392</v>
       </c>
       <c r="D21">
-        <v>17.34394166196604</v>
+        <v>16.97049518224392</v>
       </c>
       <c r="E21">
-        <v>5.3033</v>
+        <v>5.644</v>
       </c>
       <c r="F21">
-        <v>6.4733</v>
+        <v>6.814</v>
       </c>
       <c r="G21">
         <v>5.69</v>
@@ -3250,37 +3250,37 @@
         <v>0.377</v>
       </c>
       <c r="M21">
-        <v>1.52640414</v>
+        <v>1.6067412</v>
       </c>
       <c r="N21">
-        <v>-1.14940414</v>
+        <v>-1.2297412</v>
       </c>
       <c r="O21">
-        <v>-0.229880828</v>
+        <v>-0.24594824</v>
       </c>
       <c r="P21">
-        <v>-0.9195233120000001</v>
+        <v>-0.98379296</v>
       </c>
       <c r="Q21">
-        <v>-0.5625233120000002</v>
+        <v>-0.6267929600000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1105587923506959</v>
+        <v>0.1113682772550795</v>
       </c>
       <c r="T21">
-        <v>1.262269398391878</v>
+        <v>1.278047765871776</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.04939714065502993</v>
+        <v>0.04692728362227844</v>
       </c>
       <c r="W21">
-        <v>0.2241521542335439</v>
+        <v>0.2247345465218668</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.2469857032751497</v>
+        <v>0.2346364181113921</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3296,22 +3296,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.134041531108437</v>
+        <v>0.135941531108437</v>
       </c>
       <c r="C22">
-        <v>15.84649518224392</v>
+        <v>15.14809168586693</v>
       </c>
       <c r="D22">
-        <v>16.97049518224392</v>
+        <v>16.61279168586693</v>
       </c>
       <c r="E22">
-        <v>5.644</v>
+        <v>5.984700000000001</v>
       </c>
       <c r="F22">
-        <v>6.814</v>
+        <v>7.154700000000001</v>
       </c>
       <c r="G22">
         <v>5.69</v>
@@ -3332,37 +3332,37 @@
         <v>0.377</v>
       </c>
       <c r="M22">
-        <v>1.6067412</v>
+        <v>1.68707826</v>
       </c>
       <c r="N22">
-        <v>-1.2297412</v>
+        <v>-1.31007826</v>
       </c>
       <c r="O22">
-        <v>-0.24594824</v>
+        <v>-0.262015652</v>
       </c>
       <c r="P22">
-        <v>-0.98379296</v>
+        <v>-1.048062608</v>
       </c>
       <c r="Q22">
-        <v>-0.6267929600000001</v>
+        <v>-0.6910626080000002</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1113682772550795</v>
+        <v>0.1121982554481818</v>
       </c>
       <c r="T22">
-        <v>1.278047765871776</v>
+        <v>1.294225585692938</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.04692728362227844</v>
+        <v>0.0446926510688366</v>
       </c>
       <c r="W22">
-        <v>0.2247345465218668</v>
+        <v>0.2252614728779684</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.2346364181113921</v>
+        <v>0.223463255344183</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3378,22 +3378,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.135941531108437</v>
+        <v>0.137841531108437</v>
       </c>
       <c r="C23">
-        <v>15.14809168586693</v>
+        <v>14.46445623245775</v>
       </c>
       <c r="D23">
-        <v>16.61279168586693</v>
+        <v>16.26985623245775</v>
       </c>
       <c r="E23">
-        <v>5.9847</v>
+        <v>6.3254</v>
       </c>
       <c r="F23">
-        <v>7.1547</v>
+        <v>7.4954</v>
       </c>
       <c r="G23">
         <v>5.69</v>
@@ -3414,37 +3414,37 @@
         <v>0.377</v>
       </c>
       <c r="M23">
-        <v>1.68707826</v>
+        <v>1.76741532</v>
       </c>
       <c r="N23">
-        <v>-1.31007826</v>
+        <v>-1.39041532</v>
       </c>
       <c r="O23">
-        <v>-0.262015652</v>
+        <v>-0.278083064</v>
       </c>
       <c r="P23">
-        <v>-1.048062608</v>
+        <v>-1.112332256</v>
       </c>
       <c r="Q23">
-        <v>-0.691062608</v>
+        <v>-0.755332256</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1121982554481818</v>
+        <v>0.1130495151334149</v>
       </c>
       <c r="T23">
-        <v>1.294225585692938</v>
+        <v>1.31081822140695</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.0446926510688366</v>
+        <v>0.04266116692934403</v>
       </c>
       <c r="W23">
-        <v>0.2252614728779684</v>
+        <v>0.2257404968380607</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.223463255344183</v>
+        <v>0.2133058346467201</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3460,22 +3460,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.137841531108437</v>
+        <v>0.139741531108437</v>
       </c>
       <c r="C24">
-        <v>14.46445623245775</v>
+        <v>13.79469275566614</v>
       </c>
       <c r="D24">
-        <v>16.26985623245775</v>
+        <v>15.94079275566614</v>
       </c>
       <c r="E24">
-        <v>6.3254</v>
+        <v>6.6661</v>
       </c>
       <c r="F24">
-        <v>7.4954</v>
+        <v>7.8361</v>
       </c>
       <c r="G24">
         <v>5.69</v>
@@ -3496,37 +3496,37 @@
         <v>0.377</v>
       </c>
       <c r="M24">
-        <v>1.76741532</v>
+        <v>1.84775238</v>
       </c>
       <c r="N24">
-        <v>-1.39041532</v>
+        <v>-1.47075238</v>
       </c>
       <c r="O24">
-        <v>-0.278083064</v>
+        <v>-0.294150476</v>
       </c>
       <c r="P24">
-        <v>-1.112332256</v>
+        <v>-1.176601904</v>
       </c>
       <c r="Q24">
-        <v>-0.755332256</v>
+        <v>-0.8196019040000002</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1130495151334149</v>
+        <v>0.1139228854598229</v>
       </c>
       <c r="T24">
-        <v>1.31081822140695</v>
+        <v>1.327841834671975</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.04266116692934403</v>
+        <v>0.04080633358458994</v>
       </c>
       <c r="W24">
-        <v>0.2257404968380607</v>
+        <v>0.2261778665407537</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.2133058346467201</v>
+        <v>0.2040316679229497</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3542,22 +3542,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.139741531108437</v>
+        <v>0.141641531108437</v>
       </c>
       <c r="C25">
-        <v>13.79469275566614</v>
+        <v>13.1379762450211</v>
       </c>
       <c r="D25">
-        <v>15.94079275566614</v>
+        <v>15.6247762450211</v>
       </c>
       <c r="E25">
-        <v>6.6661</v>
+        <v>7.0068</v>
       </c>
       <c r="F25">
-        <v>7.8361</v>
+        <v>8.1768</v>
       </c>
       <c r="G25">
         <v>5.69</v>
@@ -3578,37 +3578,37 @@
         <v>0.377</v>
       </c>
       <c r="M25">
-        <v>1.84775238</v>
+        <v>1.92808944</v>
       </c>
       <c r="N25">
-        <v>-1.47075238</v>
+        <v>-1.55108944</v>
       </c>
       <c r="O25">
-        <v>-0.294150476</v>
+        <v>-0.3102178880000001</v>
       </c>
       <c r="P25">
-        <v>-1.176601904</v>
+        <v>-1.240871552</v>
       </c>
       <c r="Q25">
-        <v>-0.8196019040000002</v>
+        <v>-0.8838715520000002</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1139228854598229</v>
+        <v>0.1148192392158732</v>
       </c>
       <c r="T25">
-        <v>1.327841834671975</v>
+        <v>1.345313437759765</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.04080633358458994</v>
+        <v>0.03910606968523203</v>
       </c>
       <c r="W25">
-        <v>0.2261778665407537</v>
+        <v>0.2265787887682223</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.2040316679229497</v>
+        <v>0.1955303484261601</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3624,22 +3624,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.141641531108437</v>
+        <v>0.143541531108437</v>
       </c>
       <c r="C26">
-        <v>13.1379762450211</v>
+        <v>12.49354583964609</v>
       </c>
       <c r="D26">
-        <v>15.6247762450211</v>
+        <v>15.32104583964609</v>
       </c>
       <c r="E26">
-        <v>7.0068</v>
+        <v>7.3475</v>
       </c>
       <c r="F26">
-        <v>8.1768</v>
+        <v>8.5175</v>
       </c>
       <c r="G26">
         <v>5.69</v>
@@ -3660,37 +3660,37 @@
         <v>0.377</v>
       </c>
       <c r="M26">
-        <v>1.92808944</v>
+        <v>2.0084265</v>
       </c>
       <c r="N26">
-        <v>-1.55108944</v>
+        <v>-1.6314265</v>
       </c>
       <c r="O26">
-        <v>-0.3102178880000001</v>
+        <v>-0.3262853000000001</v>
       </c>
       <c r="P26">
-        <v>-1.240871552</v>
+        <v>-1.3051412</v>
       </c>
       <c r="Q26">
-        <v>-0.8838715520000002</v>
+        <v>-0.9481412</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1148192392158732</v>
+        <v>0.1157394957387515</v>
       </c>
       <c r="T26">
-        <v>1.345313437759764</v>
+        <v>1.363250950263228</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.03910606968523203</v>
+        <v>0.03754182689782275</v>
       </c>
       <c r="W26">
-        <v>0.2265787887682223</v>
+        <v>0.2269476372174934</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.1955303484261601</v>
+        <v>0.1877091344891137</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3706,22 +3706,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.143541531108437</v>
+        <v>0.145441531108437</v>
       </c>
       <c r="C27">
-        <v>12.49354583964609</v>
+        <v>11.86069871212305</v>
       </c>
       <c r="D27">
-        <v>15.32104583964609</v>
+        <v>15.02889871212305</v>
       </c>
       <c r="E27">
-        <v>7.3475</v>
+        <v>7.6882</v>
       </c>
       <c r="F27">
-        <v>8.5175</v>
+        <v>8.8582</v>
       </c>
       <c r="G27">
         <v>5.69</v>
@@ -3742,37 +3742,37 @@
         <v>0.377</v>
       </c>
       <c r="M27">
-        <v>2.0084265</v>
+        <v>2.08876356</v>
       </c>
       <c r="N27">
-        <v>-1.6314265</v>
+        <v>-1.71176356</v>
       </c>
       <c r="O27">
-        <v>-0.3262853000000001</v>
+        <v>-0.3423527120000001</v>
       </c>
       <c r="P27">
-        <v>-1.3051412</v>
+        <v>-1.369410848</v>
       </c>
       <c r="Q27">
-        <v>-0.9481412</v>
+        <v>-1.012410848</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1157394957387515</v>
+        <v>0.1166846240595454</v>
       </c>
       <c r="T27">
-        <v>1.363250950263228</v>
+        <v>1.38167326040192</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.03754182689782275</v>
+        <v>0.03609791047867571</v>
       </c>
       <c r="W27">
-        <v>0.2269476372174934</v>
+        <v>0.2272881127091283</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.1877091344891137</v>
+        <v>0.1804895523933786</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3788,22 +3788,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.145441531108437</v>
+        <v>0.147341531108437</v>
       </c>
       <c r="C28">
-        <v>11.86069871212305</v>
+        <v>11.23878463901103</v>
       </c>
       <c r="D28">
-        <v>15.02889871212305</v>
+        <v>14.74768463901103</v>
       </c>
       <c r="E28">
-        <v>7.6882</v>
+        <v>8.0289</v>
       </c>
       <c r="F28">
-        <v>8.8582</v>
+        <v>9.1989</v>
       </c>
       <c r="G28">
         <v>5.69</v>
@@ -3824,37 +3824,37 @@
         <v>0.377</v>
       </c>
       <c r="M28">
-        <v>2.08876356</v>
+        <v>2.16910062</v>
       </c>
       <c r="N28">
-        <v>-1.71176356</v>
+        <v>-1.79210062</v>
       </c>
       <c r="O28">
-        <v>-0.3423527120000001</v>
+        <v>-0.358420124</v>
       </c>
       <c r="P28">
-        <v>-1.369410848</v>
+        <v>-1.433680496</v>
       </c>
       <c r="Q28">
-        <v>-1.012410848</v>
+        <v>-1.076680496</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1166846240595454</v>
+        <v>0.1176556463069365</v>
       </c>
       <c r="T28">
-        <v>1.38167326040192</v>
+        <v>1.40060029136633</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.03609791047867571</v>
+        <v>0.03476095083131736</v>
       </c>
       <c r="W28">
-        <v>0.2272881127091283</v>
+        <v>0.2276033677939754</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.1804895523933786</v>
+        <v>0.1738047541565868</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3870,22 +3870,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.147341531108437</v>
+        <v>0.149241531108437</v>
       </c>
       <c r="C29">
-        <v>11.23878463901103</v>
+        <v>10.62720116973265</v>
       </c>
       <c r="D29">
-        <v>14.74768463901103</v>
+        <v>14.47680116973265</v>
       </c>
       <c r="E29">
-        <v>8.0289</v>
+        <v>8.369600000000002</v>
       </c>
       <c r="F29">
-        <v>9.1989</v>
+        <v>9.539600000000002</v>
       </c>
       <c r="G29">
         <v>5.69</v>
@@ -3906,37 +3906,37 @@
         <v>0.377</v>
       </c>
       <c r="M29">
-        <v>2.16910062</v>
+        <v>2.249437680000001</v>
       </c>
       <c r="N29">
-        <v>-1.79210062</v>
+        <v>-1.872437680000001</v>
       </c>
       <c r="O29">
-        <v>-0.358420124</v>
+        <v>-0.3744875360000002</v>
       </c>
       <c r="P29">
-        <v>-1.433680496</v>
+        <v>-1.497950144</v>
       </c>
       <c r="Q29">
-        <v>-1.076680496</v>
+        <v>-1.140950144</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1176556463069365</v>
+        <v>0.1186536413945328</v>
       </c>
       <c r="T29">
-        <v>1.40060029136633</v>
+        <v>1.420053073190863</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.03476095083131736</v>
+        <v>0.03351948830162745</v>
       </c>
       <c r="W29">
-        <v>0.2276033677939754</v>
+        <v>0.2278961046584763</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.1738047541565868</v>
+        <v>0.1675974415081373</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3952,22 +3952,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.149241531108437</v>
+        <v>0.151141531108437</v>
       </c>
       <c r="C30">
-        <v>10.62720116973265</v>
+        <v>10.02538931828085</v>
       </c>
       <c r="D30">
-        <v>14.47680116973265</v>
+        <v>14.21568931828085</v>
       </c>
       <c r="E30">
-        <v>8.369600000000002</v>
+        <v>8.710300000000002</v>
       </c>
       <c r="F30">
-        <v>9.539600000000002</v>
+        <v>9.880300000000002</v>
       </c>
       <c r="G30">
         <v>5.69</v>
@@ -3988,37 +3988,37 @@
         <v>0.377</v>
       </c>
       <c r="M30">
-        <v>2.249437680000001</v>
+        <v>2.32977474</v>
       </c>
       <c r="N30">
-        <v>-1.872437680000001</v>
+        <v>-1.95277474</v>
       </c>
       <c r="O30">
-        <v>-0.3744875360000002</v>
+        <v>-0.3905549480000001</v>
       </c>
       <c r="P30">
-        <v>-1.497950144</v>
+        <v>-1.562219792</v>
       </c>
       <c r="Q30">
-        <v>-1.140950144</v>
+        <v>-1.205219792</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1186536413945328</v>
+        <v>0.1196797490198079</v>
       </c>
       <c r="T30">
-        <v>1.420053073190863</v>
+        <v>1.440053820700593</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.03351948830162745</v>
+        <v>0.03236364387743339</v>
       </c>
       <c r="W30">
-        <v>0.2278961046584763</v>
+        <v>0.2281686527737012</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.1675974415081373</v>
+        <v>0.161818219387167</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4034,22 +4034,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1511415311084369</v>
+        <v>0.1530415311084369</v>
       </c>
       <c r="C31">
-        <v>10.02538931828085</v>
+        <v>9.432829712906301</v>
       </c>
       <c r="D31">
-        <v>14.21568931828085</v>
+        <v>13.9638297129063</v>
       </c>
       <c r="E31">
-        <v>8.7103</v>
+        <v>9.051</v>
       </c>
       <c r="F31">
-        <v>9.8803</v>
+        <v>10.221</v>
       </c>
       <c r="G31">
         <v>5.69</v>
@@ -4070,37 +4070,37 @@
         <v>0.377</v>
       </c>
       <c r="M31">
-        <v>2.32977474</v>
+        <v>2.4101118</v>
       </c>
       <c r="N31">
-        <v>-1.95277474</v>
+        <v>-2.0331118</v>
       </c>
       <c r="O31">
-        <v>-0.390554948</v>
+        <v>-0.4066223600000001</v>
       </c>
       <c r="P31">
-        <v>-1.562219792</v>
+        <v>-1.62648944</v>
       </c>
       <c r="Q31">
-        <v>-1.205219792</v>
+        <v>-1.26948944</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1196797490198079</v>
+        <v>0.1207351740058052</v>
       </c>
       <c r="T31">
-        <v>1.440053820700593</v>
+        <v>1.460626018139173</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.03236364387743341</v>
+        <v>0.03128485574818562</v>
       </c>
       <c r="W31">
-        <v>0.2281686527737012</v>
+        <v>0.2284230310145778</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.161818219387167</v>
+        <v>0.156424278740928</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4116,22 +4116,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1530415311084369</v>
+        <v>0.1549415311084369</v>
       </c>
       <c r="C32">
-        <v>9.432829712906301</v>
+        <v>8.849039147975867</v>
       </c>
       <c r="D32">
-        <v>13.9638297129063</v>
+        <v>13.72073914797587</v>
       </c>
       <c r="E32">
-        <v>9.051</v>
+        <v>9.3917</v>
       </c>
       <c r="F32">
-        <v>10.221</v>
+        <v>10.5617</v>
       </c>
       <c r="G32">
         <v>5.69</v>
@@ -4152,37 +4152,37 @@
         <v>0.377</v>
       </c>
       <c r="M32">
-        <v>2.4101118</v>
+        <v>2.49044886</v>
       </c>
       <c r="N32">
-        <v>-2.0331118</v>
+        <v>-2.11344886</v>
       </c>
       <c r="O32">
-        <v>-0.4066223600000001</v>
+        <v>-0.422689772</v>
       </c>
       <c r="P32">
-        <v>-1.62648944</v>
+        <v>-1.690759088</v>
       </c>
       <c r="Q32">
-        <v>-1.26948944</v>
+        <v>-1.333759088</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1207351740058052</v>
+        <v>0.1218211910203821</v>
       </c>
       <c r="T32">
-        <v>1.460626018139173</v>
+        <v>1.481794511155683</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.03128485574818562</v>
+        <v>0.03027566685308286</v>
       </c>
       <c r="W32">
-        <v>0.2284230310145778</v>
+        <v>0.2286609977560431</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.156424278740928</v>
+        <v>0.1513783342654144</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4198,22 +4198,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1549415311084369</v>
+        <v>0.156841531108437</v>
       </c>
       <c r="C33">
-        <v>8.849039147975867</v>
+        <v>8.273567489832068</v>
       </c>
       <c r="D33">
-        <v>13.72073914797587</v>
+        <v>13.48596748983207</v>
       </c>
       <c r="E33">
-        <v>9.3917</v>
+        <v>9.7324</v>
       </c>
       <c r="F33">
-        <v>10.5617</v>
+        <v>10.9024</v>
       </c>
       <c r="G33">
         <v>5.69</v>
@@ -4234,37 +4234,37 @@
         <v>0.377</v>
       </c>
       <c r="M33">
-        <v>2.49044886</v>
+        <v>2.57078592</v>
       </c>
       <c r="N33">
-        <v>-2.11344886</v>
+        <v>-2.19378592</v>
       </c>
       <c r="O33">
-        <v>-0.422689772</v>
+        <v>-0.438757184</v>
       </c>
       <c r="P33">
-        <v>-1.690759088</v>
+        <v>-1.755028736</v>
       </c>
       <c r="Q33">
-        <v>-1.333759088</v>
+        <v>-1.398028736</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1218211910203821</v>
+        <v>0.1229391497118583</v>
       </c>
       <c r="T33">
-        <v>1.481794511155683</v>
+        <v>1.503585606907972</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.03027566685308286</v>
+        <v>0.02932955226392402</v>
       </c>
       <c r="W33">
-        <v>0.2286609977560431</v>
+        <v>0.2288840915761667</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.1513783342654144</v>
+        <v>0.1466477613196202</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4280,22 +4280,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.156841531108437</v>
+        <v>0.158741531108437</v>
       </c>
       <c r="C34">
-        <v>8.273567489832068</v>
+        <v>7.705994894966326</v>
       </c>
       <c r="D34">
-        <v>13.48596748983207</v>
+        <v>13.25909489496632</v>
       </c>
       <c r="E34">
-        <v>9.7324</v>
+        <v>10.0731</v>
       </c>
       <c r="F34">
-        <v>10.9024</v>
+        <v>11.2431</v>
       </c>
       <c r="G34">
         <v>5.69</v>
@@ -4316,37 +4316,37 @@
         <v>0.377</v>
       </c>
       <c r="M34">
-        <v>2.57078592</v>
+        <v>2.65112298</v>
       </c>
       <c r="N34">
-        <v>-2.19378592</v>
+        <v>-2.27412298</v>
       </c>
       <c r="O34">
-        <v>-0.438757184</v>
+        <v>-0.4548245960000001</v>
       </c>
       <c r="P34">
-        <v>-1.755028736</v>
+        <v>-1.819298384</v>
       </c>
       <c r="Q34">
-        <v>-1.398028736</v>
+        <v>-1.462298384</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1229391497118583</v>
+        <v>0.1240904803045726</v>
       </c>
       <c r="T34">
-        <v>1.503585606907972</v>
+        <v>1.526027183130479</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.02932955226392402</v>
+        <v>0.02844077795289602</v>
       </c>
       <c r="W34">
-        <v>0.2288840915761667</v>
+        <v>0.2290936645587071</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.1466477613196202</v>
+        <v>0.1422038897644801</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4362,22 +4362,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.158741531108437</v>
+        <v>0.160641531108437</v>
       </c>
       <c r="C35">
-        <v>7.705994894966326</v>
+        <v>7.145929304336498</v>
       </c>
       <c r="D35">
-        <v>13.25909489496632</v>
+        <v>13.0397293043365</v>
       </c>
       <c r="E35">
-        <v>10.0731</v>
+        <v>10.4138</v>
       </c>
       <c r="F35">
-        <v>11.2431</v>
+        <v>11.5838</v>
       </c>
       <c r="G35">
         <v>5.69</v>
@@ -4398,37 +4398,37 @@
         <v>0.377</v>
       </c>
       <c r="M35">
-        <v>2.65112298</v>
+        <v>2.73146004</v>
       </c>
       <c r="N35">
-        <v>-2.27412298</v>
+        <v>-2.35446004</v>
       </c>
       <c r="O35">
-        <v>-0.4548245960000001</v>
+        <v>-0.4708920080000001</v>
       </c>
       <c r="P35">
-        <v>-1.819298384</v>
+        <v>-1.883568032</v>
       </c>
       <c r="Q35">
-        <v>-1.462298384</v>
+        <v>-1.526568032</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1240904803045726</v>
+        <v>0.1252766997031267</v>
       </c>
       <c r="T35">
-        <v>1.526027183130479</v>
+        <v>1.549148807117305</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.02844077795289602</v>
+        <v>0.0276042844836932</v>
       </c>
       <c r="W35">
-        <v>0.2290936645587071</v>
+        <v>0.2292909097187451</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.1422038897644801</v>
+        <v>0.1380214224184659</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4444,22 +4444,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.160641531108437</v>
+        <v>0.162541531108437</v>
       </c>
       <c r="C36">
-        <v>7.145929304336498</v>
+        <v>6.593004182368322</v>
       </c>
       <c r="D36">
-        <v>13.0397293043365</v>
+        <v>12.82750418236832</v>
       </c>
       <c r="E36">
-        <v>10.4138</v>
+        <v>10.7545</v>
       </c>
       <c r="F36">
-        <v>11.5838</v>
+        <v>11.9245</v>
       </c>
       <c r="G36">
         <v>5.69</v>
@@ -4480,37 +4480,37 @@
         <v>0.377</v>
       </c>
       <c r="M36">
-        <v>2.73146004</v>
+        <v>2.811797100000001</v>
       </c>
       <c r="N36">
-        <v>-2.35446004</v>
+        <v>-2.434797100000001</v>
       </c>
       <c r="O36">
-        <v>-0.4708920080000001</v>
+        <v>-0.4869594200000002</v>
       </c>
       <c r="P36">
-        <v>-1.883568032</v>
+        <v>-1.947837680000001</v>
       </c>
       <c r="Q36">
-        <v>-1.526568032</v>
+        <v>-1.590837680000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1252766997031267</v>
+        <v>0.1264994181600979</v>
       </c>
       <c r="T36">
-        <v>1.549148807117305</v>
+        <v>1.57298186568834</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.0276042844836932</v>
+        <v>0.02681559064130196</v>
       </c>
       <c r="W36">
-        <v>0.2292909097187451</v>
+        <v>0.229476883726781</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1380214224184659</v>
+        <v>0.1340779532065097</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4526,22 +4526,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.162541531108437</v>
+        <v>0.164441531108437</v>
       </c>
       <c r="C37">
-        <v>6.593004182368322</v>
+        <v>6.046876473211201</v>
       </c>
       <c r="D37">
-        <v>12.82750418236832</v>
+        <v>12.6220764732112</v>
       </c>
       <c r="E37">
-        <v>10.7545</v>
+        <v>11.0952</v>
       </c>
       <c r="F37">
-        <v>11.9245</v>
+        <v>12.2652</v>
       </c>
       <c r="G37">
         <v>5.69</v>
@@ -4562,37 +4562,37 @@
         <v>0.377</v>
       </c>
       <c r="M37">
-        <v>2.811797100000001</v>
+        <v>2.89213416</v>
       </c>
       <c r="N37">
-        <v>-2.434797100000001</v>
+        <v>-2.515134160000001</v>
       </c>
       <c r="O37">
-        <v>-0.4869594200000002</v>
+        <v>-0.5030268320000001</v>
       </c>
       <c r="P37">
-        <v>-1.947837680000001</v>
+        <v>-2.012107328</v>
       </c>
       <c r="Q37">
-        <v>-1.590837680000001</v>
+        <v>-1.655107328</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1264994181600979</v>
+        <v>0.1277603465688494</v>
       </c>
       <c r="T37">
-        <v>1.57298186568834</v>
+        <v>1.597559707339721</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.02681559064130196</v>
+        <v>0.02607071312348802</v>
       </c>
       <c r="W37">
-        <v>0.229476883726781</v>
+        <v>0.2296525258454815</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1340779532065097</v>
+        <v>0.13035356561744</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4608,22 +4608,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.164441531108437</v>
+        <v>0.166341531108437</v>
       </c>
       <c r="C38">
-        <v>6.046876473211203</v>
+        <v>5.507224750277407</v>
       </c>
       <c r="D38">
-        <v>12.6220764732112</v>
+        <v>12.42312475027741</v>
       </c>
       <c r="E38">
-        <v>11.0952</v>
+        <v>11.4359</v>
       </c>
       <c r="F38">
-        <v>12.2652</v>
+        <v>12.6059</v>
       </c>
       <c r="G38">
         <v>5.69</v>
@@ -4644,37 +4644,37 @@
         <v>0.377</v>
       </c>
       <c r="M38">
-        <v>2.89213416</v>
+        <v>2.97247122</v>
       </c>
       <c r="N38">
-        <v>-2.515134160000001</v>
+        <v>-2.59547122</v>
       </c>
       <c r="O38">
-        <v>-0.5030268320000001</v>
+        <v>-0.519094244</v>
       </c>
       <c r="P38">
-        <v>-2.012107328</v>
+        <v>-2.076376976</v>
       </c>
       <c r="Q38">
-        <v>-1.655107328</v>
+        <v>-1.719376976</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1277603465688494</v>
+        <v>0.1290613044508946</v>
       </c>
       <c r="T38">
-        <v>1.59755970733972</v>
+        <v>1.622917797932414</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.02607071312348802</v>
+        <v>0.02536609925528564</v>
       </c>
       <c r="W38">
-        <v>0.2296525258454815</v>
+        <v>0.2298186737956036</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.13035356561744</v>
+        <v>0.1268304962764282</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4690,22 +4690,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.166341531108437</v>
+        <v>0.168241531108437</v>
       </c>
       <c r="C39">
-        <v>5.507224750277407</v>
+        <v>4.973747538069702</v>
       </c>
       <c r="D39">
-        <v>12.42312475027741</v>
+        <v>12.2303475380697</v>
       </c>
       <c r="E39">
-        <v>11.4359</v>
+        <v>11.7766</v>
       </c>
       <c r="F39">
-        <v>12.6059</v>
+        <v>12.9466</v>
       </c>
       <c r="G39">
         <v>5.69</v>
@@ -4726,37 +4726,37 @@
         <v>0.377</v>
       </c>
       <c r="M39">
-        <v>2.97247122</v>
+        <v>3.05280828</v>
       </c>
       <c r="N39">
-        <v>-2.59547122</v>
+        <v>-2.67580828</v>
       </c>
       <c r="O39">
-        <v>-0.519094244</v>
+        <v>-0.535161656</v>
       </c>
       <c r="P39">
-        <v>-2.076376976</v>
+        <v>-2.140646624</v>
       </c>
       <c r="Q39">
-        <v>-1.719376976</v>
+        <v>-1.783646624</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1290613044508946</v>
+        <v>0.1304042287162316</v>
       </c>
       <c r="T39">
-        <v>1.622917797932414</v>
+        <v>1.649093891447453</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.02536609925528564</v>
+        <v>0.02469857032751496</v>
       </c>
       <c r="W39">
-        <v>0.2298186737956036</v>
+        <v>0.229976077116772</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1268304962764282</v>
+        <v>0.1234928516375748</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4772,22 +4772,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.168241531108437</v>
+        <v>0.170141531108437</v>
       </c>
       <c r="C40">
-        <v>4.973747538069702</v>
+        <v>4.446161787868776</v>
       </c>
       <c r="D40">
-        <v>12.2303475380697</v>
+        <v>12.04346178786878</v>
       </c>
       <c r="E40">
-        <v>11.7766</v>
+        <v>12.1173</v>
       </c>
       <c r="F40">
-        <v>12.9466</v>
+        <v>13.2873</v>
       </c>
       <c r="G40">
         <v>5.69</v>
@@ -4808,37 +4808,37 @@
         <v>0.377</v>
       </c>
       <c r="M40">
-        <v>3.05280828</v>
+        <v>3.13314534</v>
       </c>
       <c r="N40">
-        <v>-2.67580828</v>
+        <v>-2.75614534</v>
       </c>
       <c r="O40">
-        <v>-0.535161656</v>
+        <v>-0.5512290679999999</v>
       </c>
       <c r="P40">
-        <v>-2.140646624</v>
+        <v>-2.204916272</v>
       </c>
       <c r="Q40">
-        <v>-1.783646624</v>
+        <v>-1.847916272</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1304042287162316</v>
+        <v>0.1317911832853502</v>
       </c>
       <c r="T40">
-        <v>1.649093891447453</v>
+        <v>1.676128217536756</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.02469857032751496</v>
+        <v>0.02406527365245048</v>
       </c>
       <c r="W40">
-        <v>0.229976077116772</v>
+        <v>0.2301254084727522</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1234928516375748</v>
+        <v>0.1203263682622525</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4854,22 +4854,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.170141531108437</v>
+        <v>0.172041531108437</v>
       </c>
       <c r="C41">
-        <v>4.446161787868776</v>
+        <v>3.924201491070761</v>
       </c>
       <c r="D41">
-        <v>12.04346178786878</v>
+        <v>11.86220149107076</v>
       </c>
       <c r="E41">
-        <v>12.1173</v>
+        <v>12.458</v>
       </c>
       <c r="F41">
-        <v>13.2873</v>
+        <v>13.628</v>
       </c>
       <c r="G41">
         <v>5.69</v>
@@ -4890,37 +4890,37 @@
         <v>0.377</v>
       </c>
       <c r="M41">
-        <v>3.13314534</v>
+        <v>3.2134824</v>
       </c>
       <c r="N41">
-        <v>-2.75614534</v>
+        <v>-2.8364824</v>
       </c>
       <c r="O41">
-        <v>-0.5512290679999999</v>
+        <v>-0.5672964800000001</v>
       </c>
       <c r="P41">
-        <v>-2.204916272</v>
+        <v>-2.26918592</v>
       </c>
       <c r="Q41">
-        <v>-1.847916272</v>
+        <v>-1.91218592</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1317911832853502</v>
+        <v>0.1332243696734394</v>
       </c>
       <c r="T41">
-        <v>1.676128217536756</v>
+        <v>1.704063687829035</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.02406527365245048</v>
+        <v>0.02346364181113922</v>
       </c>
       <c r="W41">
-        <v>0.2301254084727522</v>
+        <v>0.2302672732609334</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1203263682622525</v>
+        <v>0.117318209055696</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4936,22 +4936,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.172041531108437</v>
+        <v>0.173941531108437</v>
       </c>
       <c r="C42">
-        <v>3.924201491070761</v>
+        <v>3.407616415888054</v>
       </c>
       <c r="D42">
-        <v>11.86220149107076</v>
+        <v>11.68631641588806</v>
       </c>
       <c r="E42">
-        <v>12.458</v>
+        <v>12.7987</v>
       </c>
       <c r="F42">
-        <v>13.628</v>
+        <v>13.9687</v>
       </c>
       <c r="G42">
         <v>5.69</v>
@@ -4972,37 +4972,37 @@
         <v>0.377</v>
       </c>
       <c r="M42">
-        <v>3.2134824</v>
+        <v>3.29381946</v>
       </c>
       <c r="N42">
-        <v>-2.8364824</v>
+        <v>-2.91681946</v>
       </c>
       <c r="O42">
-        <v>-0.5672964800000001</v>
+        <v>-0.5833638920000001</v>
       </c>
       <c r="P42">
-        <v>-2.26918592</v>
+        <v>-2.333455568</v>
       </c>
       <c r="Q42">
-        <v>-1.91218592</v>
+        <v>-1.976455568</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1332243696734394</v>
+        <v>0.1347061386509553</v>
       </c>
       <c r="T42">
-        <v>1.704063687829035</v>
+        <v>1.732946123215968</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.02346364181113922</v>
+        <v>0.02289135786452606</v>
       </c>
       <c r="W42">
-        <v>0.2302672732609334</v>
+        <v>0.2304022178155448</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.117318209055696</v>
+        <v>0.1144567893226304</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5018,22 +5018,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.173941531108437</v>
+        <v>0.175841531108437</v>
       </c>
       <c r="C43">
-        <v>3.407616415888054</v>
+        <v>2.896170954796306</v>
       </c>
       <c r="D43">
-        <v>11.68631641588806</v>
+        <v>11.51557095479631</v>
       </c>
       <c r="E43">
-        <v>12.7987</v>
+        <v>13.1394</v>
       </c>
       <c r="F43">
-        <v>13.9687</v>
+        <v>14.3094</v>
       </c>
       <c r="G43">
         <v>5.69</v>
@@ -5054,37 +5054,37 @@
         <v>0.377</v>
       </c>
       <c r="M43">
-        <v>3.29381946</v>
+        <v>3.374156520000001</v>
       </c>
       <c r="N43">
-        <v>-2.91681946</v>
+        <v>-2.997156520000001</v>
       </c>
       <c r="O43">
-        <v>-0.5833638920000001</v>
+        <v>-0.5994313040000002</v>
       </c>
       <c r="P43">
-        <v>-2.333455568</v>
+        <v>-2.397725216</v>
       </c>
       <c r="Q43">
-        <v>-1.976455568</v>
+        <v>-2.040725216</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1347061386509553</v>
+        <v>0.1362390031104545</v>
       </c>
       <c r="T43">
-        <v>1.732946123215968</v>
+        <v>1.762824504650726</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.02289135786452606</v>
+        <v>0.0223463255344183</v>
       </c>
       <c r="W43">
-        <v>0.2304022178155448</v>
+        <v>0.2305307364389842</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1144567893226304</v>
+        <v>0.1117316276720914</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5100,22 +5100,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.175841531108437</v>
+        <v>0.177741531108437</v>
       </c>
       <c r="C44">
-        <v>2.896170954796307</v>
+        <v>2.389643071564214</v>
       </c>
       <c r="D44">
-        <v>11.51557095479631</v>
+        <v>11.34974307156421</v>
       </c>
       <c r="E44">
-        <v>13.1394</v>
+        <v>13.4801</v>
       </c>
       <c r="F44">
-        <v>14.3094</v>
+        <v>14.6501</v>
       </c>
       <c r="G44">
         <v>5.69</v>
@@ -5136,37 +5136,37 @@
         <v>0.377</v>
       </c>
       <c r="M44">
-        <v>3.37415652</v>
+        <v>3.45449358</v>
       </c>
       <c r="N44">
-        <v>-2.99715652</v>
+        <v>-3.077493580000001</v>
       </c>
       <c r="O44">
-        <v>-0.599431304</v>
+        <v>-0.6154987160000002</v>
       </c>
       <c r="P44">
-        <v>-2.397725216</v>
+        <v>-2.461994864</v>
       </c>
       <c r="Q44">
-        <v>-2.040725216</v>
+        <v>-2.104994864</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1362390031104545</v>
+        <v>0.1378256522878309</v>
       </c>
       <c r="T44">
-        <v>1.762824504650726</v>
+        <v>1.793751250346353</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.0223463255344183</v>
+        <v>0.02182664354524579</v>
       </c>
       <c r="W44">
-        <v>0.2305307364389842</v>
+        <v>0.2306532774520311</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1117316276720915</v>
+        <v>0.1091332177262289</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5182,22 +5182,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.177741531108437</v>
+        <v>0.179641531108437</v>
       </c>
       <c r="C45">
-        <v>2.389643071564214</v>
+        <v>1.88782333797046</v>
       </c>
       <c r="D45">
-        <v>11.34974307156421</v>
+        <v>11.18862333797046</v>
       </c>
       <c r="E45">
-        <v>13.4801</v>
+        <v>13.8208</v>
       </c>
       <c r="F45">
-        <v>14.6501</v>
+        <v>14.9908</v>
       </c>
       <c r="G45">
         <v>5.69</v>
@@ -5218,37 +5218,37 @@
         <v>0.377</v>
       </c>
       <c r="M45">
-        <v>3.45449358</v>
+        <v>3.53483064</v>
       </c>
       <c r="N45">
-        <v>-3.077493580000001</v>
+        <v>-3.15783064</v>
       </c>
       <c r="O45">
-        <v>-0.6154987160000002</v>
+        <v>-0.6315661280000001</v>
       </c>
       <c r="P45">
-        <v>-2.461994864</v>
+        <v>-2.526264512</v>
       </c>
       <c r="Q45">
-        <v>-2.104994864</v>
+        <v>-2.169264512</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1378256522878309</v>
+        <v>0.1394689675072565</v>
       </c>
       <c r="T45">
-        <v>1.793751250346353</v>
+        <v>1.825782522673966</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.02182664354524579</v>
+        <v>0.02133058346467202</v>
       </c>
       <c r="W45">
-        <v>0.2306532774520311</v>
+        <v>0.2307702484190303</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1091332177262289</v>
+        <v>0.10665291732336</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5264,22 +5264,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.179641531108437</v>
+        <v>0.181541531108437</v>
       </c>
       <c r="C46">
-        <v>1.88782333797046</v>
+        <v>1.390514051420114</v>
       </c>
       <c r="D46">
-        <v>11.18862333797046</v>
+        <v>11.03201405142011</v>
       </c>
       <c r="E46">
-        <v>13.8208</v>
+        <v>14.1615</v>
       </c>
       <c r="F46">
-        <v>14.9908</v>
+        <v>15.3315</v>
       </c>
       <c r="G46">
         <v>5.69</v>
@@ -5300,37 +5300,37 @@
         <v>0.377</v>
       </c>
       <c r="M46">
-        <v>3.53483064</v>
+        <v>3.6151677</v>
       </c>
       <c r="N46">
-        <v>-3.15783064</v>
+        <v>-3.2381677</v>
       </c>
       <c r="O46">
-        <v>-0.6315661280000001</v>
+        <v>-0.6476335400000001</v>
       </c>
       <c r="P46">
-        <v>-2.526264512</v>
+        <v>-2.59053416</v>
       </c>
       <c r="Q46">
-        <v>-2.169264512</v>
+        <v>-2.23353416</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1394689675072565</v>
+        <v>0.1411720396437521</v>
       </c>
       <c r="T46">
-        <v>1.825782522673966</v>
+        <v>1.858978568540766</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.02133058346467202</v>
+        <v>0.02085657049879042</v>
       </c>
       <c r="W46">
-        <v>0.2307702484190303</v>
+        <v>0.2308820206763852</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.10665291732336</v>
+        <v>0.1042828524939521</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5346,22 +5346,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.181541531108437</v>
+        <v>0.183441531108437</v>
       </c>
       <c r="C47">
-        <v>1.390514051420114</v>
+        <v>0.897528425643511</v>
       </c>
       <c r="D47">
-        <v>11.03201405142011</v>
+        <v>10.87972842564351</v>
       </c>
       <c r="E47">
-        <v>14.1615</v>
+        <v>14.5022</v>
       </c>
       <c r="F47">
-        <v>15.3315</v>
+        <v>15.6722</v>
       </c>
       <c r="G47">
         <v>5.69</v>
@@ -5382,37 +5382,37 @@
         <v>0.377</v>
       </c>
       <c r="M47">
-        <v>3.6151677</v>
+        <v>3.69550476</v>
       </c>
       <c r="N47">
-        <v>-3.2381677</v>
+        <v>-3.318504760000001</v>
       </c>
       <c r="O47">
-        <v>-0.6476335400000001</v>
+        <v>-0.6637009520000001</v>
       </c>
       <c r="P47">
-        <v>-2.59053416</v>
+        <v>-2.654803808</v>
       </c>
       <c r="Q47">
-        <v>-2.23353416</v>
+        <v>-2.297803808</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1411720396437521</v>
+        <v>0.1429381885260437</v>
       </c>
       <c r="T47">
-        <v>1.858978568540766</v>
+        <v>1.893404097587817</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.02085657049879042</v>
+        <v>0.02040316679229497</v>
       </c>
       <c r="W47">
-        <v>0.2308820206763852</v>
+        <v>0.2309889332703769</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1042828524939521</v>
+        <v>0.1020158339614748</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5428,22 +5428,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.183441531108437</v>
+        <v>0.185341531108437</v>
       </c>
       <c r="C48">
-        <v>0.897528425643511</v>
+        <v>0.4086898475118197</v>
       </c>
       <c r="D48">
-        <v>10.87972842564351</v>
+        <v>10.73158984751182</v>
       </c>
       <c r="E48">
-        <v>14.5022</v>
+        <v>14.8429</v>
       </c>
       <c r="F48">
-        <v>15.6722</v>
+        <v>16.0129</v>
       </c>
       <c r="G48">
         <v>5.69</v>
@@ -5464,37 +5464,37 @@
         <v>0.377</v>
       </c>
       <c r="M48">
-        <v>3.69550476</v>
+        <v>3.775841820000001</v>
       </c>
       <c r="N48">
-        <v>-3.318504760000001</v>
+        <v>-3.39884182</v>
       </c>
       <c r="O48">
-        <v>-0.6637009520000001</v>
+        <v>-0.6797683640000001</v>
       </c>
       <c r="P48">
-        <v>-2.654803808</v>
+        <v>-2.719073456</v>
       </c>
       <c r="Q48">
-        <v>-2.297803808</v>
+        <v>-2.362073456</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1429381885260437</v>
+        <v>0.1447709845359691</v>
       </c>
       <c r="T48">
-        <v>1.893404097587817</v>
+        <v>1.929128703202681</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.02040316679229497</v>
+        <v>0.01996905686054401</v>
       </c>
       <c r="W48">
-        <v>0.2309889332703769</v>
+        <v>0.2310912963922837</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1020158339614748</v>
+        <v>0.09984528430272011</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5510,22 +5510,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.185341531108437</v>
+        <v>0.187241531108437</v>
       </c>
       <c r="C49">
-        <v>0.4086898475118197</v>
+        <v>-0.07616880624766509</v>
       </c>
       <c r="D49">
-        <v>10.73158984751182</v>
+        <v>10.58743119375233</v>
       </c>
       <c r="E49">
-        <v>14.8429</v>
+        <v>15.1836</v>
       </c>
       <c r="F49">
-        <v>16.0129</v>
+        <v>16.3536</v>
       </c>
       <c r="G49">
         <v>5.69</v>
@@ -5546,37 +5546,37 @@
         <v>0.377</v>
       </c>
       <c r="M49">
-        <v>3.775841820000001</v>
+        <v>3.85617888</v>
       </c>
       <c r="N49">
-        <v>-3.39884182</v>
+        <v>-3.47917888</v>
       </c>
       <c r="O49">
-        <v>-0.6797683640000001</v>
+        <v>-0.695835776</v>
       </c>
       <c r="P49">
-        <v>-2.719073456</v>
+        <v>-2.783343104</v>
       </c>
       <c r="Q49">
-        <v>-2.362073456</v>
+        <v>-2.426343104</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1447709845359691</v>
+        <v>0.1466742727001223</v>
       </c>
       <c r="T49">
-        <v>1.929128703202681</v>
+        <v>1.966227332110425</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.01996905686054401</v>
+        <v>0.01955303484261602</v>
       </c>
       <c r="W49">
-        <v>0.2310912963922837</v>
+        <v>0.2311893943841112</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.09984528430272011</v>
+        <v>0.09776517421308017</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5592,22 +5592,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.187241531108437</v>
+        <v>0.189141531108437</v>
       </c>
       <c r="C50">
-        <v>-0.07616880624766154</v>
+        <v>-0.5572057979943956</v>
       </c>
       <c r="D50">
-        <v>10.58743119375234</v>
+        <v>10.4470942020056</v>
       </c>
       <c r="E50">
-        <v>15.1836</v>
+        <v>15.5243</v>
       </c>
       <c r="F50">
-        <v>16.3536</v>
+        <v>16.6943</v>
       </c>
       <c r="G50">
         <v>5.69</v>
@@ -5628,37 +5628,37 @@
         <v>0.377</v>
       </c>
       <c r="M50">
-        <v>3.85617888</v>
+        <v>3.93651594</v>
       </c>
       <c r="N50">
-        <v>-3.47917888</v>
+        <v>-3.55951594</v>
       </c>
       <c r="O50">
-        <v>-0.695835776</v>
+        <v>-0.711903188</v>
       </c>
       <c r="P50">
-        <v>-2.783343104</v>
+        <v>-2.847612752</v>
       </c>
       <c r="Q50">
-        <v>-2.426343104</v>
+        <v>-2.490612752</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1466742727001223</v>
+        <v>0.148652199615811</v>
       </c>
       <c r="T50">
-        <v>1.966227332110425</v>
+        <v>2.004780809210629</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.01955303484261602</v>
+        <v>0.01915399331521569</v>
       </c>
       <c r="W50">
-        <v>0.2311893943841112</v>
+        <v>0.2312834883762721</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.09776517421308017</v>
+        <v>0.09576996657607839</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5674,22 +5674,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.189141531108437</v>
+        <v>0.191041531108437</v>
       </c>
       <c r="C51">
-        <v>-0.5572057979943956</v>
+        <v>-1.03457110875177</v>
       </c>
       <c r="D51">
-        <v>10.4470942020056</v>
+        <v>10.31042889124823</v>
       </c>
       <c r="E51">
-        <v>15.5243</v>
+        <v>15.865</v>
       </c>
       <c r="F51">
-        <v>16.6943</v>
+        <v>17.035</v>
       </c>
       <c r="G51">
         <v>5.69</v>
@@ -5710,37 +5710,37 @@
         <v>0.377</v>
       </c>
       <c r="M51">
-        <v>3.93651594</v>
+        <v>4.016853</v>
       </c>
       <c r="N51">
-        <v>-3.55951594</v>
+        <v>-3.639853</v>
       </c>
       <c r="O51">
-        <v>-0.711903188</v>
+        <v>-0.7279706000000001</v>
       </c>
       <c r="P51">
-        <v>-2.847612752</v>
+        <v>-2.911882400000001</v>
       </c>
       <c r="Q51">
-        <v>-2.490612752</v>
+        <v>-2.5548824</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.148652199615811</v>
+        <v>0.1507092436081272</v>
       </c>
       <c r="T51">
-        <v>2.004780809210629</v>
+        <v>2.044876425394842</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.01915399331521569</v>
+        <v>0.01877091344891137</v>
       </c>
       <c r="W51">
-        <v>0.2312834883762721</v>
+        <v>0.2313738186087467</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.09576996657607839</v>
+        <v>0.09385456724455676</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5756,22 +5756,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.191041531108437</v>
+        <v>0.192941531108437</v>
       </c>
       <c r="C52">
-        <v>-1.03457110875177</v>
+        <v>-1.508406972880678</v>
       </c>
       <c r="D52">
-        <v>10.31042889124823</v>
+        <v>10.17729302711932</v>
       </c>
       <c r="E52">
-        <v>15.865</v>
+        <v>16.2057</v>
       </c>
       <c r="F52">
-        <v>17.035</v>
+        <v>17.3757</v>
       </c>
       <c r="G52">
         <v>5.69</v>
@@ -5792,37 +5792,37 @@
         <v>0.377</v>
       </c>
       <c r="M52">
-        <v>4.016853</v>
+        <v>4.097190060000001</v>
       </c>
       <c r="N52">
-        <v>-3.639853</v>
+        <v>-3.720190060000001</v>
       </c>
       <c r="O52">
-        <v>-0.7279706000000001</v>
+        <v>-0.7440380120000003</v>
       </c>
       <c r="P52">
-        <v>-2.911882400000001</v>
+        <v>-2.976152048000001</v>
       </c>
       <c r="Q52">
-        <v>-2.5548824</v>
+        <v>-2.619152048000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1507092436081272</v>
+        <v>0.1528502485797217</v>
       </c>
       <c r="T52">
-        <v>2.044876425394842</v>
+        <v>2.086608597341676</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.01877091344891137</v>
+        <v>0.01840285632246213</v>
       </c>
       <c r="W52">
-        <v>0.2313738186087467</v>
+        <v>0.2314606064791634</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.09385456724455676</v>
+        <v>0.09201428161231062</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5838,22 +5838,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.192941531108437</v>
+        <v>0.194841531108437</v>
       </c>
       <c r="C53">
-        <v>-1.508406972880678</v>
+        <v>-1.978848371856628</v>
       </c>
       <c r="D53">
-        <v>10.17729302711932</v>
+        <v>10.04755162814337</v>
       </c>
       <c r="E53">
-        <v>16.2057</v>
+        <v>16.5464</v>
       </c>
       <c r="F53">
-        <v>17.3757</v>
+        <v>17.7164</v>
       </c>
       <c r="G53">
         <v>5.69</v>
@@ -5874,37 +5874,37 @@
         <v>0.377</v>
       </c>
       <c r="M53">
-        <v>4.097190060000001</v>
+        <v>4.177527120000001</v>
       </c>
       <c r="N53">
-        <v>-3.720190060000001</v>
+        <v>-3.800527120000001</v>
       </c>
       <c r="O53">
-        <v>-0.7440380120000003</v>
+        <v>-0.7601054240000003</v>
       </c>
       <c r="P53">
-        <v>-2.976152048000001</v>
+        <v>-3.040421696000001</v>
       </c>
       <c r="Q53">
-        <v>-2.619152048000001</v>
+        <v>-2.683421696000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1528502485797217</v>
+        <v>0.1550804620917992</v>
       </c>
       <c r="T53">
-        <v>2.086608597341676</v>
+        <v>2.130079609786294</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.01840285632246213</v>
+        <v>0.01804895523933786</v>
       </c>
       <c r="W53">
-        <v>0.2314606064791634</v>
+        <v>0.2315440563545642</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.09201428161231062</v>
+        <v>0.09024477619668925</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5920,22 +5920,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.194841531108437</v>
+        <v>0.196741531108437</v>
       </c>
       <c r="C54">
-        <v>-1.978848371856628</v>
+        <v>-2.446023490753877</v>
       </c>
       <c r="D54">
-        <v>10.04755162814337</v>
+        <v>9.921076509246124</v>
       </c>
       <c r="E54">
-        <v>16.5464</v>
+        <v>16.8871</v>
       </c>
       <c r="F54">
-        <v>17.7164</v>
+        <v>18.0571</v>
       </c>
       <c r="G54">
         <v>5.69</v>
@@ -5956,37 +5956,37 @@
         <v>0.377</v>
       </c>
       <c r="M54">
-        <v>4.177527120000001</v>
+        <v>4.25786418</v>
       </c>
       <c r="N54">
-        <v>-3.800527120000001</v>
+        <v>-3.880864180000001</v>
       </c>
       <c r="O54">
-        <v>-0.7601054240000003</v>
+        <v>-0.7761728360000002</v>
       </c>
       <c r="P54">
-        <v>-3.040421696000001</v>
+        <v>-3.104691344</v>
       </c>
       <c r="Q54">
-        <v>-2.683421696000001</v>
+        <v>-2.747691344000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1550804620917992</v>
+        <v>0.1574055783065184</v>
       </c>
       <c r="T54">
-        <v>2.130079609786294</v>
+        <v>2.175400452547705</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.01804895523933786</v>
+        <v>0.01770840891406733</v>
       </c>
       <c r="W54">
-        <v>0.2315440563545642</v>
+        <v>0.2316243571780629</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.09024477619668925</v>
+        <v>0.08854204457033665</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6002,22 +6002,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.196741531108437</v>
+        <v>0.198641531108437</v>
       </c>
       <c r="C55">
-        <v>-2.446023490753877</v>
+        <v>-2.910054140681705</v>
       </c>
       <c r="D55">
-        <v>9.921076509246124</v>
+        <v>9.797745859318296</v>
       </c>
       <c r="E55">
-        <v>16.8871</v>
+        <v>17.2278</v>
       </c>
       <c r="F55">
-        <v>18.0571</v>
+        <v>18.3978</v>
       </c>
       <c r="G55">
         <v>5.69</v>
@@ -6038,37 +6038,37 @@
         <v>0.377</v>
       </c>
       <c r="M55">
-        <v>4.25786418</v>
+        <v>4.33820124</v>
       </c>
       <c r="N55">
-        <v>-3.880864180000001</v>
+        <v>-3.96120124</v>
       </c>
       <c r="O55">
-        <v>-0.7761728360000002</v>
+        <v>-0.7922402480000001</v>
       </c>
       <c r="P55">
-        <v>-3.104691344</v>
+        <v>-3.168960992</v>
       </c>
       <c r="Q55">
-        <v>-2.747691344000001</v>
+        <v>-2.811960992</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1574055783065184</v>
+        <v>0.1598317865305731</v>
       </c>
       <c r="T55">
-        <v>2.175400452547705</v>
+        <v>2.222691766733524</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.01770840891406733</v>
+        <v>0.01738047541565868</v>
       </c>
       <c r="W55">
-        <v>0.2316243571780629</v>
+        <v>0.2317016838969877</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.08854204457033665</v>
+        <v>0.08690237707829329</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6084,22 +6084,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.198641531108437</v>
+        <v>0.200541531108437</v>
       </c>
       <c r="C56">
-        <v>-2.910054140681705</v>
+        <v>-3.371056150099328</v>
       </c>
       <c r="D56">
-        <v>9.797745859318296</v>
+        <v>9.677443849900675</v>
       </c>
       <c r="E56">
-        <v>17.2278</v>
+        <v>17.5685</v>
       </c>
       <c r="F56">
-        <v>18.3978</v>
+        <v>18.7385</v>
       </c>
       <c r="G56">
         <v>5.69</v>
@@ -6120,37 +6120,37 @@
         <v>0.377</v>
       </c>
       <c r="M56">
-        <v>4.33820124</v>
+        <v>4.418538300000001</v>
       </c>
       <c r="N56">
-        <v>-3.96120124</v>
+        <v>-4.041538300000001</v>
       </c>
       <c r="O56">
-        <v>-0.7922402480000001</v>
+        <v>-0.8083076600000002</v>
       </c>
       <c r="P56">
-        <v>-3.168960992</v>
+        <v>-3.233230640000001</v>
       </c>
       <c r="Q56">
-        <v>-2.811960992</v>
+        <v>-2.876230640000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1598317865305731</v>
+        <v>0.1623658262312525</v>
       </c>
       <c r="T56">
-        <v>2.222691766733524</v>
+        <v>2.272084917105381</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.01738047541565868</v>
+        <v>0.01706446677173761</v>
       </c>
       <c r="W56">
-        <v>0.2317016838969877</v>
+        <v>0.2317761987352243</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.08690237707829329</v>
+        <v>0.08532233385868804</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6166,22 +6166,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.200541531108437</v>
+        <v>0.202441531108437</v>
       </c>
       <c r="C57">
-        <v>-3.371056150099328</v>
+        <v>-3.829139727651842</v>
       </c>
       <c r="D57">
-        <v>9.677443849900675</v>
+        <v>9.560060272348162</v>
       </c>
       <c r="E57">
-        <v>17.5685</v>
+        <v>17.90920000000001</v>
       </c>
       <c r="F57">
-        <v>18.7385</v>
+        <v>19.0792</v>
       </c>
       <c r="G57">
         <v>5.69</v>
@@ -6202,37 +6202,37 @@
         <v>0.377</v>
       </c>
       <c r="M57">
-        <v>4.418538300000001</v>
+        <v>4.498875360000001</v>
       </c>
       <c r="N57">
-        <v>-4.041538300000001</v>
+        <v>-4.121875360000002</v>
       </c>
       <c r="O57">
-        <v>-0.8083076600000002</v>
+        <v>-0.8243750720000004</v>
       </c>
       <c r="P57">
-        <v>-3.233230640000001</v>
+        <v>-3.297500288000001</v>
       </c>
       <c r="Q57">
-        <v>-2.876230640000001</v>
+        <v>-2.940500288000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1623658262312525</v>
+        <v>0.1650150495546901</v>
       </c>
       <c r="T57">
-        <v>2.272084917105381</v>
+        <v>2.323723210675957</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.01706446677173761</v>
+        <v>0.01675974415081372</v>
       </c>
       <c r="W57">
-        <v>0.2317761987352243</v>
+        <v>0.2318480523292381</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.08532233385868804</v>
+        <v>0.08379872075406858</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6248,22 +6248,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.202441531108437</v>
+        <v>0.204341531108437</v>
       </c>
       <c r="C58">
-        <v>-3.829139727651842</v>
+        <v>-4.284409798916247</v>
       </c>
       <c r="D58">
-        <v>9.560060272348162</v>
+        <v>9.445490201083755</v>
       </c>
       <c r="E58">
-        <v>17.90920000000001</v>
+        <v>18.2499</v>
       </c>
       <c r="F58">
-        <v>19.0792</v>
+        <v>19.4199</v>
       </c>
       <c r="G58">
         <v>5.69</v>
@@ -6284,37 +6284,37 @@
         <v>0.377</v>
       </c>
       <c r="M58">
-        <v>4.498875360000001</v>
+        <v>4.579212420000001</v>
       </c>
       <c r="N58">
-        <v>-4.121875360000002</v>
+        <v>-4.202212420000001</v>
       </c>
       <c r="O58">
-        <v>-0.8243750720000004</v>
+        <v>-0.8404424840000003</v>
       </c>
       <c r="P58">
-        <v>-3.297500288000001</v>
+        <v>-3.361769936000001</v>
       </c>
       <c r="Q58">
-        <v>-2.940500288000001</v>
+        <v>-3.004769936000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1650150495546901</v>
+        <v>0.1677874925675898</v>
       </c>
       <c r="T58">
-        <v>2.323723210675957</v>
+        <v>2.37776328534284</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.01675974415081372</v>
+        <v>0.01646571355167664</v>
       </c>
       <c r="W58">
-        <v>0.2318480523292381</v>
+        <v>0.2319173847445147</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.08379872075406858</v>
+        <v>0.08232856775838315</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6330,22 +6330,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.204341531108437</v>
+        <v>0.206241531108437</v>
       </c>
       <c r="C59">
-        <v>-4.284409798916247</v>
+        <v>-4.736966319220393</v>
       </c>
       <c r="D59">
-        <v>9.445490201083755</v>
+        <v>9.333633680779609</v>
       </c>
       <c r="E59">
-        <v>18.2499</v>
+        <v>18.5906</v>
       </c>
       <c r="F59">
-        <v>19.4199</v>
+        <v>19.7606</v>
       </c>
       <c r="G59">
         <v>5.69</v>
@@ -6366,37 +6366,37 @@
         <v>0.377</v>
       </c>
       <c r="M59">
-        <v>4.579212420000001</v>
+        <v>4.659549480000001</v>
       </c>
       <c r="N59">
-        <v>-4.202212420000001</v>
+        <v>-4.282549480000001</v>
       </c>
       <c r="O59">
-        <v>-0.8404424840000003</v>
+        <v>-0.8565098960000003</v>
       </c>
       <c r="P59">
-        <v>-3.361769936000001</v>
+        <v>-3.426039584000001</v>
       </c>
       <c r="Q59">
-        <v>-3.004769936000001</v>
+        <v>-3.069039584</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1677874925675898</v>
+        <v>0.170691956676342</v>
       </c>
       <c r="T59">
-        <v>2.37776328534284</v>
+        <v>2.434376696898622</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.01646571355167664</v>
+        <v>0.0161818219387167</v>
       </c>
       <c r="W59">
-        <v>0.2319173847445147</v>
+        <v>0.2319843263868506</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.08232856775838315</v>
+        <v>0.08090910969358345</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6412,22 +6412,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.206241531108437</v>
+        <v>0.208141531108437</v>
       </c>
       <c r="C60">
-        <v>-4.736966319220389</v>
+        <v>-5.186904564495009</v>
       </c>
       <c r="D60">
-        <v>9.333633680779611</v>
+        <v>9.22439543550499</v>
       </c>
       <c r="E60">
-        <v>18.5906</v>
+        <v>18.9313</v>
       </c>
       <c r="F60">
-        <v>19.7606</v>
+        <v>20.1013</v>
       </c>
       <c r="G60">
         <v>5.69</v>
@@ -6448,37 +6448,37 @@
         <v>0.377</v>
       </c>
       <c r="M60">
-        <v>4.65954948</v>
+        <v>4.73988654</v>
       </c>
       <c r="N60">
-        <v>-4.28254948</v>
+        <v>-4.36288654</v>
       </c>
       <c r="O60">
-        <v>-0.856509896</v>
+        <v>-0.872577308</v>
       </c>
       <c r="P60">
-        <v>-3.426039584</v>
+        <v>-3.490309232</v>
       </c>
       <c r="Q60">
-        <v>-3.069039584</v>
+        <v>-3.133309232</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1706919566763419</v>
+        <v>0.1737381019611308</v>
       </c>
       <c r="T60">
-        <v>2.434376696898621</v>
+        <v>2.493751738286393</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.0161818219387167</v>
+        <v>0.01590755377026388</v>
       </c>
       <c r="W60">
-        <v>0.2319843263868506</v>
+        <v>0.2320489988209718</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.08090910969358345</v>
+        <v>0.07953776885131936</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6494,22 +6494,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.208141531108437</v>
+        <v>0.210041531108437</v>
       </c>
       <c r="C61">
-        <v>-5.186904564495009</v>
+        <v>-5.634315401937755</v>
       </c>
       <c r="D61">
-        <v>9.22439543550499</v>
+        <v>9.117684598062246</v>
       </c>
       <c r="E61">
-        <v>18.9313</v>
+        <v>19.272</v>
       </c>
       <c r="F61">
-        <v>20.1013</v>
+        <v>20.442</v>
       </c>
       <c r="G61">
         <v>5.69</v>
@@ -6530,37 +6530,37 @@
         <v>0.377</v>
       </c>
       <c r="M61">
-        <v>4.73988654</v>
+        <v>4.8202236</v>
       </c>
       <c r="N61">
-        <v>-4.36288654</v>
+        <v>-4.4432236</v>
       </c>
       <c r="O61">
-        <v>-0.872577308</v>
+        <v>-0.8886447200000002</v>
       </c>
       <c r="P61">
-        <v>-3.490309232</v>
+        <v>-3.55457888</v>
       </c>
       <c r="Q61">
-        <v>-3.133309232</v>
+        <v>-3.19757888</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1737381019611308</v>
+        <v>0.176936554510159</v>
       </c>
       <c r="T61">
-        <v>2.493751738286393</v>
+        <v>2.556095531743552</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.01590755377026388</v>
+        <v>0.01564242787409281</v>
       </c>
       <c r="W61">
-        <v>0.2320489988209718</v>
+        <v>0.2321115155072889</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.07953776885131936</v>
+        <v>0.07821213937046401</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6576,22 +6576,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.210041531108437</v>
+        <v>0.211941531108437</v>
       </c>
       <c r="C62">
-        <v>-5.634315401937755</v>
+        <v>-6.079285542105243</v>
       </c>
       <c r="D62">
-        <v>9.117684598062246</v>
+        <v>9.013414457894754</v>
       </c>
       <c r="E62">
-        <v>19.272</v>
+        <v>19.6127</v>
       </c>
       <c r="F62">
-        <v>20.442</v>
+        <v>20.7827</v>
       </c>
       <c r="G62">
         <v>5.69</v>
@@ -6612,37 +6612,37 @@
         <v>0.377</v>
       </c>
       <c r="M62">
-        <v>4.8202236</v>
+        <v>4.90056066</v>
       </c>
       <c r="N62">
-        <v>-4.4432236</v>
+        <v>-4.52356066</v>
       </c>
       <c r="O62">
-        <v>-0.8886447200000002</v>
+        <v>-0.9047121320000001</v>
       </c>
       <c r="P62">
-        <v>-3.55457888</v>
+        <v>-3.618848528</v>
       </c>
       <c r="Q62">
-        <v>-3.19757888</v>
+        <v>-3.261848528</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.176936554510159</v>
+        <v>0.1802990302668298</v>
       </c>
       <c r="T62">
-        <v>2.556095531743552</v>
+        <v>2.6216364428139</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.01564242787409281</v>
+        <v>0.01538599463025523</v>
       </c>
       <c r="W62">
-        <v>0.2321115155072889</v>
+        <v>0.2321719824661858</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.07821213937046401</v>
+        <v>0.07692997315127603</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6658,22 +6658,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.211941531108437</v>
+        <v>0.213841531108437</v>
       </c>
       <c r="C63">
-        <v>-6.079285542105243</v>
+        <v>-6.521897773903163</v>
       </c>
       <c r="D63">
-        <v>9.013414457894754</v>
+        <v>8.911502226096838</v>
       </c>
       <c r="E63">
-        <v>19.6127</v>
+        <v>19.9534</v>
       </c>
       <c r="F63">
-        <v>20.7827</v>
+        <v>21.1234</v>
       </c>
       <c r="G63">
         <v>5.69</v>
@@ -6694,37 +6694,37 @@
         <v>0.377</v>
       </c>
       <c r="M63">
-        <v>4.90056066</v>
+        <v>4.980897720000001</v>
       </c>
       <c r="N63">
-        <v>-4.52356066</v>
+        <v>-4.603897720000001</v>
       </c>
       <c r="O63">
-        <v>-0.9047121320000001</v>
+        <v>-0.9207795440000002</v>
       </c>
       <c r="P63">
-        <v>-3.618848528</v>
+        <v>-3.683118176000001</v>
       </c>
       <c r="Q63">
-        <v>-3.261848528</v>
+        <v>-3.326118176</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1802990302668298</v>
+        <v>0.1838384784317464</v>
       </c>
       <c r="T63">
-        <v>2.6216364428139</v>
+        <v>2.690626875519529</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.01538599463025523</v>
+        <v>0.01513783342654143</v>
       </c>
       <c r="W63">
-        <v>0.2321719824661858</v>
+        <v>0.2322304988780216</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.07692997315127603</v>
+        <v>0.07568916713270712</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6740,22 +6740,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.213841531108437</v>
+        <v>0.215741531108437</v>
       </c>
       <c r="C64">
-        <v>-6.521897773903163</v>
+        <v>-6.962231183812719</v>
       </c>
       <c r="D64">
-        <v>8.911502226096838</v>
+        <v>8.811868816187282</v>
       </c>
       <c r="E64">
-        <v>19.9534</v>
+        <v>20.2941</v>
       </c>
       <c r="F64">
-        <v>21.1234</v>
+        <v>21.4641</v>
       </c>
       <c r="G64">
         <v>5.69</v>
@@ -6776,37 +6776,37 @@
         <v>0.377</v>
       </c>
       <c r="M64">
-        <v>4.980897720000001</v>
+        <v>5.06123478</v>
       </c>
       <c r="N64">
-        <v>-4.603897720000001</v>
+        <v>-4.684234780000001</v>
       </c>
       <c r="O64">
-        <v>-0.9207795440000002</v>
+        <v>-0.9368469560000001</v>
       </c>
       <c r="P64">
-        <v>-3.683118176000001</v>
+        <v>-3.747387824</v>
       </c>
       <c r="Q64">
-        <v>-3.326118176</v>
+        <v>-3.390387824</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1838384784317464</v>
+        <v>0.1875692481190909</v>
       </c>
       <c r="T64">
-        <v>2.690626875519529</v>
+        <v>2.76334652080384</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.01513783342654143</v>
+        <v>0.01489755035627887</v>
       </c>
       <c r="W64">
-        <v>0.2322304988780216</v>
+        <v>0.2322871576259895</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.07568916713270712</v>
+        <v>0.07448775178139433</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6822,22 +6822,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.215741531108437</v>
+        <v>0.217641531108437</v>
       </c>
       <c r="C65">
-        <v>-6.962231183812719</v>
+        <v>-7.400361360573601</v>
       </c>
       <c r="D65">
-        <v>8.811868816187282</v>
+        <v>8.714438639426399</v>
       </c>
       <c r="E65">
-        <v>20.2941</v>
+        <v>20.6348</v>
       </c>
       <c r="F65">
-        <v>21.4641</v>
+        <v>21.8048</v>
       </c>
       <c r="G65">
         <v>5.69</v>
@@ -6858,37 +6858,37 @@
         <v>0.377</v>
       </c>
       <c r="M65">
-        <v>5.06123478</v>
+        <v>5.14157184</v>
       </c>
       <c r="N65">
-        <v>-4.684234780000001</v>
+        <v>-4.76457184</v>
       </c>
       <c r="O65">
-        <v>-0.9368469560000001</v>
+        <v>-0.9529143680000001</v>
       </c>
       <c r="P65">
-        <v>-3.747387824</v>
+        <v>-3.811657472</v>
       </c>
       <c r="Q65">
-        <v>-3.390387824</v>
+        <v>-3.454657472</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1875692481190909</v>
+        <v>0.1915072827890656</v>
       </c>
       <c r="T65">
-        <v>2.76334652080384</v>
+        <v>2.840106146381725</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.01489755035627887</v>
+        <v>0.01466477613196201</v>
       </c>
       <c r="W65">
-        <v>0.2322871576259895</v>
+        <v>0.2323420457880834</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.07448775178139433</v>
+        <v>0.07332388065980999</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6904,22 +6904,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.217641531108437</v>
+        <v>0.219541531108437</v>
       </c>
       <c r="C66">
-        <v>-7.400361360573601</v>
+        <v>-7.83636058643674</v>
       </c>
       <c r="D66">
-        <v>8.714438639426399</v>
+        <v>8.619139413563262</v>
       </c>
       <c r="E66">
-        <v>20.6348</v>
+        <v>20.9755</v>
       </c>
       <c r="F66">
-        <v>21.8048</v>
+        <v>22.1455</v>
       </c>
       <c r="G66">
         <v>5.69</v>
@@ -6940,37 +6940,37 @@
         <v>0.377</v>
       </c>
       <c r="M66">
-        <v>5.14157184</v>
+        <v>5.221908900000001</v>
       </c>
       <c r="N66">
-        <v>-4.76457184</v>
+        <v>-4.844908900000001</v>
       </c>
       <c r="O66">
-        <v>-0.9529143680000001</v>
+        <v>-0.9689817800000002</v>
       </c>
       <c r="P66">
-        <v>-3.811657472</v>
+        <v>-3.875927120000001</v>
       </c>
       <c r="Q66">
-        <v>-3.454657472</v>
+        <v>-3.518927120000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1915072827890656</v>
+        <v>0.1956703480116104</v>
       </c>
       <c r="T66">
-        <v>2.840106146381725</v>
+        <v>2.921252036278346</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.01466477613196201</v>
+        <v>0.01443916419147029</v>
       </c>
       <c r="W66">
-        <v>0.2323420457880834</v>
+        <v>0.2323952450836513</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.07332388065980999</v>
+        <v>0.07219582095735144</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6986,22 +6986,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.219541531108437</v>
+        <v>0.221441531108437</v>
       </c>
       <c r="C67">
-        <v>-7.83636058643674</v>
+        <v>-8.270298016003775</v>
       </c>
       <c r="D67">
-        <v>8.619139413563262</v>
+        <v>8.525901983996224</v>
       </c>
       <c r="E67">
-        <v>20.9755</v>
+        <v>21.3162</v>
       </c>
       <c r="F67">
-        <v>22.1455</v>
+        <v>22.4862</v>
       </c>
       <c r="G67">
         <v>5.69</v>
@@ -7022,37 +7022,37 @@
         <v>0.377</v>
       </c>
       <c r="M67">
-        <v>5.221908900000001</v>
+        <v>5.30224596</v>
       </c>
       <c r="N67">
-        <v>-4.844908900000001</v>
+        <v>-4.925245960000001</v>
       </c>
       <c r="O67">
-        <v>-0.9689817800000002</v>
+        <v>-0.9850491920000002</v>
       </c>
       <c r="P67">
-        <v>-3.875927120000001</v>
+        <v>-3.940196768000001</v>
       </c>
       <c r="Q67">
-        <v>-3.518927120000001</v>
+        <v>-3.583196768000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1956703480116104</v>
+        <v>0.2000782994237165</v>
       </c>
       <c r="T67">
-        <v>2.921252036278346</v>
+        <v>3.007171213815945</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.01443916419147029</v>
+        <v>0.01422038897644801</v>
       </c>
       <c r="W67">
-        <v>0.2323952450836513</v>
+        <v>0.2324468322793536</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.07219582095735144</v>
+        <v>0.07110194488223998</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7068,22 +7068,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.221441531108437</v>
+        <v>0.223341531108437</v>
       </c>
       <c r="C68">
-        <v>-8.270298016003775</v>
+        <v>-8.702239843583257</v>
       </c>
       <c r="D68">
-        <v>8.525901983996224</v>
+        <v>8.434660156416744</v>
       </c>
       <c r="E68">
-        <v>21.3162</v>
+        <v>21.6569</v>
       </c>
       <c r="F68">
-        <v>22.4862</v>
+        <v>22.8269</v>
       </c>
       <c r="G68">
         <v>5.69</v>
@@ -7104,37 +7104,37 @@
         <v>0.377</v>
       </c>
       <c r="M68">
-        <v>5.30224596</v>
+        <v>5.382583020000001</v>
       </c>
       <c r="N68">
-        <v>-4.925245960000001</v>
+        <v>-5.005583020000001</v>
       </c>
       <c r="O68">
-        <v>-0.9850491920000002</v>
+        <v>-1.001116604</v>
       </c>
       <c r="P68">
-        <v>-3.940196768000001</v>
+        <v>-4.004466416000001</v>
       </c>
       <c r="Q68">
-        <v>-3.583196768000001</v>
+        <v>-3.647466416000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2000782994237165</v>
+        <v>0.2047533994062534</v>
       </c>
       <c r="T68">
-        <v>3.007171213815945</v>
+        <v>3.098297614234609</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.01422038897644801</v>
+        <v>0.01400814436485923</v>
       </c>
       <c r="W68">
-        <v>0.2324468322793536</v>
+        <v>0.2324968795587662</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.07110194488223998</v>
+        <v>0.0700407218242961</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7150,22 +7150,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.223341531108437</v>
+        <v>0.225241531108437</v>
       </c>
       <c r="C69">
-        <v>-8.702239843583257</v>
+        <v>-9.132249459914533</v>
       </c>
       <c r="D69">
-        <v>8.434660156416744</v>
+        <v>8.345350540085466</v>
       </c>
       <c r="E69">
-        <v>21.6569</v>
+        <v>21.9976</v>
       </c>
       <c r="F69">
-        <v>22.8269</v>
+        <v>23.1676</v>
       </c>
       <c r="G69">
         <v>5.69</v>
@@ -7186,37 +7186,37 @@
         <v>0.377</v>
       </c>
       <c r="M69">
-        <v>5.382583020000001</v>
+        <v>5.46292008</v>
       </c>
       <c r="N69">
-        <v>-5.005583020000001</v>
+        <v>-5.08592008</v>
       </c>
       <c r="O69">
-        <v>-1.001116604</v>
+        <v>-1.017184016</v>
       </c>
       <c r="P69">
-        <v>-4.004466416000001</v>
+        <v>-4.068736064</v>
       </c>
       <c r="Q69">
-        <v>-3.647466416000001</v>
+        <v>-3.711736064</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2047533994062534</v>
+        <v>0.2097206931376988</v>
       </c>
       <c r="T69">
-        <v>3.098297614234609</v>
+        <v>3.195119414679441</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.01400814436485923</v>
+        <v>0.0138021422418466</v>
       </c>
       <c r="W69">
-        <v>0.2324968795587662</v>
+        <v>0.2325454548593726</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.0700407218242961</v>
+        <v>0.06901071120923297</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7232,22 +7232,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.225241531108437</v>
+        <v>0.227141531108437</v>
       </c>
       <c r="C70">
-        <v>-9.132249459914533</v>
+        <v>-9.560387599039327</v>
       </c>
       <c r="D70">
-        <v>8.345350540085466</v>
+        <v>8.257912400960674</v>
       </c>
       <c r="E70">
-        <v>21.9976</v>
+        <v>22.3383</v>
       </c>
       <c r="F70">
-        <v>23.1676</v>
+        <v>23.5083</v>
       </c>
       <c r="G70">
         <v>5.69</v>
@@ -7268,37 +7268,37 @@
         <v>0.377</v>
       </c>
       <c r="M70">
-        <v>5.46292008</v>
+        <v>5.543257140000001</v>
       </c>
       <c r="N70">
-        <v>-5.08592008</v>
+        <v>-5.166257140000001</v>
       </c>
       <c r="O70">
-        <v>-1.017184016</v>
+        <v>-1.033251428</v>
       </c>
       <c r="P70">
-        <v>-4.068736064</v>
+        <v>-4.133005712000001</v>
       </c>
       <c r="Q70">
-        <v>-3.711736064</v>
+        <v>-3.776005712000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2097206931376988</v>
+        <v>0.2150084574324633</v>
       </c>
       <c r="T70">
-        <v>3.195119414679441</v>
+        <v>3.298187782894907</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0138021422418466</v>
+        <v>0.01360211119486331</v>
       </c>
       <c r="W70">
-        <v>0.2325454548593726</v>
+        <v>0.2325926221802512</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.06901071120923297</v>
+        <v>0.06801055597431649</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7314,22 +7314,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.227141531108437</v>
+        <v>0.229041531108437</v>
       </c>
       <c r="C71">
-        <v>-9.560387599039327</v>
+        <v>-9.986712476035912</v>
       </c>
       <c r="D71">
-        <v>8.257912400960674</v>
+        <v>8.172287523964091</v>
       </c>
       <c r="E71">
-        <v>22.3383</v>
+        <v>22.679</v>
       </c>
       <c r="F71">
-        <v>23.5083</v>
+        <v>23.849</v>
       </c>
       <c r="G71">
         <v>5.69</v>
@@ -7350,37 +7350,37 @@
         <v>0.377</v>
       </c>
       <c r="M71">
-        <v>5.543257140000001</v>
+        <v>5.623594200000001</v>
       </c>
       <c r="N71">
-        <v>-5.166257140000001</v>
+        <v>-5.246594200000001</v>
       </c>
       <c r="O71">
-        <v>-1.033251428</v>
+        <v>-1.04931884</v>
       </c>
       <c r="P71">
-        <v>-4.133005712000001</v>
+        <v>-4.197275360000001</v>
       </c>
       <c r="Q71">
-        <v>-3.776005712000001</v>
+        <v>-3.840275360000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2150084574324633</v>
+        <v>0.2206487393468788</v>
       </c>
       <c r="T71">
-        <v>3.298187782894907</v>
+        <v>3.408127375658071</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01360211119486331</v>
+        <v>0.01340779532065098</v>
       </c>
       <c r="W71">
-        <v>0.2325926221802512</v>
+        <v>0.2326384418633905</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.06801055597431649</v>
+        <v>0.06703897660325486</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7396,22 +7396,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.229041531108437</v>
+        <v>0.230941531108437</v>
       </c>
       <c r="C72">
-        <v>-9.986712476035912</v>
+        <v>-10.41127991627242</v>
       </c>
       <c r="D72">
-        <v>8.172287523964091</v>
+        <v>8.088420083727584</v>
       </c>
       <c r="E72">
-        <v>22.679</v>
+        <v>23.0197</v>
       </c>
       <c r="F72">
-        <v>23.849</v>
+        <v>24.1897</v>
       </c>
       <c r="G72">
         <v>5.69</v>
@@ -7432,37 +7432,37 @@
         <v>0.377</v>
       </c>
       <c r="M72">
-        <v>5.623594200000001</v>
+        <v>5.703931260000001</v>
       </c>
       <c r="N72">
-        <v>-5.246594200000001</v>
+        <v>-5.326931260000001</v>
       </c>
       <c r="O72">
-        <v>-1.04931884</v>
+        <v>-1.065386252</v>
       </c>
       <c r="P72">
-        <v>-4.197275360000001</v>
+        <v>-4.261545008000001</v>
       </c>
       <c r="Q72">
-        <v>-3.840275360000001</v>
+        <v>-3.904545008</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2206487393468788</v>
+        <v>0.2266780062209091</v>
       </c>
       <c r="T72">
-        <v>3.408127375658071</v>
+        <v>3.525649009301453</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01340779532065098</v>
+        <v>0.01321895313303618</v>
       </c>
       <c r="W72">
-        <v>0.2326384418633905</v>
+        <v>0.2326829708512301</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.06703897660325486</v>
+        <v>0.0660947656651808</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7478,22 +7478,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.230941531108437</v>
+        <v>0.232841531108437</v>
       </c>
       <c r="C73">
-        <v>-10.41127991627241</v>
+        <v>-10.83414347678226</v>
       </c>
       <c r="D73">
-        <v>8.088420083727586</v>
+        <v>8.006256523217742</v>
       </c>
       <c r="E73">
-        <v>23.0197</v>
+        <v>23.3604</v>
       </c>
       <c r="F73">
-        <v>24.1897</v>
+        <v>24.5304</v>
       </c>
       <c r="G73">
         <v>5.69</v>
@@ -7514,37 +7514,37 @@
         <v>0.377</v>
       </c>
       <c r="M73">
-        <v>5.70393126</v>
+        <v>5.784268320000001</v>
       </c>
       <c r="N73">
-        <v>-5.32693126</v>
+        <v>-5.407268320000001</v>
       </c>
       <c r="O73">
-        <v>-1.065386252</v>
+        <v>-1.081453664</v>
       </c>
       <c r="P73">
-        <v>-4.261545008000001</v>
+        <v>-4.325814656</v>
       </c>
       <c r="Q73">
-        <v>-3.904545008</v>
+        <v>-3.968814656</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.226678006220909</v>
+        <v>0.2331379350145129</v>
       </c>
       <c r="T73">
-        <v>3.525649009301451</v>
+        <v>3.651565045347932</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01321895313303618</v>
+        <v>0.01303535656174401</v>
       </c>
       <c r="W73">
-        <v>0.2326829708512301</v>
+        <v>0.2327262629227408</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.06609476566518091</v>
+        <v>0.06517678280871997</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7560,22 +7560,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.232841531108437</v>
+        <v>0.234741531108437</v>
       </c>
       <c r="C74">
-        <v>-10.83414347678226</v>
+        <v>-11.25535456031626</v>
       </c>
       <c r="D74">
-        <v>8.006256523217742</v>
+        <v>7.925745439683738</v>
       </c>
       <c r="E74">
-        <v>23.3604</v>
+        <v>23.7011</v>
       </c>
       <c r="F74">
-        <v>24.5304</v>
+        <v>24.8711</v>
       </c>
       <c r="G74">
         <v>5.69</v>
@@ -7596,37 +7596,37 @@
         <v>0.377</v>
       </c>
       <c r="M74">
-        <v>5.784268320000001</v>
+        <v>5.86460538</v>
       </c>
       <c r="N74">
-        <v>-5.407268320000001</v>
+        <v>-5.48760538</v>
       </c>
       <c r="O74">
-        <v>-1.081453664</v>
+        <v>-1.097521076</v>
       </c>
       <c r="P74">
-        <v>-4.325814656</v>
+        <v>-4.390084304</v>
       </c>
       <c r="Q74">
-        <v>-3.968814656</v>
+        <v>-4.033084304</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2331379350145129</v>
+        <v>0.2400763770520875</v>
       </c>
       <c r="T74">
-        <v>3.651565045347932</v>
+        <v>3.786808195175633</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01303535656174401</v>
+        <v>0.01285679003350094</v>
       </c>
       <c r="W74">
-        <v>0.2327262629227408</v>
+        <v>0.2327683689101005</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.06517678280871997</v>
+        <v>0.06428395016750466</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7642,22 +7642,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.234741531108437</v>
+        <v>0.236641531108437</v>
       </c>
       <c r="C75">
-        <v>-11.25535456031626</v>
+        <v>-11.67496252258178</v>
       </c>
       <c r="D75">
-        <v>7.925745439683738</v>
+        <v>7.846837477418215</v>
       </c>
       <c r="E75">
-        <v>23.7011</v>
+        <v>24.0418</v>
       </c>
       <c r="F75">
-        <v>24.8711</v>
+        <v>25.2118</v>
       </c>
       <c r="G75">
         <v>5.69</v>
@@ -7678,37 +7678,37 @@
         <v>0.377</v>
       </c>
       <c r="M75">
-        <v>5.86460538</v>
+        <v>5.94494244</v>
       </c>
       <c r="N75">
-        <v>-5.48760538</v>
+        <v>-5.56794244</v>
       </c>
       <c r="O75">
-        <v>-1.097521076</v>
+        <v>-1.113588488</v>
       </c>
       <c r="P75">
-        <v>-4.390084304</v>
+        <v>-4.454353952</v>
       </c>
       <c r="Q75">
-        <v>-4.033084304</v>
+        <v>-4.097353952</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2400763770520875</v>
+        <v>0.2475485454002447</v>
       </c>
       <c r="T75">
-        <v>3.786808195175633</v>
+        <v>3.93245466422085</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01285679003350094</v>
+        <v>0.01268304962764282</v>
       </c>
       <c r="W75">
-        <v>0.2327683689101005</v>
+        <v>0.2328093368978018</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.06428395016750466</v>
+        <v>0.06341524813821409</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7724,22 +7724,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.236641531108437</v>
+        <v>0.238541531108437</v>
       </c>
       <c r="C76">
-        <v>-11.67496252258178</v>
+        <v>-12.09301477313907</v>
       </c>
       <c r="D76">
-        <v>7.846837477418215</v>
+        <v>7.769485226860926</v>
       </c>
       <c r="E76">
-        <v>24.0418</v>
+        <v>24.3825</v>
       </c>
       <c r="F76">
-        <v>25.2118</v>
+        <v>25.5525</v>
       </c>
       <c r="G76">
         <v>5.69</v>
@@ -7760,37 +7760,37 @@
         <v>0.377</v>
       </c>
       <c r="M76">
-        <v>5.94494244</v>
+        <v>6.025279500000001</v>
       </c>
       <c r="N76">
-        <v>-5.56794244</v>
+        <v>-5.648279500000001</v>
       </c>
       <c r="O76">
-        <v>-1.113588488</v>
+        <v>-1.1296559</v>
       </c>
       <c r="P76">
-        <v>-4.454353952</v>
+        <v>-4.518623600000001</v>
       </c>
       <c r="Q76">
-        <v>-4.097353952</v>
+        <v>-4.1616236</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2475485454002447</v>
+        <v>0.2556184872162545</v>
       </c>
       <c r="T76">
-        <v>3.93245466422085</v>
+        <v>4.089752850789684</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01268304962764282</v>
+        <v>0.01251394229927425</v>
       </c>
       <c r="W76">
-        <v>0.2328093368978018</v>
+        <v>0.2328492124058311</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.06341524813821409</v>
+        <v>0.06256971149637125</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7806,22 +7806,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.238541531108437</v>
+        <v>0.240441531108437</v>
       </c>
       <c r="C77">
-        <v>-12.09301477313907</v>
+        <v>-12.50955687038816</v>
       </c>
       <c r="D77">
-        <v>7.769485226860926</v>
+        <v>7.693643129611845</v>
       </c>
       <c r="E77">
-        <v>24.3825</v>
+        <v>24.7232</v>
       </c>
       <c r="F77">
-        <v>25.5525</v>
+        <v>25.8932</v>
       </c>
       <c r="G77">
         <v>5.69</v>
@@ -7842,37 +7842,37 @@
         <v>0.377</v>
       </c>
       <c r="M77">
-        <v>6.025279500000001</v>
+        <v>6.105616560000001</v>
       </c>
       <c r="N77">
-        <v>-5.648279500000001</v>
+        <v>-5.728616560000001</v>
       </c>
       <c r="O77">
-        <v>-1.1296559</v>
+        <v>-1.145723312</v>
       </c>
       <c r="P77">
-        <v>-4.518623600000001</v>
+        <v>-4.582893248</v>
       </c>
       <c r="Q77">
-        <v>-4.1616236</v>
+        <v>-4.225893248</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2556184872162545</v>
+        <v>0.2643609241835985</v>
       </c>
       <c r="T77">
-        <v>4.089752850789684</v>
+        <v>4.260159219572588</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01251394229927425</v>
+        <v>0.01234928516375748</v>
       </c>
       <c r="W77">
-        <v>0.2328492124058311</v>
+        <v>0.232888038558386</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.06256971149637125</v>
+        <v>0.06174642581878742</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7888,22 +7888,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.240441531108437</v>
+        <v>0.242341531108437</v>
       </c>
       <c r="C78">
-        <v>-12.50955687038816</v>
+        <v>-12.92463261104623</v>
       </c>
       <c r="D78">
-        <v>7.693643129611845</v>
+        <v>7.619267388953772</v>
       </c>
       <c r="E78">
-        <v>24.7232</v>
+        <v>25.0639</v>
       </c>
       <c r="F78">
-        <v>25.8932</v>
+        <v>26.2339</v>
       </c>
       <c r="G78">
         <v>5.69</v>
@@ -7924,37 +7924,37 @@
         <v>0.377</v>
       </c>
       <c r="M78">
-        <v>6.105616560000001</v>
+        <v>6.185953620000001</v>
       </c>
       <c r="N78">
-        <v>-5.728616560000001</v>
+        <v>-5.808953620000001</v>
       </c>
       <c r="O78">
-        <v>-1.145723312</v>
+        <v>-1.161790724</v>
       </c>
       <c r="P78">
-        <v>-4.582893248</v>
+        <v>-4.647162896000001</v>
       </c>
       <c r="Q78">
-        <v>-4.225893248</v>
+        <v>-4.290162896000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2643609241835985</v>
+        <v>0.2738635730611462</v>
       </c>
       <c r="T78">
-        <v>4.260159219572588</v>
+        <v>4.445383533467049</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01234928516375748</v>
+        <v>0.01218890483695544</v>
       </c>
       <c r="W78">
-        <v>0.232888038558386</v>
+        <v>0.2329258562394459</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.06174642581878742</v>
+        <v>0.06094452418477714</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7970,22 +7970,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.242341531108437</v>
+        <v>0.244241531108437</v>
       </c>
       <c r="C79">
-        <v>-12.92463261104623</v>
+        <v>-13.3382841144848</v>
       </c>
       <c r="D79">
-        <v>7.619267388953772</v>
+        <v>7.546315885515202</v>
       </c>
       <c r="E79">
-        <v>25.0639</v>
+        <v>25.4046</v>
       </c>
       <c r="F79">
-        <v>26.2339</v>
+        <v>26.5746</v>
       </c>
       <c r="G79">
         <v>5.69</v>
@@ -8006,37 +8006,37 @@
         <v>0.377</v>
       </c>
       <c r="M79">
-        <v>6.185953620000001</v>
+        <v>6.26629068</v>
       </c>
       <c r="N79">
-        <v>-5.808953620000001</v>
+        <v>-5.88929068</v>
       </c>
       <c r="O79">
-        <v>-1.161790724</v>
+        <v>-1.177858136</v>
       </c>
       <c r="P79">
-        <v>-4.647162896000001</v>
+        <v>-4.711432544</v>
       </c>
       <c r="Q79">
-        <v>-4.290162896000001</v>
+        <v>-4.354432544</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2738635730611462</v>
+        <v>0.2842300991093801</v>
       </c>
       <c r="T79">
-        <v>4.445383533467049</v>
+        <v>4.647446421351915</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01218890483695544</v>
+        <v>0.01203263682622524</v>
       </c>
       <c r="W79">
-        <v>0.2329258562394459</v>
+        <v>0.2329627042363761</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.06094452418477714</v>
+        <v>0.0601631841311262</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8052,22 +8052,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.244241531108437</v>
+        <v>0.246141531108437</v>
       </c>
       <c r="C80">
-        <v>-13.3382841144848</v>
+        <v>-13.75055190226774</v>
       </c>
       <c r="D80">
-        <v>7.546315885515202</v>
+        <v>7.474748097732256</v>
       </c>
       <c r="E80">
-        <v>25.4046</v>
+        <v>25.7453</v>
       </c>
       <c r="F80">
-        <v>26.5746</v>
+        <v>26.9153</v>
       </c>
       <c r="G80">
         <v>5.69</v>
@@ -8088,37 +8088,37 @@
         <v>0.377</v>
       </c>
       <c r="M80">
-        <v>6.26629068</v>
+        <v>6.346627740000001</v>
       </c>
       <c r="N80">
-        <v>-5.88929068</v>
+        <v>-5.969627740000001</v>
       </c>
       <c r="O80">
-        <v>-1.177858136</v>
+        <v>-1.193925548</v>
       </c>
       <c r="P80">
-        <v>-4.711432544</v>
+        <v>-4.775702192000001</v>
       </c>
       <c r="Q80">
-        <v>-4.354432544</v>
+        <v>-4.418702192</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2842300991093801</v>
+        <v>0.2955839133526839</v>
       </c>
       <c r="T80">
-        <v>4.647446421351915</v>
+        <v>4.868753393797244</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01203263682622524</v>
+        <v>0.01188032496766543</v>
       </c>
       <c r="W80">
-        <v>0.2329627042363761</v>
+        <v>0.2329986193726245</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.0601631841311262</v>
+        <v>0.05940162483832712</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8134,22 +8134,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.246141531108437</v>
+        <v>0.248041531108437</v>
       </c>
       <c r="C81">
-        <v>-13.75055190226774</v>
+        <v>-14.16147497320601</v>
       </c>
       <c r="D81">
-        <v>7.474748097732256</v>
+        <v>7.404525026793993</v>
       </c>
       <c r="E81">
-        <v>25.7453</v>
+        <v>26.086</v>
       </c>
       <c r="F81">
-        <v>26.9153</v>
+        <v>27.256</v>
       </c>
       <c r="G81">
         <v>5.69</v>
@@ -8170,37 +8170,37 @@
         <v>0.377</v>
       </c>
       <c r="M81">
-        <v>6.346627740000001</v>
+        <v>6.4269648</v>
       </c>
       <c r="N81">
-        <v>-5.969627740000001</v>
+        <v>-6.049964800000001</v>
       </c>
       <c r="O81">
-        <v>-1.193925548</v>
+        <v>-1.20999296</v>
       </c>
       <c r="P81">
-        <v>-4.775702192000001</v>
+        <v>-4.83997184</v>
       </c>
       <c r="Q81">
-        <v>-4.418702192</v>
+        <v>-4.48297184</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2955839133526839</v>
+        <v>0.3080731090203181</v>
       </c>
       <c r="T81">
-        <v>4.868753393797244</v>
+        <v>5.112191063487106</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01188032496766543</v>
+        <v>0.01173182090556961</v>
       </c>
       <c r="W81">
-        <v>0.2329986193726245</v>
+        <v>0.2330336366304667</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.05940162483832712</v>
+        <v>0.05865910452784806</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8216,22 +8216,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.248041531108437</v>
+        <v>0.249941531108437</v>
       </c>
       <c r="C82">
-        <v>-14.16147497320601</v>
+        <v>-14.57109087422096</v>
       </c>
       <c r="D82">
-        <v>7.404525026793993</v>
+        <v>7.335609125779043</v>
       </c>
       <c r="E82">
-        <v>26.086</v>
+        <v>26.4267</v>
       </c>
       <c r="F82">
-        <v>27.256</v>
+        <v>27.5967</v>
       </c>
       <c r="G82">
         <v>5.69</v>
@@ -8252,37 +8252,37 @@
         <v>0.377</v>
       </c>
       <c r="M82">
-        <v>6.4269648</v>
+        <v>6.507301860000001</v>
       </c>
       <c r="N82">
-        <v>-6.049964800000001</v>
+        <v>-6.130301860000001</v>
       </c>
       <c r="O82">
-        <v>-1.20999296</v>
+        <v>-1.226060372</v>
       </c>
       <c r="P82">
-        <v>-4.83997184</v>
+        <v>-4.904241488000001</v>
       </c>
       <c r="Q82">
-        <v>-4.48297184</v>
+        <v>-4.547241488000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3080731090203181</v>
+        <v>0.3218769568634928</v>
       </c>
       <c r="T82">
-        <v>5.112191063487106</v>
+        <v>5.381253751039059</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01173182090556961</v>
+        <v>0.01158698361043912</v>
       </c>
       <c r="W82">
-        <v>0.2330336366304667</v>
+        <v>0.2330677892646585</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.05865910452784806</v>
+        <v>0.05793491805219553</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8298,22 +8298,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.249941531108437</v>
+        <v>0.251841531108437</v>
       </c>
       <c r="C83">
-        <v>-14.57109087422096</v>
+        <v>-14.97943576728693</v>
       </c>
       <c r="D83">
-        <v>7.335609125779043</v>
+        <v>7.267964232713068</v>
       </c>
       <c r="E83">
-        <v>26.4267</v>
+        <v>26.7674</v>
       </c>
       <c r="F83">
-        <v>27.5967</v>
+        <v>27.9374</v>
       </c>
       <c r="G83">
         <v>5.69</v>
@@ -8334,37 +8334,37 @@
         <v>0.377</v>
       </c>
       <c r="M83">
-        <v>6.507301860000001</v>
+        <v>6.587638920000001</v>
       </c>
       <c r="N83">
-        <v>-6.130301860000001</v>
+        <v>-6.210638920000001</v>
       </c>
       <c r="O83">
-        <v>-1.226060372</v>
+        <v>-1.242127784</v>
       </c>
       <c r="P83">
-        <v>-4.904241488000001</v>
+        <v>-4.968511136000001</v>
       </c>
       <c r="Q83">
-        <v>-4.547241488000001</v>
+        <v>-4.611511136000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3218769568634928</v>
+        <v>0.3372145655781313</v>
       </c>
       <c r="T83">
-        <v>5.381253751039059</v>
+        <v>5.680212292763452</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01158698361043912</v>
+        <v>0.01144567893226303</v>
       </c>
       <c r="W83">
-        <v>0.2330677892646585</v>
+        <v>0.2331011089077724</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.05793491805219553</v>
+        <v>0.05722839466131513</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8380,22 +8380,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.251841531108437</v>
+        <v>0.253741531108437</v>
       </c>
       <c r="C84">
-        <v>-14.97943576728693</v>
+        <v>-15.38654449270386</v>
       </c>
       <c r="D84">
-        <v>7.267964232713068</v>
+        <v>7.201555507296145</v>
       </c>
       <c r="E84">
-        <v>26.7674</v>
+        <v>27.1081</v>
       </c>
       <c r="F84">
-        <v>27.9374</v>
+        <v>28.2781</v>
       </c>
       <c r="G84">
         <v>5.69</v>
@@ -8416,37 +8416,37 @@
         <v>0.377</v>
       </c>
       <c r="M84">
-        <v>6.587638920000001</v>
+        <v>6.66797598</v>
       </c>
       <c r="N84">
-        <v>-6.210638920000001</v>
+        <v>-6.290975980000001</v>
       </c>
       <c r="O84">
-        <v>-1.242127784</v>
+        <v>-1.258195196</v>
       </c>
       <c r="P84">
-        <v>-4.968511136000001</v>
+        <v>-5.032780784000001</v>
       </c>
       <c r="Q84">
-        <v>-4.611511136000001</v>
+        <v>-4.675780784000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3372145655781313</v>
+        <v>0.3543565988474332</v>
       </c>
       <c r="T84">
-        <v>5.680212292763452</v>
+        <v>6.014342427631891</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01144567893226303</v>
+        <v>0.01130777918609119</v>
       </c>
       <c r="W84">
-        <v>0.2331011089077724</v>
+        <v>0.2331336256679197</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.05722839466131513</v>
+        <v>0.05653889593045591</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8462,22 +8462,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.253741531108437</v>
+        <v>0.255641531108437</v>
       </c>
       <c r="C85">
-        <v>-15.38654449270386</v>
+        <v>-15.7924506289324</v>
       </c>
       <c r="D85">
-        <v>7.201555507296145</v>
+        <v>7.136349371067602</v>
       </c>
       <c r="E85">
-        <v>27.1081</v>
+        <v>27.44880000000001</v>
       </c>
       <c r="F85">
-        <v>28.2781</v>
+        <v>28.6188</v>
       </c>
       <c r="G85">
         <v>5.69</v>
@@ -8498,37 +8498,37 @@
         <v>0.377</v>
       </c>
       <c r="M85">
-        <v>6.66797598</v>
+        <v>6.748313040000001</v>
       </c>
       <c r="N85">
-        <v>-6.290975980000001</v>
+        <v>-6.371313040000001</v>
       </c>
       <c r="O85">
-        <v>-1.258195196</v>
+        <v>-1.274262608</v>
       </c>
       <c r="P85">
-        <v>-5.032780784000001</v>
+        <v>-5.097050432000001</v>
       </c>
       <c r="Q85">
-        <v>-4.675780784000001</v>
+        <v>-4.740050432000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3543565988474332</v>
+        <v>0.3736413862753978</v>
       </c>
       <c r="T85">
-        <v>6.014342427631891</v>
+        <v>6.390238829358885</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01130777918609119</v>
+        <v>0.01117316276720915</v>
       </c>
       <c r="W85">
-        <v>0.2331336256679197</v>
+        <v>0.2331653682194921</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.05653889593045591</v>
+        <v>0.05586581383604572</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8544,22 +8544,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.255641531108437</v>
+        <v>0.257541531108437</v>
       </c>
       <c r="C86">
-        <v>-15.79245062893239</v>
+        <v>-16.19718654920769</v>
       </c>
       <c r="D86">
-        <v>7.136349371067606</v>
+        <v>7.07231345079231</v>
       </c>
       <c r="E86">
-        <v>27.4488</v>
+        <v>27.7895</v>
       </c>
       <c r="F86">
-        <v>28.6188</v>
+        <v>28.9595</v>
       </c>
       <c r="G86">
         <v>5.69</v>
@@ -8580,37 +8580,37 @@
         <v>0.377</v>
       </c>
       <c r="M86">
-        <v>6.74831304</v>
+        <v>6.8286501</v>
       </c>
       <c r="N86">
-        <v>-6.37131304</v>
+        <v>-6.4516501</v>
       </c>
       <c r="O86">
-        <v>-1.274262608</v>
+        <v>-1.29033002</v>
       </c>
       <c r="P86">
-        <v>-5.097050432000001</v>
+        <v>-5.16132008</v>
       </c>
       <c r="Q86">
-        <v>-4.740050432</v>
+        <v>-4.80432008</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3736413862753976</v>
+        <v>0.3954974786937575</v>
       </c>
       <c r="T86">
-        <v>6.39023882935888</v>
+        <v>6.81625475131614</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01117316276720915</v>
+        <v>0.01104171379347728</v>
       </c>
       <c r="W86">
-        <v>0.2331653682194921</v>
+        <v>0.2331963638874981</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.05586581383604572</v>
+        <v>0.05520856896738635</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8626,22 +8626,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.257541531108437</v>
+        <v>0.2594415311084369</v>
       </c>
       <c r="C87">
-        <v>-16.19718654920769</v>
+        <v>-16.6007834751321</v>
       </c>
       <c r="D87">
-        <v>7.07231345079231</v>
+        <v>7.009416524867901</v>
       </c>
       <c r="E87">
-        <v>27.7895</v>
+        <v>28.1302</v>
       </c>
       <c r="F87">
-        <v>28.9595</v>
+        <v>29.3002</v>
       </c>
       <c r="G87">
         <v>5.69</v>
@@ -8662,37 +8662,37 @@
         <v>0.377</v>
       </c>
       <c r="M87">
-        <v>6.8286501</v>
+        <v>6.908987160000001</v>
       </c>
       <c r="N87">
-        <v>-6.4516501</v>
+        <v>-6.531987160000001</v>
       </c>
       <c r="O87">
-        <v>-1.29033002</v>
+        <v>-1.306397432</v>
       </c>
       <c r="P87">
-        <v>-5.16132008</v>
+        <v>-5.225589728000001</v>
       </c>
       <c r="Q87">
-        <v>-4.80432008</v>
+        <v>-4.868589728000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3954974786937575</v>
+        <v>0.4204758700290258</v>
       </c>
       <c r="T87">
-        <v>6.81625475131614</v>
+        <v>7.303130090695864</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01104171379347728</v>
+        <v>0.01091332177262289</v>
       </c>
       <c r="W87">
-        <v>0.2331963638874981</v>
+        <v>0.2332266387260155</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.05520856896738635</v>
+        <v>0.05456660886311437</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8708,22 +8708,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2594415311084369</v>
+        <v>0.261341531108437</v>
       </c>
       <c r="C88">
-        <v>-16.6007834751321</v>
+        <v>-17.00327152743349</v>
       </c>
       <c r="D88">
-        <v>7.009416524867901</v>
+        <v>6.947628472566511</v>
       </c>
       <c r="E88">
-        <v>28.1302</v>
+        <v>28.4709</v>
       </c>
       <c r="F88">
-        <v>29.3002</v>
+        <v>29.6409</v>
       </c>
       <c r="G88">
         <v>5.69</v>
@@ -8744,37 +8744,37 @@
         <v>0.377</v>
       </c>
       <c r="M88">
-        <v>6.908987160000001</v>
+        <v>6.98932422</v>
       </c>
       <c r="N88">
-        <v>-6.531987160000001</v>
+        <v>-6.612324220000001</v>
       </c>
       <c r="O88">
-        <v>-1.306397432</v>
+        <v>-1.322464844</v>
       </c>
       <c r="P88">
-        <v>-5.225589728000001</v>
+        <v>-5.289859376000001</v>
       </c>
       <c r="Q88">
-        <v>-4.868589728000001</v>
+        <v>-4.932859376000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4204758700290258</v>
+        <v>0.4492970908004894</v>
       </c>
       <c r="T88">
-        <v>7.303130090695864</v>
+        <v>7.8649093284417</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01091332177262289</v>
+        <v>0.0107878812924778</v>
       </c>
       <c r="W88">
-        <v>0.2332266387260155</v>
+        <v>0.2332562175912337</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.05456660886311437</v>
+        <v>0.05393940646238893</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8790,22 +8790,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.261341531108437</v>
+        <v>0.263241531108437</v>
       </c>
       <c r="C89">
-        <v>-17.00327152743349</v>
+        <v>-17.40467977406229</v>
       </c>
       <c r="D89">
-        <v>6.947628472566511</v>
+        <v>6.886920225937703</v>
       </c>
       <c r="E89">
-        <v>28.4709</v>
+        <v>28.8116</v>
       </c>
       <c r="F89">
-        <v>29.6409</v>
+        <v>29.9816</v>
       </c>
       <c r="G89">
         <v>5.69</v>
@@ -8826,37 +8826,37 @@
         <v>0.377</v>
       </c>
       <c r="M89">
-        <v>6.98932422</v>
+        <v>7.06966128</v>
       </c>
       <c r="N89">
-        <v>-6.612324220000001</v>
+        <v>-6.69266128</v>
       </c>
       <c r="O89">
-        <v>-1.322464844</v>
+        <v>-1.338532256</v>
       </c>
       <c r="P89">
-        <v>-5.289859376000001</v>
+        <v>-5.354129024000001</v>
       </c>
       <c r="Q89">
-        <v>-4.932859376000001</v>
+        <v>-4.997129024</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4492970908004894</v>
+        <v>0.4829218483671969</v>
       </c>
       <c r="T89">
-        <v>7.8649093284417</v>
+        <v>8.520318439145177</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0107878812924778</v>
+        <v>0.01066529173233601</v>
       </c>
       <c r="W89">
-        <v>0.2332562175912337</v>
+        <v>0.2332851242095152</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.05393940646238893</v>
+        <v>0.05332645866167995</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8872,22 +8872,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.263241531108437</v>
+        <v>0.265141531108437</v>
       </c>
       <c r="C90">
-        <v>-17.40467977406229</v>
+        <v>-17.80503627578888</v>
       </c>
       <c r="D90">
-        <v>6.886920225937703</v>
+        <v>6.827263724211123</v>
       </c>
       <c r="E90">
-        <v>28.8116</v>
+        <v>29.1523</v>
       </c>
       <c r="F90">
-        <v>29.9816</v>
+        <v>30.3223</v>
       </c>
       <c r="G90">
         <v>5.69</v>
@@ -8908,37 +8908,37 @@
         <v>0.377</v>
       </c>
       <c r="M90">
-        <v>7.06966128</v>
+        <v>7.149998340000001</v>
       </c>
       <c r="N90">
-        <v>-6.69266128</v>
+        <v>-6.772998340000001</v>
       </c>
       <c r="O90">
-        <v>-1.338532256</v>
+        <v>-1.354599668</v>
       </c>
       <c r="P90">
-        <v>-5.354129024000001</v>
+        <v>-5.418398672</v>
       </c>
       <c r="Q90">
-        <v>-4.997129024</v>
+        <v>-5.061398672</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4829218483671969</v>
+        <v>0.5226601982187602</v>
       </c>
       <c r="T90">
-        <v>8.520318439145177</v>
+        <v>9.294892842703829</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01066529173233601</v>
+        <v>0.01054545699377044</v>
       </c>
       <c r="W90">
-        <v>0.2332851242095152</v>
+        <v>0.233313381240869</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.05332645866167995</v>
+        <v>0.05272728496885215</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8954,22 +8954,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.265141531108437</v>
+        <v>0.267041531108437</v>
       </c>
       <c r="C91">
-        <v>-17.80503627578888</v>
+        <v>-18.2043681294513</v>
       </c>
       <c r="D91">
-        <v>6.827263724211123</v>
+        <v>6.768631870548695</v>
       </c>
       <c r="E91">
-        <v>29.1523</v>
+        <v>29.493</v>
       </c>
       <c r="F91">
-        <v>30.3223</v>
+        <v>30.663</v>
       </c>
       <c r="G91">
         <v>5.69</v>
@@ -8990,37 +8990,37 @@
         <v>0.377</v>
       </c>
       <c r="M91">
-        <v>7.149998340000001</v>
+        <v>7.2303354</v>
       </c>
       <c r="N91">
-        <v>-6.772998340000001</v>
+        <v>-6.853335400000001</v>
       </c>
       <c r="O91">
-        <v>-1.354599668</v>
+        <v>-1.37066708</v>
       </c>
       <c r="P91">
-        <v>-5.418398672</v>
+        <v>-5.48266832</v>
       </c>
       <c r="Q91">
-        <v>-5.061398672</v>
+        <v>-5.12566832</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5226601982187602</v>
+        <v>0.5703462180406362</v>
       </c>
       <c r="T91">
-        <v>9.294892842703829</v>
+        <v>10.22438212697421</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01054545699377044</v>
+        <v>0.01042828524939521</v>
       </c>
       <c r="W91">
-        <v>0.233313381240869</v>
+        <v>0.2333410103381926</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.05272728496885215</v>
+        <v>0.05214142624697604</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9036,22 +9036,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.267041531108437</v>
+        <v>0.268941531108437</v>
       </c>
       <c r="C92">
-        <v>-18.2043681294513</v>
+        <v>-18.6027015089937</v>
       </c>
       <c r="D92">
-        <v>6.768631870548695</v>
+        <v>6.710998491006306</v>
       </c>
       <c r="E92">
-        <v>29.493</v>
+        <v>29.8337</v>
       </c>
       <c r="F92">
-        <v>30.663</v>
+        <v>31.0037</v>
       </c>
       <c r="G92">
         <v>5.69</v>
@@ -9072,37 +9072,37 @@
         <v>0.377</v>
       </c>
       <c r="M92">
-        <v>7.2303354</v>
+        <v>7.310672460000001</v>
       </c>
       <c r="N92">
-        <v>-6.853335400000001</v>
+        <v>-6.933672460000001</v>
       </c>
       <c r="O92">
-        <v>-1.37066708</v>
+        <v>-1.386734492</v>
       </c>
       <c r="P92">
-        <v>-5.48266832</v>
+        <v>-5.546937968000001</v>
       </c>
       <c r="Q92">
-        <v>-5.12566832</v>
+        <v>-5.189937968000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5703462180406362</v>
+        <v>0.6286291311562625</v>
       </c>
       <c r="T92">
-        <v>10.22438212697421</v>
+        <v>11.3604245855269</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01042828524939521</v>
+        <v>0.01031368870819306</v>
       </c>
       <c r="W92">
-        <v>0.2333410103381926</v>
+        <v>0.2333680322026081</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.05214142624697604</v>
+        <v>0.05156844354096524</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9118,22 +9118,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.268941531108437</v>
+        <v>0.270841531108437</v>
       </c>
       <c r="C93">
-        <v>-18.6027015089937</v>
+        <v>-19.00006170442565</v>
       </c>
       <c r="D93">
-        <v>6.710998491006306</v>
+        <v>6.654338295574345</v>
       </c>
       <c r="E93">
-        <v>29.8337</v>
+        <v>30.1744</v>
       </c>
       <c r="F93">
-        <v>31.0037</v>
+        <v>31.3444</v>
       </c>
       <c r="G93">
         <v>5.69</v>
@@ -9154,37 +9154,37 @@
         <v>0.377</v>
       </c>
       <c r="M93">
-        <v>7.310672460000001</v>
+        <v>7.391009520000001</v>
       </c>
       <c r="N93">
-        <v>-6.933672460000001</v>
+        <v>-7.014009520000001</v>
       </c>
       <c r="O93">
-        <v>-1.386734492</v>
+        <v>-1.402801904</v>
       </c>
       <c r="P93">
-        <v>-5.546937968000001</v>
+        <v>-5.611207616000001</v>
       </c>
       <c r="Q93">
-        <v>-5.189937968000001</v>
+        <v>-5.254207616</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6286291311562625</v>
+        <v>0.7014827725507955</v>
       </c>
       <c r="T93">
-        <v>11.3604245855269</v>
+        <v>12.78047765871777</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01031368870819306</v>
+        <v>0.01020158339614748</v>
       </c>
       <c r="W93">
-        <v>0.2333680322026081</v>
+        <v>0.2333944666351884</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.05156844354096524</v>
+        <v>0.05100791698073737</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9200,22 +9200,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.270841531108437</v>
+        <v>0.272741531108437</v>
       </c>
       <c r="C94">
-        <v>-19.00006170442565</v>
+        <v>-19.39647315882468</v>
       </c>
       <c r="D94">
-        <v>6.654338295574345</v>
+        <v>6.598626841175327</v>
       </c>
       <c r="E94">
-        <v>30.1744</v>
+        <v>30.5151</v>
       </c>
       <c r="F94">
-        <v>31.3444</v>
+        <v>31.6851</v>
       </c>
       <c r="G94">
         <v>5.69</v>
@@ -9236,37 +9236,37 @@
         <v>0.377</v>
       </c>
       <c r="M94">
-        <v>7.391009520000001</v>
+        <v>7.471346580000001</v>
       </c>
       <c r="N94">
-        <v>-7.014009520000001</v>
+        <v>-7.094346580000001</v>
       </c>
       <c r="O94">
-        <v>-1.402801904</v>
+        <v>-1.418869316</v>
       </c>
       <c r="P94">
-        <v>-5.611207616000001</v>
+        <v>-5.675477264</v>
       </c>
       <c r="Q94">
-        <v>-5.254207616</v>
+        <v>-5.318477264</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7014827725507955</v>
+        <v>0.7951517400580521</v>
       </c>
       <c r="T94">
-        <v>12.78047765871777</v>
+        <v>14.60626018139174</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01020158339614748</v>
+        <v>0.01009188895102762</v>
       </c>
       <c r="W94">
-        <v>0.2333944666351884</v>
+        <v>0.2334203325853477</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.05100791698073737</v>
+        <v>0.05045944475513808</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9282,22 +9282,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.272741531108437</v>
+        <v>0.274641531108437</v>
       </c>
       <c r="C95">
-        <v>-19.39647315882468</v>
+        <v>-19.79195950349519</v>
       </c>
       <c r="D95">
-        <v>6.598626841175327</v>
+        <v>6.54384049650482</v>
       </c>
       <c r="E95">
-        <v>30.5151</v>
+        <v>30.8558</v>
       </c>
       <c r="F95">
-        <v>31.6851</v>
+        <v>32.0258</v>
       </c>
       <c r="G95">
         <v>5.69</v>
@@ -9318,37 +9318,37 @@
         <v>0.377</v>
       </c>
       <c r="M95">
-        <v>7.471346580000001</v>
+        <v>7.551683640000001</v>
       </c>
       <c r="N95">
-        <v>-7.094346580000001</v>
+        <v>-7.174683640000001</v>
       </c>
       <c r="O95">
-        <v>-1.418869316</v>
+        <v>-1.434936728</v>
       </c>
       <c r="P95">
-        <v>-5.675477264</v>
+        <v>-5.739746912000001</v>
       </c>
       <c r="Q95">
-        <v>-5.318477264</v>
+        <v>-5.382746912000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7951517400580521</v>
+        <v>0.9200436967343945</v>
       </c>
       <c r="T95">
-        <v>14.60626018139174</v>
+        <v>17.04063687829037</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01009188895102762</v>
+        <v>0.009984528430272007</v>
       </c>
       <c r="W95">
-        <v>0.2334203325853477</v>
+        <v>0.2334456481961419</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.05045944475513808</v>
+        <v>0.04992264215136</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9364,22 +9364,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.274641531108437</v>
+        <v>0.276541531108437</v>
       </c>
       <c r="C96">
-        <v>-19.79195950349519</v>
+        <v>-20.18654359139055</v>
       </c>
       <c r="D96">
-        <v>6.54384049650482</v>
+        <v>6.489956408609449</v>
       </c>
       <c r="E96">
-        <v>30.8558</v>
+        <v>31.1965</v>
       </c>
       <c r="F96">
-        <v>32.0258</v>
+        <v>32.3665</v>
       </c>
       <c r="G96">
         <v>5.69</v>
@@ -9400,37 +9400,37 @@
         <v>0.377</v>
       </c>
       <c r="M96">
-        <v>7.551683640000001</v>
+        <v>7.632020700000001</v>
       </c>
       <c r="N96">
-        <v>-7.174683640000001</v>
+        <v>-7.255020700000001</v>
       </c>
       <c r="O96">
-        <v>-1.434936728</v>
+        <v>-1.45100414</v>
       </c>
       <c r="P96">
-        <v>-5.739746912000001</v>
+        <v>-5.804016560000001</v>
       </c>
       <c r="Q96">
-        <v>-5.382746912000001</v>
+        <v>-5.447016560000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9200436967343945</v>
+        <v>1.094892436081274</v>
       </c>
       <c r="T96">
-        <v>17.04063687829037</v>
+        <v>20.44876425394845</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.009984528430272007</v>
+        <v>0.009879428131005986</v>
       </c>
       <c r="W96">
-        <v>0.2334456481961419</v>
+        <v>0.2334704308467088</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.04992264215136</v>
+        <v>0.04939714065502987</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9446,22 +9446,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.276541531108437</v>
+        <v>0.278441531108437</v>
       </c>
       <c r="C97">
-        <v>-20.18654359139055</v>
+        <v>-20.58024752889735</v>
       </c>
       <c r="D97">
-        <v>6.489956408609449</v>
+        <v>6.436952471102648</v>
       </c>
       <c r="E97">
-        <v>31.1965</v>
+        <v>31.5372</v>
       </c>
       <c r="F97">
-        <v>32.3665</v>
+        <v>32.7072</v>
       </c>
       <c r="G97">
         <v>5.69</v>
@@ -9482,37 +9482,37 @@
         <v>0.377</v>
       </c>
       <c r="M97">
-        <v>7.632020700000001</v>
+        <v>7.712357760000001</v>
       </c>
       <c r="N97">
-        <v>-7.255020700000001</v>
+        <v>-7.335357760000001</v>
       </c>
       <c r="O97">
-        <v>-1.45100414</v>
+        <v>-1.467071552</v>
       </c>
       <c r="P97">
-        <v>-5.804016560000001</v>
+        <v>-5.868286208000001</v>
       </c>
       <c r="Q97">
-        <v>-5.447016560000001</v>
+        <v>-5.511286208</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.094892436081274</v>
+        <v>1.357165545101593</v>
       </c>
       <c r="T97">
-        <v>20.44876425394845</v>
+        <v>25.56095531743557</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.009879428131005986</v>
+        <v>0.009776517421308008</v>
       </c>
       <c r="W97">
-        <v>0.2334704308467088</v>
+        <v>0.2334946971920556</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.04939714065502987</v>
+        <v>0.04888258710654003</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9528,22 +9528,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2784415311084369</v>
+        <v>0.280341531108437</v>
       </c>
       <c r="C98">
-        <v>-20.58024752889735</v>
+        <v>-20.97309270607469</v>
       </c>
       <c r="D98">
-        <v>6.436952471102651</v>
+        <v>6.384807293925308</v>
       </c>
       <c r="E98">
-        <v>31.5372</v>
+        <v>31.8779</v>
       </c>
       <c r="F98">
-        <v>32.7072</v>
+        <v>33.0479</v>
       </c>
       <c r="G98">
         <v>5.69</v>
@@ -9564,37 +9564,37 @@
         <v>0.377</v>
       </c>
       <c r="M98">
-        <v>7.712357760000001</v>
+        <v>7.79269482</v>
       </c>
       <c r="N98">
-        <v>-7.335357760000001</v>
+        <v>-7.415694820000001</v>
       </c>
       <c r="O98">
-        <v>-1.467071552</v>
+        <v>-1.483138964</v>
       </c>
       <c r="P98">
-        <v>-5.868286208000001</v>
+        <v>-5.932555856</v>
       </c>
       <c r="Q98">
-        <v>-5.511286208</v>
+        <v>-5.575555856</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.357165545101589</v>
+        <v>1.794287393468786</v>
       </c>
       <c r="T98">
-        <v>25.5609553174355</v>
+        <v>34.08127375658067</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.009776517421308008</v>
+        <v>0.00967572858191308</v>
       </c>
       <c r="W98">
-        <v>0.2334946971920556</v>
+        <v>0.2335184632003849</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.04888258710654003</v>
+        <v>0.04837864290956539</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9610,22 +9610,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.280341531108437</v>
+        <v>0.282241531108437</v>
       </c>
       <c r="C99">
-        <v>-20.97309270607469</v>
+        <v>-21.36509982543561</v>
       </c>
       <c r="D99">
-        <v>6.384807293925308</v>
+        <v>6.333500174564391</v>
       </c>
       <c r="E99">
-        <v>31.8779</v>
+        <v>32.2186</v>
       </c>
       <c r="F99">
-        <v>33.0479</v>
+        <v>33.3886</v>
       </c>
       <c r="G99">
         <v>5.69</v>
@@ -9646,37 +9646,37 @@
         <v>0.377</v>
       </c>
       <c r="M99">
-        <v>7.79269482</v>
+        <v>7.873031879999999</v>
       </c>
       <c r="N99">
-        <v>-7.415694820000001</v>
+        <v>-7.496031879999999</v>
       </c>
       <c r="O99">
-        <v>-1.483138964</v>
+        <v>-1.499206376</v>
       </c>
       <c r="P99">
-        <v>-5.932555856</v>
+        <v>-5.996825503999999</v>
       </c>
       <c r="Q99">
-        <v>-5.575555856</v>
+        <v>-5.639825503999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.794287393468786</v>
+        <v>2.668531090203178</v>
       </c>
       <c r="T99">
-        <v>34.08127375658067</v>
+        <v>51.12191063487101</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.00967572858191308</v>
+        <v>0.009576996657607846</v>
       </c>
       <c r="W99">
-        <v>0.2335184632003849</v>
+        <v>0.2335417441881361</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.04837864290956539</v>
+        <v>0.04788498328803925</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9692,22 +9692,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.282241531108437</v>
+        <v>0.284141531108437</v>
       </c>
       <c r="C100">
-        <v>-21.36509982543561</v>
+        <v>-21.75628892935178</v>
       </c>
       <c r="D100">
-        <v>6.333500174564391</v>
+        <v>6.283011070648224</v>
       </c>
       <c r="E100">
-        <v>32.2186</v>
+        <v>32.5593</v>
       </c>
       <c r="F100">
-        <v>33.3886</v>
+        <v>33.7293</v>
       </c>
       <c r="G100">
         <v>5.69</v>
@@ -9728,37 +9728,37 @@
         <v>0.377</v>
       </c>
       <c r="M100">
-        <v>7.873031879999999</v>
+        <v>7.953368940000001</v>
       </c>
       <c r="N100">
-        <v>-7.496031879999999</v>
+        <v>-7.576368940000001</v>
       </c>
       <c r="O100">
-        <v>-1.499206376</v>
+        <v>-1.515273788</v>
       </c>
       <c r="P100">
-        <v>-5.996825503999999</v>
+        <v>-6.061095152000001</v>
       </c>
       <c r="Q100">
-        <v>-5.639825503999999</v>
+        <v>-5.704095152000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.668531090203178</v>
+        <v>5.291262180406357</v>
       </c>
       <c r="T100">
-        <v>51.12191063487101</v>
+        <v>102.243821269742</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.009576996657607846</v>
+        <v>0.009480259317632007</v>
       </c>
       <c r="W100">
-        <v>0.2335417441881361</v>
+        <v>0.2335645548529024</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9766,91 +9766,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.04788498328803925</v>
+        <v>0.04740129658816006</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.284141531108437</v>
-      </c>
-      <c r="C101">
-        <v>-21.75628892935178</v>
-      </c>
-      <c r="D101">
-        <v>6.283011070648224</v>
-      </c>
-      <c r="E101">
-        <v>32.5593</v>
-      </c>
-      <c r="F101">
-        <v>33.7293</v>
-      </c>
-      <c r="G101">
-        <v>5.69</v>
-      </c>
-      <c r="H101">
-        <v>32.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.734</v>
-      </c>
-      <c r="K101">
-        <v>0.357</v>
-      </c>
-      <c r="L101">
-        <v>0.377</v>
-      </c>
-      <c r="M101">
-        <v>7.953368940000001</v>
-      </c>
-      <c r="N101">
-        <v>-7.576368940000001</v>
-      </c>
-      <c r="O101">
-        <v>-1.515273788</v>
-      </c>
-      <c r="P101">
-        <v>-6.061095152000001</v>
-      </c>
-      <c r="Q101">
-        <v>-5.704095152000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.291262180406357</v>
-      </c>
-      <c r="T101">
-        <v>102.243821269742</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.009480259317632007</v>
-      </c>
-      <c r="W101">
-        <v>0.2335645548529024</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.04740129658816006</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
